--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,11 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,11 +440,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -446,7 +458,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,6 +540,5046 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21HOULAL-HOUASENGUN28-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-66.40000000000001</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>79</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-HOUASENGUN28-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>79</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>79</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21HOULAL-HOUATHOMPSON1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-HOUATHOMPSON1-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>30</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20TORCLE-TORBINGRAM3-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>89</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-80.59999999999999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>89</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20TORCLE-TORBINGRAM3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cason Wallace</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-49.2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR19PHXOKC-OKCCWALLACE22-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>89</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-72</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>89</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR19PHXOKC-OKCCHOLMGREN7-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>86</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-74</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR19PHXOKC-OKCCHOLMGREN7-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cj Mccollum</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-84.3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-ATLCMCCOLLUM3-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>De'Aaron Fox</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-SASDFOX4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>De'Aaron Fox</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>79</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-76</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>79</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PORSAS-SASDFOX4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>54</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>54</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21HOULAL-LALDAYTON5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-LALDAYTON5-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deni Avdija</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-45.6</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-PORDAVDIJA8-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deni Avdija</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>79</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-45.9</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>79</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PORSAS-PORDAVDIJA8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20TORCLE-CLEDSCHRODER8-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-54.7</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-BOSDWHITE9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>59</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-54.4</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>59</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-SASDVASSELL24-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Donovan Clingan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PORSAS-PORDCLINGAN23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Donovan Clingan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>59</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>59</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-PORDCLINGAN23-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>59</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-50.4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>59</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-SASDHARPER2-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dyson Daniels</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>79</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>79</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-ATLDDANIELS5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dyson Daniels</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>59</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-54.5</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>59</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-ATLDDANIELS5-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>49</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>49</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR19PHXOKC-OKCIHARTENSTEIN55-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>59</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR19PHXOKC-OKCIHARTENSTEIN55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>79</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-47.7</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>79</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21HOULAL-HOUJSMITH10-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>25</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>59</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>59</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-HOUJSMITH10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jake Laravia</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>59</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>59</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-LALJLARAVIA12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>48</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-45</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>48</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-NYKJBRUNSON11-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>79</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-76</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>79</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-NYKJBRUNSON11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-ATLJJOHNSON1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>30</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>59</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-53.1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>59</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-ATLJJOHNSON1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Jalen Williams</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>16</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR19PHXOKC-OKCJWILLIAMS8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jalen Williams</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>30</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>59</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>59</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR19PHXOKC-OKCJWILLIAMS8-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>24</v>
+      </c>
+      <c r="G37" t="n">
+        <v>28</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>28</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-BOSJBROWN7-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>79</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-47.9</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>79</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-BOSJBROWN7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jaylon Tyson</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>59</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>59</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20TORCLE-CLEJTYSON20-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-31.9</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>100</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-BOSJTATUM0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>35</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>59</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>59</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-BOSJTATUM0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Jerami Grant</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>33</v>
+      </c>
+      <c r="G42" t="n">
+        <v>59</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-26</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>59</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-PORJGRANT9-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Jonathan Kuminga</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>79</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-64.90000000000001</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>79</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-ATLJKUMINGA0-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Jonathan Kuminga</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>79</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-76</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>79</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-ATLJKUMINGA0-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>20</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>16</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>16</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-NYKJHART3-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-66.59999999999999</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>100</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-NYKJHART3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Jrue Holiday</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>25</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G47" t="n">
+        <v>59</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-46.2</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>59</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-PORJHOLIDAY5-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Jrue Holiday</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>79</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-66.8</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>79</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PORSAS-PORJHOLIDAY5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>30</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>59</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>59</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-NYKKTOWNS32-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>16</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>13</v>
+      </c>
+      <c r="G50" t="n">
+        <v>79</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-66</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>79</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-NYKKTOWNS32-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>25</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>59</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-54.4</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>59</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-PHIKOUBRE9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>79</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-71.90000000000001</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>79</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-PHIKOUBRE9-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>35</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G53" t="n">
+        <v>16</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>16</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-HOUKDURANT7-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>79</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-66.90000000000001</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>79</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21HOULAL-HOUKDURANT7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>35</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>12</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>12</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-LALLJAMES23-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>44</v>
+      </c>
+      <c r="G56" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>100</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21HOULAL-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>20</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>100</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-88.8</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>100</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-LALMSMART36-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>25</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>59</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>59</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-NYKMBRIDGES25-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>79</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-76</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>79</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-NYKMBRIDGES25-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mitchell Robinson</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>25</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>59</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>59</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-NYKMROBINSON23-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mitchell Robinson</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>79</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-61.7</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>79</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-NYKMROBINSON23-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>25</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>59</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>59</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-BOSNQUETA88-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" t="n">
+        <v>79</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-72</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>79</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-BOSNQUETA88-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nickeil Alexander-Walker</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>30</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>59</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-46.2</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>59</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-ATLNALEXANDERWALKER7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nickeil Alexander-Walker</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>8</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>79</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-74.5</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>79</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-ATLNALEXANDERWALKER7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>20</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G66" t="n">
+        <v>43</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-34.8</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>43</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-BOSNVUCEVIC4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>31</v>
+      </c>
+      <c r="G67" t="n">
+        <v>79</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>79</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-BOSNVUCEVIC4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Og Anunoby</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>25</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G68" t="n">
+        <v>59</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-37.4</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>59</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-NYKOANUNOBY8-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Og Anunoby</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G69" t="n">
+        <v>100</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-65.3</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>100</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-NYKOANUNOBY8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Onyeka Okongwu</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>100</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-47.9</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>100</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR20ATLNYK-ATLOOKONGWU17-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Onyeka Okongwu</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>25</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G71" t="n">
+        <v>59</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-54.8</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>59</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR20ATLNYK-ATLOOKONGWU17-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G72" t="n">
+        <v>79</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-70.59999999999999</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>79</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>30</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>8</v>
+      </c>
+      <c r="G73" t="n">
+        <v>100</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-92</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>100</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-PHIPGEORGE8-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G74" t="n">
+        <v>59</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-42.2</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>59</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-BOSPPRITCHARD11-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>79</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-75.8</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>79</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-BOSPPRITCHARD11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Reed Sheppard</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>25</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>59</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>59</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-HOURSHEPPARD15-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>25</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>59</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>59</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-LALRHACHIMURA28-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sam Hauser</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>59</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-44.8</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>59</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-BOSSHAUSER30-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Shaedon Sharpe</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>59</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>59</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-PORSSHARPE17-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>40</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>59</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-44.5</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>59</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR19PHXOKC-OKCSGILGEOUSALEXANDER2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="n">
+        <v>89</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-86</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>89</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR19PHXOKC-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>25</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>60</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-57</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>60</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-SASSCASTLE5-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>26</v>
+      </c>
+      <c r="G83" t="n">
+        <v>100</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-74</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>100</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PORSAS-SASSCASTLE5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>8</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="G84" t="n">
+        <v>99</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-44.4</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>99</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21HOULAL-HOUTEASON17-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>20</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G85" t="n">
+        <v>59</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-52.2</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>59</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21HOULAL-HOUTEASON17-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Toumani Camara</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>20</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G86" t="n">
+        <v>59</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-43.6</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>59</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-PORTCAMARA33-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>35</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>25</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>25</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-PHITMAXEY0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>279</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PORSAS-SASVWEMBANYAMA1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>40</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>11</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>9</v>
+      </c>
+      <c r="K89" t="n">
+        <v>11</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PORSAS-SASVWEMBANYAMA1-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G90" t="n">
+        <v>100</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-67.59999999999999</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>100</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR21PHIBOS-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>25</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>14</v>
+      </c>
+      <c r="G91" t="n">
+        <v>100</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-86</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>100</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR21PHIBOS-PHIVEDGECOMBE77-25</t>
         </is>
       </c>
     </row>
@@ -542,10 +5594,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -603,6 +5655,33 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -614,10 +5693,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -655,6 +5734,1066 @@
         <is>
           <t>Total P&amp;L ($)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jalen Williams</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>De'Aaron Fox</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Donovan Clingan</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jalen Johnson</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Og Anunoby</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dyson Daniels</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Deni Avdija</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Nickeil Alexander-Walker</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jrue Holiday</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Onyeka Okongwu</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mitchell Robinson</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jonathan Kuminga</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Shaedon Sharpe</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Jerami Grant</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Toumani Camara</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sam Hauser</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cason Wallace</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Reed Sheppard</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jaylon Tyson</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jake Laravia</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cj Mccollum</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -668,7 +6807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -711,6 +6850,46 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -47,12 +47,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -587,9 +587,9 @@
       <c r="K2" t="n">
         <v>100</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -643,9 +643,9 @@
       <c r="K3" t="n">
         <v>79</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -699,12 +699,20 @@
       <c r="K4" t="n">
         <v>79</v>
       </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR21HOULAL-HOUATHOMPSON1-8</t>
@@ -755,12 +763,20 @@
       <c r="K5" t="n">
         <v>59</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR21HOULAL-HOUATHOMPSON1-25</t>
@@ -811,9 +827,9 @@
       <c r="K6" t="n">
         <v>30</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -867,9 +883,9 @@
       <c r="K7" t="n">
         <v>89</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -923,12 +939,20 @@
       <c r="K8" t="n">
         <v>59</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR19PHXOKC-OKCCWALLACE22-20</t>
@@ -979,12 +1003,20 @@
       <c r="K9" t="n">
         <v>89</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR19PHXOKC-OKCCHOLMGREN7-12</t>
@@ -1035,12 +1067,20 @@
       <c r="K10" t="n">
         <v>86</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L10" t="n">
+        <v>19</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR19PHXOKC-OKCCHOLMGREN7-25</t>
@@ -1091,9 +1131,9 @@
       <c r="K11" t="n">
         <v>100</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1147,9 +1187,9 @@
       <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1203,9 +1243,9 @@
       <c r="K13" t="n">
         <v>79</v>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1259,9 +1299,9 @@
       <c r="K14" t="n">
         <v>54</v>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1315,9 +1355,9 @@
       <c r="K15" t="n">
         <v>59</v>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1371,9 +1411,9 @@
       <c r="K16" t="n">
         <v>59</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1427,9 +1467,9 @@
       <c r="K17" t="n">
         <v>79</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1483,9 +1523,9 @@
       <c r="K18" t="n">
         <v>59</v>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1539,9 +1579,9 @@
       <c r="K19" t="n">
         <v>59</v>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1595,9 +1635,9 @@
       <c r="K20" t="n">
         <v>59</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1651,9 +1691,9 @@
       <c r="K21" t="n">
         <v>100</v>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1707,9 +1747,9 @@
       <c r="K22" t="n">
         <v>59</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1763,9 +1803,9 @@
       <c r="K23" t="n">
         <v>59</v>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -1819,9 +1859,9 @@
       <c r="K24" t="n">
         <v>79</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1875,9 +1915,9 @@
       <c r="K25" t="n">
         <v>59</v>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -1931,12 +1971,20 @@
       <c r="K26" t="n">
         <v>49</v>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L26" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR19PHXOKC-OKCIHARTENSTEIN55-12</t>
@@ -1987,12 +2035,20 @@
       <c r="K27" t="n">
         <v>59</v>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L27" t="n">
+        <v>9</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR19PHXOKC-OKCIHARTENSTEIN55-20</t>
@@ -2043,12 +2099,20 @@
       <c r="K28" t="n">
         <v>79</v>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR21HOULAL-HOUJSMITH10-8</t>
@@ -2099,12 +2163,20 @@
       <c r="K29" t="n">
         <v>59</v>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR21HOULAL-HOUJSMITH10-25</t>
@@ -2155,9 +2227,9 @@
       <c r="K30" t="n">
         <v>59</v>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2211,9 +2283,9 @@
       <c r="K31" t="n">
         <v>48</v>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2267,9 +2339,9 @@
       <c r="K32" t="n">
         <v>79</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2323,9 +2395,9 @@
       <c r="K33" t="n">
         <v>100</v>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2379,9 +2451,9 @@
       <c r="K34" t="n">
         <v>59</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2435,12 +2507,22 @@
       <c r="K35" t="n">
         <v>5</v>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR19PHXOKC-OKCJWILLIAMS8-8</t>
@@ -2491,12 +2573,20 @@
       <c r="K36" t="n">
         <v>59</v>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L36" t="n">
+        <v>19</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR19PHXOKC-OKCJWILLIAMS8-30</t>
@@ -2547,9 +2637,9 @@
       <c r="K37" t="n">
         <v>28</v>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2603,9 +2693,9 @@
       <c r="K38" t="n">
         <v>79</v>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2659,9 +2749,9 @@
       <c r="K39" t="n">
         <v>59</v>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2715,9 +2805,9 @@
       <c r="K40" t="n">
         <v>100</v>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2771,9 +2861,9 @@
       <c r="K41" t="n">
         <v>59</v>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2827,9 +2917,9 @@
       <c r="K42" t="n">
         <v>59</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -2883,9 +2973,9 @@
       <c r="K43" t="n">
         <v>79</v>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2939,9 +3029,9 @@
       <c r="K44" t="n">
         <v>79</v>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -2995,9 +3085,9 @@
       <c r="K45" t="n">
         <v>16</v>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3051,9 +3141,9 @@
       <c r="K46" t="n">
         <v>100</v>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3107,9 +3197,9 @@
       <c r="K47" t="n">
         <v>59</v>
       </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3163,9 +3253,9 @@
       <c r="K48" t="n">
         <v>79</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3219,9 +3309,9 @@
       <c r="K49" t="n">
         <v>59</v>
       </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3275,9 +3365,9 @@
       <c r="K50" t="n">
         <v>79</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -3331,12 +3421,20 @@
       <c r="K51" t="n">
         <v>59</v>
       </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR21PHIBOS-PHIKOUBRE9-25</t>
@@ -3387,12 +3485,20 @@
       <c r="K52" t="n">
         <v>79</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L52" t="n">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR21PHIBOS-PHIKOUBRE9-10</t>
@@ -3443,9 +3549,9 @@
       <c r="K53" t="n">
         <v>16</v>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3499,9 +3605,9 @@
       <c r="K54" t="n">
         <v>79</v>
       </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3555,9 +3661,9 @@
       <c r="K55" t="n">
         <v>12</v>
       </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3611,9 +3717,9 @@
       <c r="K56" t="n">
         <v>100</v>
       </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3667,9 +3773,9 @@
       <c r="K57" t="n">
         <v>100</v>
       </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3723,9 +3829,9 @@
       <c r="K58" t="n">
         <v>59</v>
       </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3779,9 +3885,9 @@
       <c r="K59" t="n">
         <v>79</v>
       </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -3835,12 +3941,20 @@
       <c r="K60" t="n">
         <v>59</v>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L60" t="n">
+        <v>10</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR20ATLNYK-NYKMROBINSON23-25</t>
@@ -3891,12 +4005,20 @@
       <c r="K61" t="n">
         <v>79</v>
       </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L61" t="n">
+        <v>6</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR20ATLNYK-NYKMROBINSON23-12</t>
@@ -3947,9 +4069,9 @@
       <c r="K62" t="n">
         <v>59</v>
       </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -4003,9 +4125,9 @@
       <c r="K63" t="n">
         <v>79</v>
       </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4059,9 +4181,9 @@
       <c r="K64" t="n">
         <v>59</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -4115,9 +4237,9 @@
       <c r="K65" t="n">
         <v>79</v>
       </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -4171,9 +4293,9 @@
       <c r="K66" t="n">
         <v>43</v>
       </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -4227,9 +4349,9 @@
       <c r="K67" t="n">
         <v>79</v>
       </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4283,9 +4405,9 @@
       <c r="K68" t="n">
         <v>59</v>
       </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -4339,9 +4461,9 @@
       <c r="K69" t="n">
         <v>100</v>
       </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4395,9 +4517,9 @@
       <c r="K70" t="n">
         <v>100</v>
       </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -4451,9 +4573,9 @@
       <c r="K71" t="n">
         <v>59</v>
       </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -4507,9 +4629,9 @@
       <c r="K72" t="n">
         <v>79</v>
       </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4563,9 +4685,9 @@
       <c r="K73" t="n">
         <v>100</v>
       </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -4619,9 +4741,9 @@
       <c r="K74" t="n">
         <v>59</v>
       </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -4675,9 +4797,9 @@
       <c r="K75" t="n">
         <v>79</v>
       </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -4731,9 +4853,9 @@
       <c r="K76" t="n">
         <v>59</v>
       </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -4787,9 +4909,9 @@
       <c r="K77" t="n">
         <v>59</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -4843,9 +4965,9 @@
       <c r="K78" t="n">
         <v>59</v>
       </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -4899,9 +5021,9 @@
       <c r="K79" t="n">
         <v>59</v>
       </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -4955,12 +5077,20 @@
       <c r="K80" t="n">
         <v>59</v>
       </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L80" t="n">
+        <v>37</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR19PHXOKC-OKCSGILGEOUSALEXANDER2-40</t>
@@ -5011,12 +5141,20 @@
       <c r="K81" t="n">
         <v>89</v>
       </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L81" t="n">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR19PHXOKC-OKCSGILGEOUSALEXANDER2-8</t>
@@ -5067,9 +5205,9 @@
       <c r="K82" t="n">
         <v>60</v>
       </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -5123,9 +5261,9 @@
       <c r="K83" t="n">
         <v>100</v>
       </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5179,9 +5317,9 @@
       <c r="K84" t="n">
         <v>99</v>
       </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5235,9 +5373,9 @@
       <c r="K85" t="n">
         <v>59</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5291,9 +5429,9 @@
       <c r="K86" t="n">
         <v>59</v>
       </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5347,9 +5485,9 @@
       <c r="K87" t="n">
         <v>25</v>
       </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -5403,9 +5541,9 @@
       <c r="K88" t="n">
         <v>5</v>
       </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -5459,9 +5597,9 @@
       <c r="K89" t="n">
         <v>11</v>
       </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -5515,9 +5653,9 @@
       <c r="K90" t="n">
         <v>100</v>
       </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5571,9 +5709,9 @@
       <c r="K91" t="n">
         <v>100</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -5665,22 +5803,26 @@
         <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.059</v>
+      </c>
       <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.05</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5769,11 +5911,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="4">
@@ -5949,9 +6093,11 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
@@ -6006,12 +6152,14 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -6129,9 +6277,11 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
@@ -6229,9 +6379,11 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
@@ -6269,9 +6421,11 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
@@ -6329,9 +6483,11 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
@@ -6469,9 +6625,11 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
@@ -6609,9 +6767,11 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -6863,9 +7023,11 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
@@ -6880,14 +7042,16 @@
         <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.125</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5721,6 +5721,1406 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cason Wallace</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>20</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G92" t="n">
+        <v>59</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>59</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-OKCCWALLACE22-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>100</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-40.9</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>100</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR22PHXOKC-OKCCHOLMGREN7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>30</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G94" t="n">
+        <v>59</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-52.1</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>59</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-OKCCHOLMGREN7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Devin Booker</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>35</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" t="n">
+        <v>64</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-61</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>64</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-PHXDBOOKER1-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Devin Booker</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" t="n">
+        <v>79</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-76</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>79</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR22PHXOKC-PHXDBOOKER1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Dillon Brooks</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" t="n">
+        <v>85</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>85</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR22PHXOKC-PHXDBROOKS3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Dillon Brooks</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>85</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>85</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR22PHXOKC-PHXDBROOKS3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dillon Brooks</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" t="n">
+        <v>85</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>85</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR22PHXOKC-PHXDBROOKS3-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Dillon Brooks</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>25</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>100</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-97</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>100</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-PHXDBROOKS3-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>20</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" t="n">
+        <v>59</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>59</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-OKCIHARTENSTEIN55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G102" t="n">
+        <v>85</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-62.3</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>85</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR22PHXOKC-OKCIHARTENSTEIN55-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>30</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>399</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-PHXJGREEN4-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G104" t="n">
+        <v>85</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-78.90000000000001</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>85</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR22PHXOKC-PHXJGREEN4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>84</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>84</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR22PHXOKC-PHXJGREEN4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" t="n">
+        <v>85</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>85</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR22PHXOKC-PHXJGREEN4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Jalen Williams</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>30</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-OKCJWILLIAMS8-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Jalen Williams</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G108" t="n">
+        <v>85</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-76.7</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>85</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR22PHXOKC-OKCJWILLIAMS8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Jalen Williams</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" t="n">
+        <v>85</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>85</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR22PHXOKC-OKCJWILLIAMS8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>20</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>59</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-56</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>59</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-OKCLDORT5-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G111" t="n">
+        <v>85</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-76.90000000000001</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>85</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR22PHXOKC-OKCLDORT5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>84</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>84</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR22PHXOKC-OKCLDORT5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>40</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>3</v>
+      </c>
+      <c r="G113" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>30</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR22PHXOKC-OKCSGILGEOUSALEXANDER2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" t="n">
+        <v>85</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>85</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR22PHXOKC-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>3</v>
+      </c>
+      <c r="G115" t="n">
+        <v>85</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-82</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>85</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR22PHXOKC-OKCSGILGEOUSALEXANDER2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" t="n">
+        <v>100</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-97</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>100</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR22PHXOKC-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5732,7 +7132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5824,6 +7224,33 @@
         <v>-0.05</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5835,7 +7262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5881,19 +7308,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
@@ -5905,7 +7334,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -5923,19 +7352,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
@@ -5943,19 +7374,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
@@ -5963,11 +7396,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -5983,11 +7416,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -6003,11 +7436,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6023,7 +7456,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6043,7 +7476,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6063,7 +7496,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6083,7 +7516,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6093,11 +7526,9 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>0</v>
       </c>
@@ -6105,7 +7536,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6125,7 +7556,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6145,21 +7576,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -6167,7 +7596,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6187,7 +7616,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6207,7 +7636,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6227,7 +7656,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6247,19 +7676,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
@@ -6267,7 +7698,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6277,11 +7708,9 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
         <v>0</v>
       </c>
@@ -6289,7 +7718,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6309,7 +7738,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6329,7 +7758,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6349,7 +7778,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6369,7 +7798,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6379,11 +7808,9 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
         <v>0</v>
       </c>
@@ -6391,7 +7818,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6411,7 +7838,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6421,11 +7848,9 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
         <v>0</v>
       </c>
@@ -6433,7 +7858,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6453,7 +7878,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6463,9 +7888,11 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
@@ -6473,7 +7900,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6483,11 +7910,9 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
         <v>0</v>
       </c>
@@ -6495,7 +7920,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6505,9 +7930,11 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
@@ -6515,7 +7942,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6525,9 +7952,11 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
@@ -6535,7 +7964,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6555,7 +7984,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6575,7 +8004,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6585,9 +8014,11 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
@@ -6595,7 +8026,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6615,7 +8046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6625,11 +8056,9 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
         <v>0</v>
       </c>
@@ -6637,11 +8066,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -6657,11 +8086,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -6677,11 +8106,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -6697,11 +8126,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -6717,11 +8146,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -6737,7 +8166,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6757,7 +8186,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6767,11 +8196,9 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -6779,7 +8206,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6799,7 +8226,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6819,7 +8246,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6839,7 +8266,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6859,7 +8286,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -6879,7 +8306,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6899,7 +8326,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jake Laravia</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -6919,7 +8346,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cj Mccollum</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -6939,7 +8366,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -6953,6 +8380,86 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jake Laravia</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Cj Mccollum</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6967,7 +8474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7013,21 +8520,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>0</v>
       </c>
@@ -7035,23 +8540,65 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>REB</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>37</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B4" t="n">
+        <v>43</v>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>0.125</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7121,6 +7121,4334 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>30</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G117" t="n">
+        <v>12</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>12</v>
+      </c>
+      <c r="L117" t="n">
+        <v>33</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-HOUASENGUN28-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G118" t="n">
+        <v>25</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>25</v>
+      </c>
+      <c r="L118" t="n">
+        <v>6</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24LALHOU-HOUASENGUN28-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>9</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G119" t="n">
+        <v>55</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>55</v>
+      </c>
+      <c r="L119" t="n">
+        <v>16</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24LALHOU-HOUASENGUN28-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10</v>
+      </c>
+      <c r="H120" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>10</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR24LALHOU-HOUASENGUN28-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G121" t="n">
+        <v>18</v>
+      </c>
+      <c r="H121" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>10</v>
+      </c>
+      <c r="K121" t="n">
+        <v>18</v>
+      </c>
+      <c r="L121" t="n">
+        <v>3</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24LALHOU-HOUATHOMPSON1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>30</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G122" t="n">
+        <v>6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>6</v>
+      </c>
+      <c r="L122" t="n">
+        <v>26</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-HOUATHOMPSON1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G123" t="n">
+        <v>26</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>26</v>
+      </c>
+      <c r="L123" t="n">
+        <v>4</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24LALHOU-HOUATHOMPSON1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G124" t="n">
+        <v>49</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>49</v>
+      </c>
+      <c r="L124" t="n">
+        <v>11</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24LALHOU-HOUATHOMPSON1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>7</v>
+      </c>
+      <c r="L125" t="n">
+        <v>3</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR24LALHOU-HOUATHOMPSON1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>25</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>3</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>5</v>
+      </c>
+      <c r="L126" t="n">
+        <v>2</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-LALDAYTON5-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>9</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G127" t="n">
+        <v>45</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>45</v>
+      </c>
+      <c r="L127" t="n">
+        <v>6</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24LALHOU-LALDAYTON5-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>13</v>
+      </c>
+      <c r="G128" t="n">
+        <v>10</v>
+      </c>
+      <c r="H128" t="n">
+        <v>3</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>10</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR24LALHOU-LALDAYTON5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>14</v>
+      </c>
+      <c r="G129" t="n">
+        <v>11</v>
+      </c>
+      <c r="H129" t="n">
+        <v>3</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>11</v>
+      </c>
+      <c r="L129" t="n">
+        <v>2</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-BOSDWHITE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>25</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>8</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>8</v>
+      </c>
+      <c r="L130" t="n">
+        <v>11</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-BOSDWHITE9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G131" t="n">
+        <v>10</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>10</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-BOSDWHITE9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>25</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>3</v>
+      </c>
+      <c r="G132" t="n">
+        <v>10</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>10</v>
+      </c>
+      <c r="L132" t="n">
+        <v>24</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-HOUJSMITH10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G133" t="n">
+        <v>35</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>35</v>
+      </c>
+      <c r="L133" t="n">
+        <v>6</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24LALHOU-HOUJSMITH10-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Jake Laravia</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>25</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>3</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" t="n">
+        <v>2</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-LALJLARAVIA12-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>35</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G135" t="n">
+        <v>18</v>
+      </c>
+      <c r="H135" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>18</v>
+      </c>
+      <c r="L135" t="n">
+        <v>25</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-BOSJBROWN7-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G136" t="n">
+        <v>14</v>
+      </c>
+      <c r="H136" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>14</v>
+      </c>
+      <c r="L136" t="n">
+        <v>4</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-BOSJBROWN7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="G137" t="n">
+        <v>30</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>30</v>
+      </c>
+      <c r="L137" t="n">
+        <v>7</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-BOSJBROWN7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>3</v>
+      </c>
+      <c r="G138" t="n">
+        <v>9</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>9</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-BOSJBROWN7-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G139" t="n">
+        <v>32</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>32</v>
+      </c>
+      <c r="L139" t="n">
+        <v>7</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-BOSJTATUM0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G140" t="n">
+        <v>15</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>15</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-BOSJTATUM0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>16</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G141" t="n">
+        <v>10</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>10</v>
+      </c>
+      <c r="L141" t="n">
+        <v>5</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-BOSJTATUM0-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>35</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>3</v>
+      </c>
+      <c r="G142" t="n">
+        <v>9</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>9</v>
+      </c>
+      <c r="L142" t="n">
+        <v>25</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-BOSJTATUM0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G143" t="n">
+        <v>15</v>
+      </c>
+      <c r="H143" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>15</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-PHIKOUBRE9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>3</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>4</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-PHIKOUBRE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>25</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G145" t="n">
+        <v>6</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>6</v>
+      </c>
+      <c r="L145" t="n">
+        <v>17</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-PHIKOUBRE9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>8</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G146" t="n">
+        <v>22</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>22</v>
+      </c>
+      <c r="L146" t="n">
+        <v>6</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-PHIKOUBRE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>8</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G147" t="n">
+        <v>14</v>
+      </c>
+      <c r="H147" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>12</v>
+      </c>
+      <c r="K147" t="n">
+        <v>14</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24LALHOU-HOUKDURANT7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>35</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G148" t="n">
+        <v>11</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>11</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-HOUKDURANT7-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>17</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>17</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24LALHOU-HOUKDURANT7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Kevin Durant</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>3</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G150" t="n">
+        <v>8</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>8</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR24LALHOU-HOUKDURANT7-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>3</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G151" t="n">
+        <v>12</v>
+      </c>
+      <c r="H151" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>12</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24LALHOU-LALLJAMES23-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>9</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>41</v>
+      </c>
+      <c r="G152" t="n">
+        <v>48</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>48</v>
+      </c>
+      <c r="L152" t="n">
+        <v>6</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24LALHOU-LALLJAMES23-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>35</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" t="n">
+        <v>11</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>11</v>
+      </c>
+      <c r="L153" t="n">
+        <v>29</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-LALLJAMES23-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>8</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G154" t="n">
+        <v>43</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>43</v>
+      </c>
+      <c r="L154" t="n">
+        <v>13</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24LALHOU-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>3</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>3</v>
+      </c>
+      <c r="G155" t="n">
+        <v>7</v>
+      </c>
+      <c r="H155" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>7</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR24LALHOU-LALLJAMES23-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>25</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G156" t="n">
+        <v>5</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>5</v>
+      </c>
+      <c r="L156" t="n">
+        <v>21</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-LALMSMART36-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>8</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G157" t="n">
+        <v>18</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>18</v>
+      </c>
+      <c r="L157" t="n">
+        <v>10</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24LALHOU-LALMSMART36-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>3</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G158" t="n">
+        <v>22</v>
+      </c>
+      <c r="H158" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>22</v>
+      </c>
+      <c r="L158" t="n">
+        <v>5</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24LALHOU-LALMSMART36-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>8</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="G159" t="n">
+        <v>50</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>50</v>
+      </c>
+      <c r="L159" t="n">
+        <v>7</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-BOSNQUETA88-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>3</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G160" t="n">
+        <v>15</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>15</v>
+      </c>
+      <c r="L160" t="n">
+        <v>2</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR24BOSPHI-BOSNQUETA88-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>25</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>3</v>
+      </c>
+      <c r="G161" t="n">
+        <v>4</v>
+      </c>
+      <c r="H161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>4</v>
+      </c>
+      <c r="L161" t="n">
+        <v>6</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-BOSNQUETA88-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G162" t="n">
+        <v>8</v>
+      </c>
+      <c r="H162" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>32</v>
+      </c>
+      <c r="K162" t="n">
+        <v>8</v>
+      </c>
+      <c r="L162" t="n">
+        <v>6</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-BOSNVUCEVIC4-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>20</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G163" t="n">
+        <v>4</v>
+      </c>
+      <c r="H163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>4</v>
+      </c>
+      <c r="L163" t="n">
+        <v>11</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-BOSNVUCEVIC4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>30</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G164" t="n">
+        <v>9</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>9</v>
+      </c>
+      <c r="L164" t="n">
+        <v>18</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-PHIPGEORGE8-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>3</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>17</v>
+      </c>
+      <c r="H165" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>17</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-PHIPGEORGE8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>8</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>3</v>
+      </c>
+      <c r="G166" t="n">
+        <v>5</v>
+      </c>
+      <c r="H166" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>5</v>
+      </c>
+      <c r="L166" t="n">
+        <v>5</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>8</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G167" t="n">
+        <v>19</v>
+      </c>
+      <c r="H167" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>19</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>25</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>7</v>
+      </c>
+      <c r="H168" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>32</v>
+      </c>
+      <c r="K168" t="n">
+        <v>7</v>
+      </c>
+      <c r="L168" t="n">
+        <v>15</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-BOSPPRITCHARD11-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>8</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G169" t="n">
+        <v>8</v>
+      </c>
+      <c r="H169" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>8</v>
+      </c>
+      <c r="L169" t="n">
+        <v>2</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-BOSPPRITCHARD11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G170" t="n">
+        <v>4</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>4</v>
+      </c>
+      <c r="L170" t="n">
+        <v>4</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-BOSPPRITCHARD11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>3</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G171" t="n">
+        <v>14</v>
+      </c>
+      <c r="H171" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>14</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-BOSPPRITCHARD11-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Reed Sheppard</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>8</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G172" t="n">
+        <v>5</v>
+      </c>
+      <c r="H172" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>5</v>
+      </c>
+      <c r="L172" t="n">
+        <v>7</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24LALHOU-HOURSHEPPARD15-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Reed Sheppard</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>20</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G173" t="n">
+        <v>12</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>12</v>
+      </c>
+      <c r="L173" t="n">
+        <v>17</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-HOURSHEPPARD15-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>25</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" t="n">
+        <v>7</v>
+      </c>
+      <c r="H174" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>7</v>
+      </c>
+      <c r="L174" t="n">
+        <v>22</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-LALRHACHIMURA28-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sam Hauser</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>20</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G175" t="n">
+        <v>5</v>
+      </c>
+      <c r="H175" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>5</v>
+      </c>
+      <c r="L175" t="n">
+        <v>6</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-BOSSHAUSER30-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>20</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>7</v>
+      </c>
+      <c r="G176" t="n">
+        <v>8</v>
+      </c>
+      <c r="H176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>8</v>
+      </c>
+      <c r="L176" t="n">
+        <v>5</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24LALHOU-HOUTEASON17-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G177" t="n">
+        <v>11</v>
+      </c>
+      <c r="H177" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>11</v>
+      </c>
+      <c r="L177" t="n">
+        <v>4</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24LALHOU-HOUTEASON17-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>8</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="G178" t="n">
+        <v>34</v>
+      </c>
+      <c r="H178" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>11</v>
+      </c>
+      <c r="K178" t="n">
+        <v>34</v>
+      </c>
+      <c r="L178" t="n">
+        <v>6</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-PHITMAXEY0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>3</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G179" t="n">
+        <v>19</v>
+      </c>
+      <c r="H179" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>19</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-PHITMAXEY0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>35</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G180" t="n">
+        <v>21</v>
+      </c>
+      <c r="H180" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>21</v>
+      </c>
+      <c r="L180" t="n">
+        <v>31</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-PHITMAXEY0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>8</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G181" t="n">
+        <v>8</v>
+      </c>
+      <c r="H181" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>8</v>
+      </c>
+      <c r="L181" t="n">
+        <v>5</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR24BOSPHI-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>8</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G182" t="n">
+        <v>25</v>
+      </c>
+      <c r="H182" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>25</v>
+      </c>
+      <c r="L182" t="n">
+        <v>10</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR24BOSPHI-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>25</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G183" t="n">
+        <v>12</v>
+      </c>
+      <c r="H183" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>12</v>
+      </c>
+      <c r="L183" t="n">
+        <v>10</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR24BOSPHI-PHIVEDGECOMBE77-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>3</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G184" t="n">
+        <v>14</v>
+      </c>
+      <c r="H184" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>14</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR24BOSPHI-PHIVEDGECOMBE77-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7132,7 +11460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7250,6 +11578,37 @@
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>68</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.01</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7308,20 +11667,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -7330,39 +11689,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -7374,21 +11733,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>0</v>
       </c>
@@ -7396,19 +11753,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
@@ -7416,39 +11775,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
@@ -7456,19 +11819,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -7476,19 +11841,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
@@ -7496,19 +11863,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
@@ -7516,19 +11885,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
@@ -7536,39 +11907,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
@@ -7576,19 +11951,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -7596,39 +11973,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
@@ -7636,39 +12017,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
@@ -7676,20 +12061,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -7698,19 +12083,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
@@ -7718,19 +12105,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
         <v>2</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
@@ -7738,19 +12127,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
         <v>2</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.667</v>
+      </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
@@ -7758,11 +12149,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -7778,11 +12169,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -7798,19 +12189,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
         <v>2</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
@@ -7818,11 +12211,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -7838,7 +12231,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7858,7 +12251,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -7878,7 +12271,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7888,11 +12281,9 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
         <v>0</v>
       </c>
@@ -7900,7 +12291,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7920,7 +12311,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -7930,11 +12321,9 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
         <v>0</v>
       </c>
@@ -7942,7 +12331,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -7952,11 +12341,9 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
         <v>0</v>
       </c>
@@ -7964,7 +12351,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -7984,7 +12371,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -8004,7 +12391,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -8014,7 +12401,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -8026,7 +12413,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -8046,7 +12433,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -8066,7 +12453,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -8086,7 +12473,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -8106,7 +12493,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -8126,7 +12513,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -8136,9 +12523,11 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
@@ -8146,7 +12535,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -8156,9 +12545,11 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
@@ -8166,11 +12557,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8186,19 +12577,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -8206,19 +12599,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Jake Laravia</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
@@ -8226,11 +12621,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -8246,11 +12641,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -8266,11 +12661,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -8286,11 +12681,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -8306,7 +12701,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -8326,7 +12721,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -8346,7 +12741,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -8366,7 +12761,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -8386,7 +12781,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -8406,7 +12801,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jake Laravia</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -8426,7 +12821,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cj Mccollum</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -8446,7 +12841,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Cj Mccollum</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -8474,7 +12869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8524,36 +12919,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.077</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -8562,43 +12959,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>0.125</v>
+        <v>0.033</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>0</v>
+      <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P184"/>
+  <dimension ref="A1:P259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11449,6 +11455,4206 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Anthony Black</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>20</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>6</v>
+      </c>
+      <c r="H185" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>14</v>
+      </c>
+      <c r="K185" t="n">
+        <v>6</v>
+      </c>
+      <c r="M185" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-ORLABLACK0-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Anthony Black</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>8</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>3</v>
+      </c>
+      <c r="G186" t="n">
+        <v>6</v>
+      </c>
+      <c r="H186" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>6</v>
+      </c>
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DETORL-ORLABLACK0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>35</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>19</v>
+      </c>
+      <c r="H187" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>19</v>
+      </c>
+      <c r="M187" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-MINAEDWARDS5-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>3</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>14</v>
+      </c>
+      <c r="H188" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>14</v>
+      </c>
+      <c r="M188" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25DENMIN-MINAEDWARDS5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>8</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G189" t="n">
+        <v>25</v>
+      </c>
+      <c r="H189" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>25</v>
+      </c>
+      <c r="M189" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DENMIN-MINAEDWARDS5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>8</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>3</v>
+      </c>
+      <c r="G190" t="n">
+        <v>9</v>
+      </c>
+      <c r="H190" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>9</v>
+      </c>
+      <c r="M190" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DENMIN-MINAEDWARDS5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>3</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G191" t="n">
+        <v>34</v>
+      </c>
+      <c r="H191" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>7</v>
+      </c>
+      <c r="K191" t="n">
+        <v>34</v>
+      </c>
+      <c r="M191" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25DETORL-DETATHOMPSON9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>25</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>3</v>
+      </c>
+      <c r="G192" t="n">
+        <v>5</v>
+      </c>
+      <c r="H192" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>5</v>
+      </c>
+      <c r="M192" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-DETATHOMPSON9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>8</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>3</v>
+      </c>
+      <c r="G193" t="n">
+        <v>6</v>
+      </c>
+      <c r="H193" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>6</v>
+      </c>
+      <c r="M193" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DETORL-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>8</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G194" t="n">
+        <v>30</v>
+      </c>
+      <c r="H194" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>30</v>
+      </c>
+      <c r="M194" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DETORL-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Ayo Dosunmu</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>20</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G195" t="n">
+        <v>16</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>16</v>
+      </c>
+      <c r="M195" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-MINADOSUNMU13-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>3</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>21</v>
+      </c>
+      <c r="H196" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>21</v>
+      </c>
+      <c r="M196" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25DETORL-DETCCUNNINGHAM2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>8</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G197" t="n">
+        <v>24</v>
+      </c>
+      <c r="H197" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>24</v>
+      </c>
+      <c r="M197" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DETORL-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>8</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G198" t="n">
+        <v>75</v>
+      </c>
+      <c r="H198" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>75</v>
+      </c>
+      <c r="M198" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DETORL-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>40</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G199" t="n">
+        <v>11</v>
+      </c>
+      <c r="H199" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>11</v>
+      </c>
+      <c r="M199" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-DETCCUNNINGHAM2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Cameron Johnson</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>8</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G200" t="n">
+        <v>5</v>
+      </c>
+      <c r="H200" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>5</v>
+      </c>
+      <c r="M200" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DENMIN-DENCJOHNSON23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Cameron Johnson</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>20</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>3</v>
+      </c>
+      <c r="G201" t="n">
+        <v>10</v>
+      </c>
+      <c r="H201" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>10</v>
+      </c>
+      <c r="M201" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-DENCJOHNSON23-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>3</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G202" t="n">
+        <v>36</v>
+      </c>
+      <c r="H202" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>36</v>
+      </c>
+      <c r="M202" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR25OKCPHX-OKCCHOLMGREN7-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>25</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G203" t="n">
+        <v>15</v>
+      </c>
+      <c r="H203" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>15</v>
+      </c>
+      <c r="M203" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25OKCPHX-OKCCHOLMGREN7-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>9</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G204" t="n">
+        <v>57</v>
+      </c>
+      <c r="H204" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>57</v>
+      </c>
+      <c r="M204" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25OKCPHX-OKCCHOLMGREN7-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Christian Braun</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>20</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G205" t="n">
+        <v>10</v>
+      </c>
+      <c r="H205" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>10</v>
+      </c>
+      <c r="M205" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-DENCBRAUN0-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Desmond Bane</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>30</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G206" t="n">
+        <v>9</v>
+      </c>
+      <c r="H206" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>9</v>
+      </c>
+      <c r="M206" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-ORLDBANE3-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Devin Booker</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>35</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G207" t="n">
+        <v>11</v>
+      </c>
+      <c r="H207" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>11</v>
+      </c>
+      <c r="M207" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25OKCPHX-PHXDBOOKER1-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Devin Booker</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>8</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G208" t="n">
+        <v>22</v>
+      </c>
+      <c r="H208" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>22</v>
+      </c>
+      <c r="M208" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25OKCPHX-PHXDBOOKER1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Dillon Brooks</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>25</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G209" t="n">
+        <v>20</v>
+      </c>
+      <c r="H209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>20</v>
+      </c>
+      <c r="M209" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25OKCPHX-PHXDBROOKS3-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Dillon Brooks</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>3</v>
+      </c>
+      <c r="G210" t="n">
+        <v>8</v>
+      </c>
+      <c r="H210" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>8</v>
+      </c>
+      <c r="M210" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25OKCPHX-PHXDBROOKS3-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Dillon Brooks</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>8</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>3</v>
+      </c>
+      <c r="G211" t="n">
+        <v>9</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>9</v>
+      </c>
+      <c r="M211" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25OKCPHX-PHXDBROOKS3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Donte Divincenzo</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>3</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>14</v>
+      </c>
+      <c r="G212" t="n">
+        <v>14</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>14</v>
+      </c>
+      <c r="M212" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25DENMIN-MINDDIVINCENZO0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Donte Divincenzo</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>8</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>3</v>
+      </c>
+      <c r="G213" t="n">
+        <v>3</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>3</v>
+      </c>
+      <c r="M213" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DENMIN-MINDDIVINCENZO0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Donte Divincenzo</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>8</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>3</v>
+      </c>
+      <c r="G214" t="n">
+        <v>7</v>
+      </c>
+      <c r="H214" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>7</v>
+      </c>
+      <c r="M214" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DENMIN-MINDDIVINCENZO0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Donte Divincenzo</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>20</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G215" t="n">
+        <v>13</v>
+      </c>
+      <c r="H215" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>13</v>
+      </c>
+      <c r="M215" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-MINDDIVINCENZO0-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>20</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>3</v>
+      </c>
+      <c r="G216" t="n">
+        <v>9</v>
+      </c>
+      <c r="H216" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>9</v>
+      </c>
+      <c r="M216" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-DETDROBINSON55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Franz Wagner</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>25</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G217" t="n">
+        <v>16</v>
+      </c>
+      <c r="H217" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>16</v>
+      </c>
+      <c r="M217" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-ORLFWAGNER22-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Franz Wagner</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>8</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G218" t="n">
+        <v>14</v>
+      </c>
+      <c r="H218" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>14</v>
+      </c>
+      <c r="M218" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DETORL-ORLFWAGNER22-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>20</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>3</v>
+      </c>
+      <c r="G219" t="n">
+        <v>6</v>
+      </c>
+      <c r="H219" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>6</v>
+      </c>
+      <c r="M219" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25OKCPHX-OKCIHARTENSTEIN55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>9</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="G220" t="n">
+        <v>51</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>51</v>
+      </c>
+      <c r="M220" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25OKCPHX-OKCIHARTENSTEIN55-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>3</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G221" t="n">
+        <v>13</v>
+      </c>
+      <c r="H221" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" t="n">
+        <v>13</v>
+      </c>
+      <c r="M221" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25DENMIN-MINJMCDANIELS3-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>8</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G222" t="n">
+        <v>13</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>13</v>
+      </c>
+      <c r="M222" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DENMIN-MINJMCDANIELS3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>8</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>3</v>
+      </c>
+      <c r="G223" t="n">
+        <v>6</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>6</v>
+      </c>
+      <c r="M223" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DENMIN-MINJMCDANIELS3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>25</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G224" t="n">
+        <v>13</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>13</v>
+      </c>
+      <c r="M224" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-MINJMCDANIELS3-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>30</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G225" t="n">
+        <v>12</v>
+      </c>
+      <c r="H225" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>14</v>
+      </c>
+      <c r="K225" t="n">
+        <v>12</v>
+      </c>
+      <c r="M225" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25OKCPHX-PHXJGREEN4-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>3</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G226" t="n">
+        <v>12</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>12</v>
+      </c>
+      <c r="M226" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25OKCPHX-PHXJGREEN4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>8</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>3</v>
+      </c>
+      <c r="G227" t="n">
+        <v>7</v>
+      </c>
+      <c r="H227" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>7</v>
+      </c>
+      <c r="M227" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25OKCPHX-PHXJGREEN4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>8</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>3</v>
+      </c>
+      <c r="G228" t="n">
+        <v>15</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>15</v>
+      </c>
+      <c r="M228" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25OKCPHX-PHXJGREEN4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>3</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G229" t="n">
+        <v>29</v>
+      </c>
+      <c r="H229" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>2</v>
+      </c>
+      <c r="K229" t="n">
+        <v>29</v>
+      </c>
+      <c r="M229" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25DETORL-ORLJSUGGS4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>8</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>3</v>
+      </c>
+      <c r="G230" t="n">
+        <v>8</v>
+      </c>
+      <c r="H230" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>8</v>
+      </c>
+      <c r="M230" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DETORL-ORLJSUGGS4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>8</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G231" t="n">
+        <v>16</v>
+      </c>
+      <c r="H231" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>16</v>
+      </c>
+      <c r="M231" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DETORL-ORLJSUGGS4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>25</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>3</v>
+      </c>
+      <c r="G232" t="n">
+        <v>9</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>9</v>
+      </c>
+      <c r="M232" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-ORLJSUGGS4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Jamal Murray</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>35</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G233" t="n">
+        <v>17</v>
+      </c>
+      <c r="H233" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>17</v>
+      </c>
+      <c r="M233" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-DENJMURRAY27-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Jamal Murray</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>8</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G234" t="n">
+        <v>34</v>
+      </c>
+      <c r="H234" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>34</v>
+      </c>
+      <c r="M234" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DENMIN-DENJMURRAY27-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>30</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G235" t="n">
+        <v>12</v>
+      </c>
+      <c r="H235" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>12</v>
+      </c>
+      <c r="M235" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-MINJRANDLE30-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>8</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>3</v>
+      </c>
+      <c r="G236" t="n">
+        <v>12</v>
+      </c>
+      <c r="H236" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>12</v>
+      </c>
+      <c r="M236" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DENMIN-MINJRANDLE30-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>8</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G237" t="n">
+        <v>42</v>
+      </c>
+      <c r="H237" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>42</v>
+      </c>
+      <c r="M237" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DENMIN-MINJRANDLE30-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>3</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>7</v>
+      </c>
+      <c r="G238" t="n">
+        <v>23</v>
+      </c>
+      <c r="H238" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>23</v>
+      </c>
+      <c r="M238" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR25DENMIN-MINJRANDLE30-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>20</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>3</v>
+      </c>
+      <c r="G239" t="n">
+        <v>5</v>
+      </c>
+      <c r="H239" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>5</v>
+      </c>
+      <c r="M239" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25OKCPHX-OKCLDORT5-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Nikola Jokic</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>3</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G240" t="n">
+        <v>17</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>17</v>
+      </c>
+      <c r="M240" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25DENMIN-DENNJOKIC15-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Nikola Jokic</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>3</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G241" t="n">
+        <v>14</v>
+      </c>
+      <c r="H241" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>14</v>
+      </c>
+      <c r="M241" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR25DENMIN-DENNJOKIC15-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Nikola Jokic</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>8</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G242" t="n">
+        <v>74</v>
+      </c>
+      <c r="H242" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>74</v>
+      </c>
+      <c r="M242" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DENMIN-DENNJOKIC15-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Nikola Jokic</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>20</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G243" t="n">
+        <v>14</v>
+      </c>
+      <c r="H243" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>14</v>
+      </c>
+      <c r="M243" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DENMIN-DENNJOKIC15-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Nikola Jokic</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>40</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>3</v>
+      </c>
+      <c r="G244" t="n">
+        <v>17</v>
+      </c>
+      <c r="H244" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>17</v>
+      </c>
+      <c r="M244" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-DENNJOKIC15-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>9</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="G245" t="n">
+        <v>41</v>
+      </c>
+      <c r="H245" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>41</v>
+      </c>
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DETORL-ORLPBANCHERO5-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>35</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G246" t="n">
+        <v>6</v>
+      </c>
+      <c r="H246" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>6</v>
+      </c>
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-ORLPBANCHERO5-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>8</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G247" t="n">
+        <v>18</v>
+      </c>
+      <c r="H247" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>18</v>
+      </c>
+      <c r="M247" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DETORL-ORLPBANCHERO5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Rudy Gobert</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>3</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G248" t="n">
+        <v>22</v>
+      </c>
+      <c r="H248" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>22</v>
+      </c>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR25DENMIN-MINRGOBERT27-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Rudy Gobert</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>25</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>3</v>
+      </c>
+      <c r="G249" t="n">
+        <v>6</v>
+      </c>
+      <c r="H249" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>6</v>
+      </c>
+      <c r="M249" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DENMIN-MINRGOBERT27-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Rudy Gobert</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>8</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>75</v>
+      </c>
+      <c r="G250" t="n">
+        <v>85</v>
+      </c>
+      <c r="H250" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>85</v>
+      </c>
+      <c r="M250" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DENMIN-MINRGOBERT27-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>3</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G251" t="n">
+        <v>16</v>
+      </c>
+      <c r="H251" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>16</v>
+      </c>
+      <c r="M251" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>8</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>3</v>
+      </c>
+      <c r="G252" t="n">
+        <v>11</v>
+      </c>
+      <c r="H252" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>11</v>
+      </c>
+      <c r="M252" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>40</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>10</v>
+      </c>
+      <c r="G253" t="n">
+        <v>20</v>
+      </c>
+      <c r="H253" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>20</v>
+      </c>
+      <c r="M253" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>8</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>34</v>
+      </c>
+      <c r="G254" t="n">
+        <v>46</v>
+      </c>
+      <c r="H254" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>46</v>
+      </c>
+      <c r="M254" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>8</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>3</v>
+      </c>
+      <c r="G255" t="n">
+        <v>5</v>
+      </c>
+      <c r="H255" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>5</v>
+      </c>
+      <c r="M255" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR25DETORL-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>25</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>3</v>
+      </c>
+      <c r="G256" t="n">
+        <v>10</v>
+      </c>
+      <c r="H256" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>10</v>
+      </c>
+      <c r="M256" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-DETTHARRIS12-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>8</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G257" t="n">
+        <v>29</v>
+      </c>
+      <c r="H257" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>29</v>
+      </c>
+      <c r="M257" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DETORL-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>20</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>3</v>
+      </c>
+      <c r="G258" t="n">
+        <v>6</v>
+      </c>
+      <c r="H258" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>6</v>
+      </c>
+      <c r="M258" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR25DETORL-ORLWCARTER34-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>8</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G259" t="n">
+        <v>47</v>
+      </c>
+      <c r="H259" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>47</v>
+      </c>
+      <c r="M259" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR25DETORL-ORLWCARTER34-8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11460,7 +15666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11610,6 +15816,33 @@
         <v>-0.01</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>75</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11621,7 +15854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11667,20 +15900,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
       <c r="E2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -11689,42 +15922,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.571</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -11733,37 +15964,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.571</v>
+      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -11775,29 +16008,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>-2.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -11807,7 +16038,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11819,7 +16050,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -11829,11 +16060,9 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -11841,20 +16070,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -11863,20 +16092,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -11885,7 +16114,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -11901,48 +16130,48 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -11951,20 +16180,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -11973,33 +16202,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -12011,45 +16240,45 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12061,21 +16290,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>0</v>
       </c>
@@ -12083,7 +16310,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -12099,13 +16326,13 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -12121,26 +16348,26 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
       <c r="E23" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -12149,7 +16376,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -12159,9 +16386,11 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
@@ -12169,7 +16398,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -12179,9 +16408,11 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
@@ -12189,20 +16420,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -12215,7 +16446,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -12231,11 +16462,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -12251,11 +16482,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -12271,11 +16502,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -12291,11 +16522,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -12311,11 +16542,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Donte Divincenzo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -12331,11 +16562,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -12351,11 +16582,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -12371,11 +16602,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -12391,17 +16622,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
         <v>2</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -12413,11 +16644,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -12433,11 +16664,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -12453,11 +16684,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -12473,7 +16704,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -12493,7 +16724,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -12513,7 +16744,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -12523,11 +16754,9 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
         <v>0</v>
       </c>
@@ -12535,7 +16764,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -12545,11 +16774,9 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
         <v>0</v>
       </c>
@@ -12557,7 +16784,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -12577,7 +16804,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -12587,11 +16814,9 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -12599,7 +16824,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jake Laravia</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -12609,11 +16834,9 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
         <v>0</v>
       </c>
@@ -12621,7 +16844,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -12641,7 +16864,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -12651,9 +16874,11 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
@@ -12661,7 +16886,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -12681,7 +16906,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -12701,11 +16926,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -12721,11 +16946,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -12741,11 +16966,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -12761,19 +16986,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
@@ -12781,19 +17008,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
@@ -12801,11 +17030,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -12821,19 +17050,21 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
@@ -12841,20 +17072,422 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Jake Laravia</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jonathan Kuminga</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Anthony Black</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cameron Johnson</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Franz Wagner</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jamal Murray</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Shaedon Sharpe</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jerami Grant</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Toumani Camara</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Jaylon Tyson</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>Cj Mccollum</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B74" t="n">
         <v>1</v>
       </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ayo Dosunmu</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Desmond Bane</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Christian Braun</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12919,7 +17552,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -12941,7 +17574,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -12963,7 +17596,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -12985,7 +17618,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -13007,7 +17640,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +55,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,14 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11499,12 +11493,22 @@
       <c r="K185" t="n">
         <v>6</v>
       </c>
-      <c r="M185" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
+      <c r="L185" t="n">
+        <v>8</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-ORLABLACK0-20</t>
@@ -11555,12 +11559,20 @@
       <c r="K186" t="n">
         <v>6</v>
       </c>
-      <c r="M186" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DETORL-ORLABLACK0-8</t>
@@ -11611,12 +11623,20 @@
       <c r="K187" t="n">
         <v>19</v>
       </c>
-      <c r="M187" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L187" t="n">
+        <v>5</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-MINAEDWARDS5-35</t>
@@ -11667,12 +11687,20 @@
       <c r="K188" t="n">
         <v>14</v>
       </c>
-      <c r="M188" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25DENMIN-MINAEDWARDS5-3</t>
@@ -11723,12 +11751,20 @@
       <c r="K189" t="n">
         <v>25</v>
       </c>
-      <c r="M189" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L189" t="n">
+        <v>3</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DENMIN-MINAEDWARDS5-8</t>
@@ -11779,12 +11815,20 @@
       <c r="K190" t="n">
         <v>9</v>
       </c>
-      <c r="M190" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DENMIN-MINAEDWARDS5-8</t>
@@ -11835,12 +11879,22 @@
       <c r="K191" t="n">
         <v>34</v>
       </c>
-      <c r="M191" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>2</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25DETORL-DETATHOMPSON9-3</t>
@@ -11891,12 +11945,20 @@
       <c r="K192" t="n">
         <v>5</v>
       </c>
-      <c r="M192" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L192" t="n">
+        <v>17</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-DETATHOMPSON9-25</t>
@@ -11947,12 +12009,20 @@
       <c r="K193" t="n">
         <v>6</v>
       </c>
-      <c r="M193" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L193" t="n">
+        <v>3</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DETORL-DETATHOMPSON9-8</t>
@@ -12003,12 +12073,20 @@
       <c r="K194" t="n">
         <v>30</v>
       </c>
-      <c r="M194" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L194" t="n">
+        <v>8</v>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DETORL-DETATHOMPSON9-8</t>
@@ -12059,12 +12137,20 @@
       <c r="K195" t="n">
         <v>16</v>
       </c>
-      <c r="M195" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L195" t="n">
+        <v>43</v>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-MINADOSUNMU13-20</t>
@@ -12115,12 +12201,20 @@
       <c r="K196" t="n">
         <v>21</v>
       </c>
-      <c r="M196" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25DETORL-DETCCUNNINGHAM2-3</t>
@@ -12171,12 +12265,20 @@
       <c r="K197" t="n">
         <v>24</v>
       </c>
-      <c r="M197" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L197" t="n">
+        <v>5</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DETORL-DETCCUNNINGHAM2-8</t>
@@ -12227,12 +12329,20 @@
       <c r="K198" t="n">
         <v>75</v>
       </c>
-      <c r="M198" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L198" t="n">
+        <v>9</v>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DETORL-DETCCUNNINGHAM2-8</t>
@@ -12283,12 +12393,20 @@
       <c r="K199" t="n">
         <v>11</v>
       </c>
-      <c r="M199" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L199" t="n">
+        <v>27</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-DETCCUNNINGHAM2-40</t>
@@ -12339,12 +12457,20 @@
       <c r="K200" t="n">
         <v>5</v>
       </c>
-      <c r="M200" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L200" t="n">
+        <v>2</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DENMIN-DENCJOHNSON23-8</t>
@@ -12395,12 +12521,20 @@
       <c r="K201" t="n">
         <v>10</v>
       </c>
-      <c r="M201" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L201" t="n">
+        <v>9</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-DENCJOHNSON23-20</t>
@@ -12451,12 +12585,20 @@
       <c r="K202" t="n">
         <v>36</v>
       </c>
-      <c r="M202" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L202" t="n">
+        <v>2</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>KXNBABLK-26APR25OKCPHX-OKCCHOLMGREN7-3</t>
@@ -12507,12 +12649,20 @@
       <c r="K203" t="n">
         <v>15</v>
       </c>
-      <c r="M203" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L203" t="n">
+        <v>10</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25OKCPHX-OKCCHOLMGREN7-25</t>
@@ -12563,12 +12713,20 @@
       <c r="K204" t="n">
         <v>57</v>
       </c>
-      <c r="M204" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L204" t="n">
+        <v>7</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25OKCPHX-OKCCHOLMGREN7-9</t>
@@ -12619,12 +12777,20 @@
       <c r="K205" t="n">
         <v>10</v>
       </c>
-      <c r="M205" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L205" t="n">
+        <v>8</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-DENCBRAUN0-20</t>
@@ -12675,12 +12841,20 @@
       <c r="K206" t="n">
         <v>9</v>
       </c>
-      <c r="M206" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L206" t="n">
+        <v>25</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-ORLDBANE3-30</t>
@@ -12731,12 +12905,20 @@
       <c r="K207" t="n">
         <v>11</v>
       </c>
-      <c r="M207" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L207" t="n">
+        <v>16</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25OKCPHX-PHXDBOOKER1-35</t>
@@ -12787,12 +12969,20 @@
       <c r="K208" t="n">
         <v>22</v>
       </c>
-      <c r="M208" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L208" t="n">
+        <v>7</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25OKCPHX-PHXDBOOKER1-8</t>
@@ -12843,12 +13033,20 @@
       <c r="K209" t="n">
         <v>20</v>
       </c>
-      <c r="M209" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L209" t="n">
+        <v>33</v>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25OKCPHX-PHXDBROOKS3-25</t>
@@ -12899,12 +13097,20 @@
       <c r="K210" t="n">
         <v>8</v>
       </c>
-      <c r="M210" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25OKCPHX-PHXDBROOKS3-10</t>
@@ -12955,12 +13161,20 @@
       <c r="K211" t="n">
         <v>9</v>
       </c>
-      <c r="M211" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L211" t="n">
+        <v>7</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25OKCPHX-PHXDBROOKS3-8</t>
@@ -13011,9 +13225,9 @@
       <c r="K212" t="n">
         <v>14</v>
       </c>
-      <c r="M212" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -13067,9 +13281,9 @@
       <c r="K213" t="n">
         <v>3</v>
       </c>
-      <c r="M213" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N213" t="inlineStr"/>
@@ -13123,9 +13337,9 @@
       <c r="K214" t="n">
         <v>7</v>
       </c>
-      <c r="M214" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
@@ -13179,9 +13393,9 @@
       <c r="K215" t="n">
         <v>13</v>
       </c>
-      <c r="M215" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
@@ -13235,12 +13449,20 @@
       <c r="K216" t="n">
         <v>9</v>
       </c>
-      <c r="M216" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L216" t="n">
+        <v>10</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-DETDROBINSON55-20</t>
@@ -13291,12 +13513,20 @@
       <c r="K217" t="n">
         <v>16</v>
       </c>
-      <c r="M217" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L217" t="n">
+        <v>17</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-ORLFWAGNER22-25</t>
@@ -13347,12 +13577,20 @@
       <c r="K218" t="n">
         <v>14</v>
       </c>
-      <c r="M218" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L218" t="n">
+        <v>5</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DETORL-ORLFWAGNER22-8</t>
@@ -13403,12 +13641,20 @@
       <c r="K219" t="n">
         <v>6</v>
       </c>
-      <c r="M219" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L219" t="n">
+        <v>9</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25OKCPHX-OKCIHARTENSTEIN55-20</t>
@@ -13459,12 +13705,20 @@
       <c r="K220" t="n">
         <v>51</v>
       </c>
-      <c r="M220" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L220" t="n">
+        <v>3</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25OKCPHX-OKCIHARTENSTEIN55-9</t>
@@ -13515,12 +13769,22 @@
       <c r="K221" t="n">
         <v>13</v>
       </c>
-      <c r="M221" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25DENMIN-MINJMCDANIELS3-3</t>
@@ -13571,12 +13835,20 @@
       <c r="K222" t="n">
         <v>13</v>
       </c>
-      <c r="M222" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L222" t="n">
+        <v>8</v>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DENMIN-MINJMCDANIELS3-8</t>
@@ -13627,12 +13899,20 @@
       <c r="K223" t="n">
         <v>6</v>
       </c>
-      <c r="M223" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L223" t="n">
+        <v>3</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DENMIN-MINJMCDANIELS3-8</t>
@@ -13683,12 +13963,20 @@
       <c r="K224" t="n">
         <v>13</v>
       </c>
-      <c r="M224" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L224" t="n">
+        <v>12</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-MINJMCDANIELS3-25</t>
@@ -13739,12 +14027,22 @@
       <c r="K225" t="n">
         <v>12</v>
       </c>
-      <c r="M225" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr"/>
+      <c r="L225" t="n">
+        <v>26</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25OKCPHX-PHXJGREEN4-30</t>
@@ -13795,12 +14093,20 @@
       <c r="K226" t="n">
         <v>12</v>
       </c>
-      <c r="M226" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25OKCPHX-PHXJGREEN4-3</t>
@@ -13851,12 +14157,20 @@
       <c r="K227" t="n">
         <v>7</v>
       </c>
-      <c r="M227" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L227" t="n">
+        <v>6</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25OKCPHX-PHXJGREEN4-8</t>
@@ -13907,12 +14221,20 @@
       <c r="K228" t="n">
         <v>15</v>
       </c>
-      <c r="M228" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L228" t="n">
+        <v>5</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25OKCPHX-PHXJGREEN4-8</t>
@@ -13963,12 +14285,22 @@
       <c r="K229" t="n">
         <v>29</v>
       </c>
-      <c r="M229" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr"/>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25DETORL-ORLJSUGGS4-3</t>
@@ -14019,12 +14351,20 @@
       <c r="K230" t="n">
         <v>8</v>
       </c>
-      <c r="M230" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L230" t="n">
+        <v>3</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DETORL-ORLJSUGGS4-8</t>
@@ -14075,12 +14415,20 @@
       <c r="K231" t="n">
         <v>16</v>
       </c>
-      <c r="M231" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L231" t="n">
+        <v>3</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DETORL-ORLJSUGGS4-8</t>
@@ -14131,12 +14479,20 @@
       <c r="K232" t="n">
         <v>9</v>
       </c>
-      <c r="M232" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L232" t="n">
+        <v>15</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-ORLJSUGGS4-25</t>
@@ -14187,12 +14543,20 @@
       <c r="K233" t="n">
         <v>17</v>
       </c>
-      <c r="M233" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L233" t="n">
+        <v>30</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-DENJMURRAY27-35</t>
@@ -14243,12 +14607,20 @@
       <c r="K234" t="n">
         <v>34</v>
       </c>
-      <c r="M234" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L234" t="n">
+        <v>5</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DENMIN-DENJMURRAY27-8</t>
@@ -14299,12 +14671,20 @@
       <c r="K235" t="n">
         <v>12</v>
       </c>
-      <c r="M235" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L235" t="n">
+        <v>15</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-MINJRANDLE30-30</t>
@@ -14355,12 +14735,20 @@
       <c r="K236" t="n">
         <v>12</v>
       </c>
-      <c r="M236" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L236" t="n">
+        <v>2</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DENMIN-MINJRANDLE30-8</t>
@@ -14411,12 +14799,20 @@
       <c r="K237" t="n">
         <v>42</v>
       </c>
-      <c r="M237" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L237" t="n">
+        <v>9</v>
+      </c>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DENMIN-MINJRANDLE30-8</t>
@@ -14467,12 +14863,20 @@
       <c r="K238" t="n">
         <v>23</v>
       </c>
-      <c r="M238" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>KXNBABLK-26APR25DENMIN-MINJRANDLE30-3</t>
@@ -14523,12 +14927,20 @@
       <c r="K239" t="n">
         <v>5</v>
       </c>
-      <c r="M239" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L239" t="n">
+        <v>9</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25OKCPHX-OKCLDORT5-20</t>
@@ -14579,12 +14991,20 @@
       <c r="K240" t="n">
         <v>17</v>
       </c>
-      <c r="M240" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L240" t="n">
+        <v>3</v>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25DENMIN-DENNJOKIC15-3</t>
@@ -14635,12 +15055,20 @@
       <c r="K241" t="n">
         <v>14</v>
       </c>
-      <c r="M241" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>KXNBABLK-26APR25DENMIN-DENNJOKIC15-3</t>
@@ -14691,12 +15119,20 @@
       <c r="K242" t="n">
         <v>74</v>
       </c>
-      <c r="M242" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L242" t="n">
+        <v>9</v>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DENMIN-DENNJOKIC15-8</t>
@@ -14747,12 +15183,20 @@
       <c r="K243" t="n">
         <v>14</v>
       </c>
-      <c r="M243" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L243" t="n">
+        <v>15</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DENMIN-DENNJOKIC15-20</t>
@@ -14803,12 +15247,20 @@
       <c r="K244" t="n">
         <v>17</v>
       </c>
-      <c r="M244" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L244" t="n">
+        <v>24</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-DENNJOKIC15-40</t>
@@ -14859,12 +15311,20 @@
       <c r="K245" t="n">
         <v>41</v>
       </c>
-      <c r="M245" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L245" t="n">
+        <v>12</v>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DETORL-ORLPBANCHERO5-9</t>
@@ -14915,12 +15375,20 @@
       <c r="K246" t="n">
         <v>6</v>
       </c>
-      <c r="M246" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L246" t="n">
+        <v>25</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-ORLPBANCHERO5-35</t>
@@ -14971,12 +15439,20 @@
       <c r="K247" t="n">
         <v>18</v>
       </c>
-      <c r="M247" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L247" t="n">
+        <v>9</v>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DETORL-ORLPBANCHERO5-8</t>
@@ -15027,12 +15503,20 @@
       <c r="K248" t="n">
         <v>22</v>
       </c>
-      <c r="M248" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L248" t="n">
+        <v>2</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>KXNBABLK-26APR25DENMIN-MINRGOBERT27-3</t>
@@ -15083,12 +15567,20 @@
       <c r="K249" t="n">
         <v>6</v>
       </c>
-      <c r="M249" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L249" t="n">
+        <v>4</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DENMIN-MINRGOBERT27-25</t>
@@ -15139,12 +15631,20 @@
       <c r="K250" t="n">
         <v>85</v>
       </c>
-      <c r="M250" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L250" t="n">
+        <v>15</v>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DENMIN-MINRGOBERT27-8</t>
@@ -15195,12 +15695,20 @@
       <c r="K251" t="n">
         <v>16</v>
       </c>
-      <c r="M251" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P251" t="inlineStr">
         <is>
           <t>KXNBASTL-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-3</t>
@@ -15251,12 +15759,20 @@
       <c r="K252" t="n">
         <v>11</v>
       </c>
-      <c r="M252" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L252" t="n">
+        <v>4</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-8</t>
@@ -15307,12 +15823,20 @@
       <c r="K253" t="n">
         <v>20</v>
       </c>
-      <c r="M253" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L253" t="n">
+        <v>42</v>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-40</t>
@@ -15363,12 +15887,20 @@
       <c r="K254" t="n">
         <v>46</v>
       </c>
-      <c r="M254" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L254" t="n">
+        <v>8</v>
+      </c>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25OKCPHX-OKCSGILGEOUSALEXANDER2-8</t>
@@ -15419,12 +15951,20 @@
       <c r="K255" t="n">
         <v>5</v>
       </c>
-      <c r="M255" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L255" t="n">
+        <v>2</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
           <t>KXNBAAST-26APR25DETORL-DETTHARRIS12-8</t>
@@ -15475,12 +16015,20 @@
       <c r="K256" t="n">
         <v>10</v>
       </c>
-      <c r="M256" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L256" t="n">
+        <v>23</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P256" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-DETTHARRIS12-25</t>
@@ -15531,12 +16079,20 @@
       <c r="K257" t="n">
         <v>29</v>
       </c>
-      <c r="M257" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L257" t="n">
+        <v>7</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DETORL-DETTHARRIS12-8</t>
@@ -15587,12 +16143,20 @@
       <c r="K258" t="n">
         <v>6</v>
       </c>
-      <c r="M258" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L258" t="n">
+        <v>14</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>KXNBAPTS-26APR25DETORL-ORLWCARTER34-20</t>
@@ -15643,12 +16207,20 @@
       <c r="K259" t="n">
         <v>47</v>
       </c>
-      <c r="M259" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L259" t="n">
+        <v>17</v>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="P259" t="inlineStr">
         <is>
           <t>KXNBAREB-26APR25DETORL-ORLWCARTER34-8</t>
@@ -15826,22 +16398,26 @@
         <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-5.87</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.08</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15907,13 +16483,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -15932,11 +16508,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="4">
@@ -15996,7 +16574,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16015,12 +16593,14 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.333</v>
+      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -16080,7 +16660,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16297,12 +16877,14 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4</v>
+      </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
@@ -16452,9 +17034,11 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
@@ -16472,9 +17056,11 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
@@ -16489,14 +17075,16 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="30">
@@ -16512,11 +17100,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="31">
@@ -16529,14 +17119,16 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="32">
@@ -16572,9 +17164,11 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
@@ -16589,12 +17183,14 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
@@ -16609,12 +17205,14 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
@@ -16651,12 +17249,14 @@
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.333</v>
+      </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
@@ -16674,9 +17274,11 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
@@ -16691,12 +17293,14 @@
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.667</v>
+      </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
@@ -17164,11 +17768,13 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="63">
@@ -17184,9 +17790,11 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
@@ -17204,9 +17812,11 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
@@ -17221,12 +17831,14 @@
         <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
@@ -17244,9 +17856,11 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
@@ -17421,12 +18035,14 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
@@ -17444,9 +18060,11 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
@@ -17464,9 +18082,11 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
@@ -17484,9 +18104,11 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
@@ -17555,13 +18177,13 @@
         <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>0.077</v>
+        <v>0.179</v>
       </c>
       <c r="F2" t="n">
         <v>-3.74</v>
@@ -17580,10 +18202,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.111</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -17599,16 +18221,16 @@
         <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>0.033</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.24</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="5">
@@ -17621,13 +18243,13 @@
         <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>0.227</v>
+        <v>0.275</v>
       </c>
       <c r="F5" t="n">
         <v>-3.36</v>
@@ -17643,16 +18265,16 @@
         <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.273</v>
+        <v>0.211</v>
       </c>
       <c r="F6" t="n">
-        <v>8.199999999999999</v>
+        <v>4.85</v>
       </c>
     </row>
   </sheetData>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P259"/>
+  <dimension ref="A1:P326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16227,6 +16233,3758 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>30</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G260" t="n">
+        <v>13</v>
+      </c>
+      <c r="H260" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>13</v>
+      </c>
+      <c r="M260" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-HOUASENGUN28-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>9</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="G261" t="n">
+        <v>55</v>
+      </c>
+      <c r="H261" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>55</v>
+      </c>
+      <c r="M261" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26LALHOU-HOUASENGUN28-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>8</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="G262" t="n">
+        <v>49</v>
+      </c>
+      <c r="H262" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>49</v>
+      </c>
+      <c r="M262" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26LALHOU-HOUATHOMPSON1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>30</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>6</v>
+      </c>
+      <c r="G263" t="n">
+        <v>7</v>
+      </c>
+      <c r="H263" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>7</v>
+      </c>
+      <c r="M263" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-HOUATHOMPSON1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>30</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G264" t="n">
+        <v>11</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>11</v>
+      </c>
+      <c r="M264" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-TORBINGRAM3-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>8</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G265" t="n">
+        <v>6</v>
+      </c>
+      <c r="H265" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>6</v>
+      </c>
+      <c r="M265" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR26CLETOR-TORBINGRAM3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Brandon Ingram</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>8</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G266" t="n">
+        <v>18</v>
+      </c>
+      <c r="H266" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>18</v>
+      </c>
+      <c r="M266" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-TORBINGRAM3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>20</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G267" t="n">
+        <v>9</v>
+      </c>
+      <c r="H267" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>9</v>
+      </c>
+      <c r="M267" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-LALDAYTON5-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>9</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="G268" t="n">
+        <v>42</v>
+      </c>
+      <c r="H268" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>42</v>
+      </c>
+      <c r="M268" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26LALHOU-LALDAYTON5-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>20</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G269" t="n">
+        <v>15</v>
+      </c>
+      <c r="H269" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>15</v>
+      </c>
+      <c r="M269" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr"/>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-CLEDSCHRODER8-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>25</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G270" t="n">
+        <v>9</v>
+      </c>
+      <c r="H270" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>9</v>
+      </c>
+      <c r="M270" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr"/>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-BOSDWHITE9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>8</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G271" t="n">
+        <v>11</v>
+      </c>
+      <c r="H271" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>11</v>
+      </c>
+      <c r="M271" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR26CLETOR-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>8</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G272" t="n">
+        <v>9</v>
+      </c>
+      <c r="H272" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>9</v>
+      </c>
+      <c r="M272" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>35</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>12</v>
+      </c>
+      <c r="G273" t="n">
+        <v>18</v>
+      </c>
+      <c r="H273" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>18</v>
+      </c>
+      <c r="M273" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-CLEDMITCHELL45-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>3</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G274" t="n">
+        <v>18</v>
+      </c>
+      <c r="H274" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>18</v>
+      </c>
+      <c r="M274" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR26CLETOR-CLEDMITCHELL45-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>25</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G275" t="n">
+        <v>14</v>
+      </c>
+      <c r="H275" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>14</v>
+      </c>
+      <c r="M275" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-CLEEMOBLEY4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>9</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G276" t="n">
+        <v>48</v>
+      </c>
+      <c r="H276" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>48</v>
+      </c>
+      <c r="M276" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr"/>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-CLEEMOBLEY4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>3</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G277" t="n">
+        <v>11</v>
+      </c>
+      <c r="H277" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>11</v>
+      </c>
+      <c r="M277" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr"/>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR26CLETOR-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>3</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G278" t="n">
+        <v>28</v>
+      </c>
+      <c r="H278" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>28</v>
+      </c>
+      <c r="M278" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR26CLETOR-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>8</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G279" t="n">
+        <v>38</v>
+      </c>
+      <c r="H279" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>38</v>
+      </c>
+      <c r="M279" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr"/>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26LALHOU-HOUJSMITH10-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>25</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G280" t="n">
+        <v>12</v>
+      </c>
+      <c r="H280" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>12</v>
+      </c>
+      <c r="M280" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-HOUJSMITH10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>20</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G281" t="n">
+        <v>3</v>
+      </c>
+      <c r="H281" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="n">
+        <v>3</v>
+      </c>
+      <c r="M281" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr"/>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-TORJPOELTL19-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>8</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G282" t="n">
+        <v>21</v>
+      </c>
+      <c r="H282" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>21</v>
+      </c>
+      <c r="M282" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-TORJPOELTL19-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>10</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G283" t="n">
+        <v>38</v>
+      </c>
+      <c r="H283" t="n">
+        <v>-34.7</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>38</v>
+      </c>
+      <c r="M283" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR26CLETOR-TORJPOELTL19-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>8</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G284" t="n">
+        <v>7</v>
+      </c>
+      <c r="H284" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>7</v>
+      </c>
+      <c r="M284" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>3</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G285" t="n">
+        <v>13</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>13</v>
+      </c>
+      <c r="M285" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR26CLETOR-CLEJHARDEN1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>8</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="G286" t="n">
+        <v>38</v>
+      </c>
+      <c r="H286" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>38</v>
+      </c>
+      <c r="M286" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR26CLETOR-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>30</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G287" t="n">
+        <v>12</v>
+      </c>
+      <c r="H287" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>12</v>
+      </c>
+      <c r="M287" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-CLEJHARDEN1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>25</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G288" t="n">
+        <v>4</v>
+      </c>
+      <c r="H288" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>65</v>
+      </c>
+      <c r="K288" t="n">
+        <v>4</v>
+      </c>
+      <c r="M288" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr"/>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-CLEJALLEN31-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>8</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G289" t="n">
+        <v>52</v>
+      </c>
+      <c r="H289" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>52</v>
+      </c>
+      <c r="M289" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-CLEJALLEN31-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>3</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G290" t="n">
+        <v>13</v>
+      </c>
+      <c r="H290" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>13</v>
+      </c>
+      <c r="M290" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR26CLETOR-CLEJALLEN31-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>35</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G291" t="n">
+        <v>18</v>
+      </c>
+      <c r="H291" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>18</v>
+      </c>
+      <c r="M291" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr"/>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-BOSJBROWN7-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>8</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="G292" t="n">
+        <v>30</v>
+      </c>
+      <c r="H292" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>30</v>
+      </c>
+      <c r="M292" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr"/>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-BOSJBROWN7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Jaylon Tyson</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>20</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G293" t="n">
+        <v>3</v>
+      </c>
+      <c r="H293" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>3</v>
+      </c>
+      <c r="M293" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr"/>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-CLEJTYSON20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>35</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G294" t="n">
+        <v>11</v>
+      </c>
+      <c r="H294" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>11</v>
+      </c>
+      <c r="M294" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr"/>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-BOSJTATUM0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>8</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G295" t="n">
+        <v>78</v>
+      </c>
+      <c r="H295" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>78</v>
+      </c>
+      <c r="M295" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr"/>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-BOSJTATUM0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>25</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G296" t="n">
+        <v>7</v>
+      </c>
+      <c r="H296" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>7</v>
+      </c>
+      <c r="M296" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr"/>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-PHIKOUBRE9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>8</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G297" t="n">
+        <v>20</v>
+      </c>
+      <c r="H297" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>20</v>
+      </c>
+      <c r="M297" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-PHIKOUBRE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>35</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G298" t="n">
+        <v>10</v>
+      </c>
+      <c r="H298" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>10</v>
+      </c>
+      <c r="M298" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr"/>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-LALLJAMES23-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>8</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G299" t="n">
+        <v>45</v>
+      </c>
+      <c r="H299" t="n">
+        <v>-39.4</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>45</v>
+      </c>
+      <c r="M299" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26LALHOU-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>20</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G300" t="n">
+        <v>13</v>
+      </c>
+      <c r="H300" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>13</v>
+      </c>
+      <c r="M300" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr"/>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-LALMSMART36-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>8</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G301" t="n">
+        <v>47</v>
+      </c>
+      <c r="H301" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>47</v>
+      </c>
+      <c r="M301" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr"/>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-BOSNQUETA88-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>3</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G302" t="n">
+        <v>17</v>
+      </c>
+      <c r="H302" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>17</v>
+      </c>
+      <c r="M302" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr"/>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR26BOSPHI-BOSNQUETA88-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>20</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G303" t="n">
+        <v>5</v>
+      </c>
+      <c r="H303" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>5</v>
+      </c>
+      <c r="M303" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr"/>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-BOSNQUETA88-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>10</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G304" t="n">
+        <v>10</v>
+      </c>
+      <c r="H304" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J304" t="n">
+        <v>22</v>
+      </c>
+      <c r="K304" t="n">
+        <v>10</v>
+      </c>
+      <c r="M304" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr"/>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-BOSNVUCEVIC4-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>20</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G305" t="n">
+        <v>5</v>
+      </c>
+      <c r="H305" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>5</v>
+      </c>
+      <c r="M305" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr"/>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-BOSNVUCEVIC4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>30</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G306" t="n">
+        <v>10</v>
+      </c>
+      <c r="H306" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>10</v>
+      </c>
+      <c r="M306" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr"/>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-PHIPGEORGE8-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>8</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G307" t="n">
+        <v>19</v>
+      </c>
+      <c r="H307" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>19</v>
+      </c>
+      <c r="M307" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr"/>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>25</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G308" t="n">
+        <v>7</v>
+      </c>
+      <c r="H308" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J308" t="n">
+        <v>28</v>
+      </c>
+      <c r="K308" t="n">
+        <v>7</v>
+      </c>
+      <c r="M308" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr"/>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-BOSPPRITCHARD11-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>8</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G309" t="n">
+        <v>3</v>
+      </c>
+      <c r="H309" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>3</v>
+      </c>
+      <c r="M309" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr"/>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-BOSPPRITCHARD11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Reed Sheppard</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>25</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G310" t="n">
+        <v>7</v>
+      </c>
+      <c r="H310" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>7</v>
+      </c>
+      <c r="M310" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr"/>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-HOURSHEPPARD15-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>8</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G311" t="n">
+        <v>5</v>
+      </c>
+      <c r="H311" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>5</v>
+      </c>
+      <c r="M311" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr"/>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR26CLETOR-TORRBARRETT9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>30</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G312" t="n">
+        <v>12</v>
+      </c>
+      <c r="H312" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>12</v>
+      </c>
+      <c r="M312" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr"/>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-TORRBARRETT9-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>8</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G313" t="n">
+        <v>21</v>
+      </c>
+      <c r="H313" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>21</v>
+      </c>
+      <c r="M313" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr"/>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-TORRBARRETT9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>3</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G314" t="n">
+        <v>11</v>
+      </c>
+      <c r="H314" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="n">
+        <v>11</v>
+      </c>
+      <c r="M314" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr"/>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR26CLETOR-TORRBARRETT9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>25</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G315" t="n">
+        <v>9</v>
+      </c>
+      <c r="H315" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" t="n">
+        <v>9</v>
+      </c>
+      <c r="M315" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr"/>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-LALRHACHIMURA28-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Sam Hauser</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>20</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G316" t="n">
+        <v>5</v>
+      </c>
+      <c r="H316" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="n">
+        <v>5</v>
+      </c>
+      <c r="M316" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr"/>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-BOSSHAUSER30-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>3</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G317" t="n">
+        <v>20</v>
+      </c>
+      <c r="H317" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>20</v>
+      </c>
+      <c r="M317" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr"/>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26APR26CLETOR-TORSBARNES4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>3</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G318" t="n">
+        <v>13</v>
+      </c>
+      <c r="H318" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="n">
+        <v>13</v>
+      </c>
+      <c r="M318" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr"/>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26APR26CLETOR-TORSBARNES4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>30</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>8</v>
+      </c>
+      <c r="G319" t="n">
+        <v>12</v>
+      </c>
+      <c r="H319" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="n">
+        <v>12</v>
+      </c>
+      <c r="M319" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr"/>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26CLETOR-TORSBARNES4-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>8</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>42</v>
+      </c>
+      <c r="G320" t="n">
+        <v>46</v>
+      </c>
+      <c r="H320" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="n">
+        <v>46</v>
+      </c>
+      <c r="M320" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr"/>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26APR26CLETOR-TORSBARNES4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>8</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G321" t="n">
+        <v>45</v>
+      </c>
+      <c r="H321" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="n">
+        <v>45</v>
+      </c>
+      <c r="M321" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr"/>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26CLETOR-TORSBARNES4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>8</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G322" t="n">
+        <v>25</v>
+      </c>
+      <c r="H322" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>28</v>
+      </c>
+      <c r="K322" t="n">
+        <v>25</v>
+      </c>
+      <c r="M322" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr"/>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26LALHOU-HOUTEASON17-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>20</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G323" t="n">
+        <v>9</v>
+      </c>
+      <c r="H323" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="n">
+        <v>9</v>
+      </c>
+      <c r="M323" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr"/>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26LALHOU-HOUTEASON17-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>35</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G324" t="n">
+        <v>23</v>
+      </c>
+      <c r="H324" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="n">
+        <v>23</v>
+      </c>
+      <c r="M324" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr"/>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-PHITMAXEY0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>8</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>41</v>
+      </c>
+      <c r="G325" t="n">
+        <v>30</v>
+      </c>
+      <c r="H325" t="n">
+        <v>11</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>9</v>
+      </c>
+      <c r="K325" t="n">
+        <v>30</v>
+      </c>
+      <c r="M325" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr"/>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26APR26BOSPHI-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>25</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G326" t="n">
+        <v>13</v>
+      </c>
+      <c r="H326" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="n">
+        <v>13</v>
+      </c>
+      <c r="M326" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr"/>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26APR26BOSPHI-PHIVEDGECOMBE77-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16238,7 +19996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16419,6 +20177,33 @@
         <v>-0.08</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>67</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16430,7 +20215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16498,83 +20283,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>0.571</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16586,39 +20371,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16630,19 +20415,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -16650,17 +20437,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16672,20 +20459,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -16694,11 +20481,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -16710,48 +20497,48 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -16760,20 +20547,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -16782,20 +20569,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -16804,39 +20591,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16848,42 +20633,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
         <v>2</v>
       </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
       <c r="E20" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -16892,33 +20677,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -16930,49 +20715,47 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.56</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
         <v>0</v>
       </c>
@@ -16984,7 +20767,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -17006,7 +20789,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
         <v>2</v>
@@ -17024,20 +20807,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -17046,21 +20829,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
         <v>0</v>
       </c>
@@ -17068,29 +20849,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -17100,61 +20881,63 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jaden Mcdaniels</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Donte Divincenzo</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -17170,13 +20953,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -17192,27 +20975,25 @@
         <v>0.25</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Donte Divincenzo</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
         <v>0</v>
       </c>
@@ -17220,17 +21001,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -17242,20 +21023,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -17264,20 +21045,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -17286,21 +21067,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
         <v>0</v>
       </c>
@@ -17308,11 +21087,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -17328,11 +21107,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -17348,11 +21127,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -17368,19 +21147,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
@@ -17388,19 +21169,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
@@ -17408,19 +21191,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
         <v>2</v>
       </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>0.333</v>
+      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -17428,19 +21213,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
@@ -17448,19 +21235,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
         <v>2</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
       <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.667</v>
+      </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
@@ -17468,21 +21257,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
         <v>0</v>
       </c>
@@ -17490,11 +21277,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -17510,7 +21297,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -17530,7 +21317,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -17550,7 +21337,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -17570,7 +21357,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -17590,7 +21377,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -17600,11 +21387,9 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
         <v>0</v>
       </c>
@@ -17612,7 +21397,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -17622,11 +21407,9 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
         <v>0</v>
       </c>
@@ -17634,7 +21417,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -17654,7 +21437,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -17664,11 +21447,9 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
         <v>0</v>
       </c>
@@ -17676,7 +21457,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jake Laravia</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -17686,11 +21467,9 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>0</v>
       </c>
@@ -17698,7 +21477,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -17718,7 +21497,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -17738,7 +21517,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -17758,7 +21537,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -17768,19 +21547,17 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -17790,7 +21567,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -17802,7 +21579,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -17812,11 +21589,9 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
         <v>0</v>
       </c>
@@ -17824,20 +21599,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -17846,7 +21621,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -17856,11 +21631,9 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
         <v>0</v>
       </c>
@@ -17868,19 +21641,21 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Jake Laravia</t>
         </is>
       </c>
       <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
@@ -17888,11 +21663,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -17908,11 +21683,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -17928,11 +21703,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -17948,39 +21723,43 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
@@ -17988,19 +21767,21 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
@@ -18008,19 +21789,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cj Mccollum</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="n">
         <v>1</v>
       </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
       <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
@@ -18028,20 +21811,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -18050,7 +21833,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -18060,11 +21843,9 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
         <v>0</v>
       </c>
@@ -18072,7 +21853,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -18082,11 +21863,9 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>0</v>
       </c>
@@ -18094,7 +21873,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -18104,12 +21883,158 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cj Mccollum</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ayo Dosunmu</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Desmond Bane</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Christian Braun</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18174,7 +22099,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -18196,7 +22121,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -18218,7 +22143,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -18240,7 +22165,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
@@ -18262,7 +22187,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P587"/>
+  <dimension ref="A1:P674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37233,6 +37239,4878 @@
         </is>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>30</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F588" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G588" t="n">
+        <v>12</v>
+      </c>
+      <c r="H588" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J588" t="n">
+        <v>0</v>
+      </c>
+      <c r="K588" t="n">
+        <v>12</v>
+      </c>
+      <c r="M588" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr"/>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-HOUASENGUN28-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>3</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F589" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G589" t="n">
+        <v>14</v>
+      </c>
+      <c r="H589" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J589" t="n">
+        <v>0</v>
+      </c>
+      <c r="K589" t="n">
+        <v>14</v>
+      </c>
+      <c r="M589" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr"/>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY01LALHOU-HOUASENGUN28-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>8</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F590" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G590" t="n">
+        <v>28</v>
+      </c>
+      <c r="H590" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J590" t="n">
+        <v>0</v>
+      </c>
+      <c r="K590" t="n">
+        <v>28</v>
+      </c>
+      <c r="M590" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr"/>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01LALHOU-HOUASENGUN28-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>8</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F591" t="n">
+        <v>64</v>
+      </c>
+      <c r="G591" t="n">
+        <v>73</v>
+      </c>
+      <c r="H591" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J591" t="n">
+        <v>0</v>
+      </c>
+      <c r="K591" t="n">
+        <v>73</v>
+      </c>
+      <c r="M591" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr"/>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01LALHOU-HOUASENGUN28-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>3</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F592" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G592" t="n">
+        <v>28</v>
+      </c>
+      <c r="H592" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J592" t="n">
+        <v>6</v>
+      </c>
+      <c r="K592" t="n">
+        <v>28</v>
+      </c>
+      <c r="M592" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr"/>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01LALHOU-HOUATHOMPSON1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>8</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F593" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="G593" t="n">
+        <v>49</v>
+      </c>
+      <c r="H593" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J593" t="n">
+        <v>0</v>
+      </c>
+      <c r="K593" t="n">
+        <v>49</v>
+      </c>
+      <c r="M593" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr"/>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01LALHOU-HOUATHOMPSON1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>30</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F594" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G594" t="n">
+        <v>8</v>
+      </c>
+      <c r="H594" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J594" t="n">
+        <v>0</v>
+      </c>
+      <c r="K594" t="n">
+        <v>8</v>
+      </c>
+      <c r="M594" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr"/>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-HOUATHOMPSON1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>8</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F595" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G595" t="n">
+        <v>25</v>
+      </c>
+      <c r="H595" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J595" t="n">
+        <v>0</v>
+      </c>
+      <c r="K595" t="n">
+        <v>25</v>
+      </c>
+      <c r="M595" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr"/>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01LALHOU-HOUATHOMPSON1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Anthony Black</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>25</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F596" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G596" t="n">
+        <v>5</v>
+      </c>
+      <c r="H596" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J596" t="n">
+        <v>0</v>
+      </c>
+      <c r="K596" t="n">
+        <v>5</v>
+      </c>
+      <c r="M596" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr"/>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-ORLABLACK0-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Anthony Black</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>8</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F597" t="n">
+        <v>3</v>
+      </c>
+      <c r="G597" t="n">
+        <v>6</v>
+      </c>
+      <c r="H597" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J597" t="n">
+        <v>0</v>
+      </c>
+      <c r="K597" t="n">
+        <v>6</v>
+      </c>
+      <c r="M597" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr"/>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01DETORL-ORLABLACK0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>3</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F598" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G598" t="n">
+        <v>33</v>
+      </c>
+      <c r="H598" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J598" t="n">
+        <v>0</v>
+      </c>
+      <c r="K598" t="n">
+        <v>33</v>
+      </c>
+      <c r="M598" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr"/>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01DETORL-DETATHOMPSON9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>25</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F599" t="n">
+        <v>3</v>
+      </c>
+      <c r="G599" t="n">
+        <v>4</v>
+      </c>
+      <c r="H599" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J599" t="n">
+        <v>0</v>
+      </c>
+      <c r="K599" t="n">
+        <v>4</v>
+      </c>
+      <c r="M599" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr"/>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-DETATHOMPSON9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>8</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F600" t="n">
+        <v>3</v>
+      </c>
+      <c r="G600" t="n">
+        <v>5</v>
+      </c>
+      <c r="H600" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J600" t="n">
+        <v>0</v>
+      </c>
+      <c r="K600" t="n">
+        <v>5</v>
+      </c>
+      <c r="M600" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr"/>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01DETORL-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>8</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F601" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G601" t="n">
+        <v>47</v>
+      </c>
+      <c r="H601" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J601" t="n">
+        <v>0</v>
+      </c>
+      <c r="K601" t="n">
+        <v>47</v>
+      </c>
+      <c r="M601" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr"/>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Austin Reaves</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>35</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F602" t="n">
+        <v>3</v>
+      </c>
+      <c r="G602" t="n">
+        <v>10</v>
+      </c>
+      <c r="H602" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J602" t="n">
+        <v>0</v>
+      </c>
+      <c r="K602" t="n">
+        <v>10</v>
+      </c>
+      <c r="M602" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr"/>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-LALAREAVES15-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Austin Reaves</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>8</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F603" t="n">
+        <v>3</v>
+      </c>
+      <c r="G603" t="n">
+        <v>26</v>
+      </c>
+      <c r="H603" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J603" t="n">
+        <v>0</v>
+      </c>
+      <c r="K603" t="n">
+        <v>26</v>
+      </c>
+      <c r="M603" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr"/>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01LALHOU-LALAREAVES15-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>8</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F604" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G604" t="n">
+        <v>30</v>
+      </c>
+      <c r="H604" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J604" t="n">
+        <v>0</v>
+      </c>
+      <c r="K604" t="n">
+        <v>30</v>
+      </c>
+      <c r="M604" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr"/>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>9</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F605" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G605" t="n">
+        <v>60</v>
+      </c>
+      <c r="H605" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J605" t="n">
+        <v>0</v>
+      </c>
+      <c r="K605" t="n">
+        <v>60</v>
+      </c>
+      <c r="M605" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr"/>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01DETORL-DETCCUNNINGHAM2-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>40</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F606" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G606" t="n">
+        <v>14</v>
+      </c>
+      <c r="H606" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J606" t="n">
+        <v>0</v>
+      </c>
+      <c r="K606" t="n">
+        <v>14</v>
+      </c>
+      <c r="M606" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr"/>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-DETCCUNNINGHAM2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>3</v>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F607" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G607" t="n">
+        <v>16</v>
+      </c>
+      <c r="H607" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J607" t="n">
+        <v>0</v>
+      </c>
+      <c r="K607" t="n">
+        <v>16</v>
+      </c>
+      <c r="M607" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr"/>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01DETORL-DETCCUNNINGHAM2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>3</v>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F608" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G608" t="n">
+        <v>13</v>
+      </c>
+      <c r="H608" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J608" t="n">
+        <v>0</v>
+      </c>
+      <c r="K608" t="n">
+        <v>13</v>
+      </c>
+      <c r="M608" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr"/>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY01LALHOU-LALDAYTON5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>25</v>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F609" t="n">
+        <v>3</v>
+      </c>
+      <c r="G609" t="n">
+        <v>5</v>
+      </c>
+      <c r="H609" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J609" t="n">
+        <v>0</v>
+      </c>
+      <c r="K609" t="n">
+        <v>5</v>
+      </c>
+      <c r="M609" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr"/>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-LALDAYTON5-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>9</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F610" t="n">
+        <v>44</v>
+      </c>
+      <c r="G610" t="n">
+        <v>53</v>
+      </c>
+      <c r="H610" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J610" t="n">
+        <v>0</v>
+      </c>
+      <c r="K610" t="n">
+        <v>53</v>
+      </c>
+      <c r="M610" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr"/>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01LALHOU-LALDAYTON5-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>20</v>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F611" t="n">
+        <v>3</v>
+      </c>
+      <c r="G611" t="n">
+        <v>5</v>
+      </c>
+      <c r="H611" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J611" t="n">
+        <v>0</v>
+      </c>
+      <c r="K611" t="n">
+        <v>5</v>
+      </c>
+      <c r="M611" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr"/>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEDSCHRODER8-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>10</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F612" t="n">
+        <v>3</v>
+      </c>
+      <c r="G612" t="n">
+        <v>5</v>
+      </c>
+      <c r="H612" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J612" t="n">
+        <v>0</v>
+      </c>
+      <c r="K612" t="n">
+        <v>5</v>
+      </c>
+      <c r="M612" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr"/>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01CLETOR-CLEDSCHRODER8-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Desmond Bane</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>30</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F613" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G613" t="n">
+        <v>11</v>
+      </c>
+      <c r="H613" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J613" t="n">
+        <v>0</v>
+      </c>
+      <c r="K613" t="n">
+        <v>11</v>
+      </c>
+      <c r="M613" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr"/>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-ORLDBANE3-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>8</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F614" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G614" t="n">
+        <v>12</v>
+      </c>
+      <c r="H614" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J614" t="n">
+        <v>0</v>
+      </c>
+      <c r="K614" t="n">
+        <v>12</v>
+      </c>
+      <c r="M614" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr"/>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01CLETOR-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>8</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F615" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G615" t="n">
+        <v>10</v>
+      </c>
+      <c r="H615" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J615" t="n">
+        <v>0</v>
+      </c>
+      <c r="K615" t="n">
+        <v>10</v>
+      </c>
+      <c r="M615" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr"/>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01CLETOR-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>40</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F616" t="n">
+        <v>3</v>
+      </c>
+      <c r="G616" t="n">
+        <v>8</v>
+      </c>
+      <c r="H616" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J616" t="n">
+        <v>0</v>
+      </c>
+      <c r="K616" t="n">
+        <v>8</v>
+      </c>
+      <c r="M616" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr"/>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEDMITCHELL45-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>3</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F617" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G617" t="n">
+        <v>17</v>
+      </c>
+      <c r="H617" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J617" t="n">
+        <v>0</v>
+      </c>
+      <c r="K617" t="n">
+        <v>17</v>
+      </c>
+      <c r="M617" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr"/>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01CLETOR-CLEDMITCHELL45-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>20</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F618" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G618" t="n">
+        <v>8</v>
+      </c>
+      <c r="H618" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J618" t="n">
+        <v>0</v>
+      </c>
+      <c r="K618" t="n">
+        <v>8</v>
+      </c>
+      <c r="M618" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr"/>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-DETDROBINSON55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>25</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F619" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G619" t="n">
+        <v>11</v>
+      </c>
+      <c r="H619" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J619" t="n">
+        <v>0</v>
+      </c>
+      <c r="K619" t="n">
+        <v>11</v>
+      </c>
+      <c r="M619" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr"/>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEEMOBLEY4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>9</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F620" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="G620" t="n">
+        <v>54</v>
+      </c>
+      <c r="H620" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J620" t="n">
+        <v>0</v>
+      </c>
+      <c r="K620" t="n">
+        <v>54</v>
+      </c>
+      <c r="M620" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr"/>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01CLETOR-CLEEMOBLEY4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>3</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F621" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G621" t="n">
+        <v>27</v>
+      </c>
+      <c r="H621" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J621" t="n">
+        <v>0</v>
+      </c>
+      <c r="K621" t="n">
+        <v>27</v>
+      </c>
+      <c r="M621" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr"/>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY01CLETOR-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>3</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F622" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G622" t="n">
+        <v>8</v>
+      </c>
+      <c r="H622" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J622" t="n">
+        <v>0</v>
+      </c>
+      <c r="K622" t="n">
+        <v>8</v>
+      </c>
+      <c r="M622" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr"/>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01CLETOR-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>30</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F623" t="n">
+        <v>3</v>
+      </c>
+      <c r="G623" t="n">
+        <v>7</v>
+      </c>
+      <c r="H623" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J623" t="n">
+        <v>0</v>
+      </c>
+      <c r="K623" t="n">
+        <v>7</v>
+      </c>
+      <c r="M623" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr"/>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-HOUJSMITH10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Jabari Smith Jr.</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>8</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F624" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="G624" t="n">
+        <v>47</v>
+      </c>
+      <c r="H624" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J624" t="n">
+        <v>0</v>
+      </c>
+      <c r="K624" t="n">
+        <v>47</v>
+      </c>
+      <c r="M624" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr"/>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01LALHOU-HOUJSMITH10-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>8</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F625" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="G625" t="n">
+        <v>23</v>
+      </c>
+      <c r="H625" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J625" t="n">
+        <v>0</v>
+      </c>
+      <c r="K625" t="n">
+        <v>23</v>
+      </c>
+      <c r="M625" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr"/>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01CLETOR-TORJPOELTL19-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>8</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F626" t="n">
+        <v>3</v>
+      </c>
+      <c r="G626" t="n">
+        <v>5</v>
+      </c>
+      <c r="H626" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J626" t="n">
+        <v>0</v>
+      </c>
+      <c r="K626" t="n">
+        <v>5</v>
+      </c>
+      <c r="M626" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr"/>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01CLETOR-TORJPOELTL19-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>20</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F627" t="n">
+        <v>3</v>
+      </c>
+      <c r="G627" t="n">
+        <v>6</v>
+      </c>
+      <c r="H627" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J627" t="n">
+        <v>0</v>
+      </c>
+      <c r="K627" t="n">
+        <v>6</v>
+      </c>
+      <c r="M627" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr"/>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-TORJPOELTL19-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>8</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F628" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="G628" t="n">
+        <v>68</v>
+      </c>
+      <c r="H628" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J628" t="n">
+        <v>15</v>
+      </c>
+      <c r="K628" t="n">
+        <v>68</v>
+      </c>
+      <c r="M628" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr"/>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>25</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F629" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G629" t="n">
+        <v>6</v>
+      </c>
+      <c r="H629" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J629" t="n">
+        <v>31</v>
+      </c>
+      <c r="K629" t="n">
+        <v>6</v>
+      </c>
+      <c r="M629" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr"/>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-DETJDUREN0-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>8</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F630" t="n">
+        <v>3</v>
+      </c>
+      <c r="G630" t="n">
+        <v>4</v>
+      </c>
+      <c r="H630" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J630" t="n">
+        <v>0</v>
+      </c>
+      <c r="K630" t="n">
+        <v>4</v>
+      </c>
+      <c r="M630" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr"/>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01DETORL-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>3</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G631" t="n">
+        <v>15</v>
+      </c>
+      <c r="H631" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J631" t="n">
+        <v>0</v>
+      </c>
+      <c r="K631" t="n">
+        <v>15</v>
+      </c>
+      <c r="M631" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr"/>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY01DETORL-DETJDUREN0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>3</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F632" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G632" t="n">
+        <v>27</v>
+      </c>
+      <c r="H632" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J632" t="n">
+        <v>0</v>
+      </c>
+      <c r="K632" t="n">
+        <v>27</v>
+      </c>
+      <c r="M632" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr"/>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01DETORL-ORLJSUGGS4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>8</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F633" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G633" t="n">
+        <v>12</v>
+      </c>
+      <c r="H633" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J633" t="n">
+        <v>0</v>
+      </c>
+      <c r="K633" t="n">
+        <v>12</v>
+      </c>
+      <c r="M633" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr"/>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01DETORL-ORLJSUGGS4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>8</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G634" t="n">
+        <v>9</v>
+      </c>
+      <c r="H634" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J634" t="n">
+        <v>0</v>
+      </c>
+      <c r="K634" t="n">
+        <v>9</v>
+      </c>
+      <c r="M634" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr"/>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-ORLJSUGGS4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>25</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F635" t="n">
+        <v>3</v>
+      </c>
+      <c r="G635" t="n">
+        <v>8</v>
+      </c>
+      <c r="H635" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J635" t="n">
+        <v>0</v>
+      </c>
+      <c r="K635" t="n">
+        <v>8</v>
+      </c>
+      <c r="M635" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr"/>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-ORLJSUGGS4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>8</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F636" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G636" t="n">
+        <v>14</v>
+      </c>
+      <c r="H636" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J636" t="n">
+        <v>0</v>
+      </c>
+      <c r="K636" t="n">
+        <v>14</v>
+      </c>
+      <c r="M636" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr"/>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01CLETOR-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>8</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F637" t="n">
+        <v>35</v>
+      </c>
+      <c r="G637" t="n">
+        <v>42</v>
+      </c>
+      <c r="H637" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J637" t="n">
+        <v>0</v>
+      </c>
+      <c r="K637" t="n">
+        <v>42</v>
+      </c>
+      <c r="M637" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr"/>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01CLETOR-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>3</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F638" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G638" t="n">
+        <v>17</v>
+      </c>
+      <c r="H638" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J638" t="n">
+        <v>0</v>
+      </c>
+      <c r="K638" t="n">
+        <v>17</v>
+      </c>
+      <c r="M638" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr"/>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01CLETOR-CLEJHARDEN1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>30</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F639" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G639" t="n">
+        <v>15</v>
+      </c>
+      <c r="H639" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J639" t="n">
+        <v>0</v>
+      </c>
+      <c r="K639" t="n">
+        <v>15</v>
+      </c>
+      <c r="M639" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr"/>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEJHARDEN1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>20</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F640" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G640" t="n">
+        <v>7</v>
+      </c>
+      <c r="H640" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J640" t="n">
+        <v>39</v>
+      </c>
+      <c r="K640" t="n">
+        <v>7</v>
+      </c>
+      <c r="M640" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr"/>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEJALLEN31-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>8</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F641" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G641" t="n">
+        <v>52</v>
+      </c>
+      <c r="H641" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J641" t="n">
+        <v>0</v>
+      </c>
+      <c r="K641" t="n">
+        <v>52</v>
+      </c>
+      <c r="M641" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr"/>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01CLETOR-CLEJALLEN31-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>3</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F642" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G642" t="n">
+        <v>16</v>
+      </c>
+      <c r="H642" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J642" t="n">
+        <v>0</v>
+      </c>
+      <c r="K642" t="n">
+        <v>16</v>
+      </c>
+      <c r="M642" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr"/>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY01CLETOR-CLEJALLEN31-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Jaylon Tyson</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>20</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F643" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G643" t="n">
+        <v>5</v>
+      </c>
+      <c r="H643" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J643" t="n">
+        <v>0</v>
+      </c>
+      <c r="K643" t="n">
+        <v>5</v>
+      </c>
+      <c r="M643" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr"/>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEJTYSON20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>35</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F644" t="n">
+        <v>3</v>
+      </c>
+      <c r="G644" t="n">
+        <v>9</v>
+      </c>
+      <c r="H644" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J644" t="n">
+        <v>0</v>
+      </c>
+      <c r="K644" t="n">
+        <v>9</v>
+      </c>
+      <c r="M644" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr"/>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-LALLJAMES23-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>3</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F645" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G645" t="n">
+        <v>18</v>
+      </c>
+      <c r="H645" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J645" t="n">
+        <v>0</v>
+      </c>
+      <c r="K645" t="n">
+        <v>18</v>
+      </c>
+      <c r="M645" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr"/>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01LALHOU-LALLJAMES23-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>8</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F646" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G646" t="n">
+        <v>42</v>
+      </c>
+      <c r="H646" t="n">
+        <v>-35.6</v>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J646" t="n">
+        <v>0</v>
+      </c>
+      <c r="K646" t="n">
+        <v>42</v>
+      </c>
+      <c r="M646" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr"/>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01LALHOU-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>8</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F647" t="n">
+        <v>3</v>
+      </c>
+      <c r="G647" t="n">
+        <v>56</v>
+      </c>
+      <c r="H647" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J647" t="n">
+        <v>0</v>
+      </c>
+      <c r="K647" t="n">
+        <v>56</v>
+      </c>
+      <c r="M647" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr"/>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01LALHOU-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>8</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F648" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G648" t="n">
+        <v>7</v>
+      </c>
+      <c r="H648" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J648" t="n">
+        <v>0</v>
+      </c>
+      <c r="K648" t="n">
+        <v>7</v>
+      </c>
+      <c r="M648" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr"/>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01LALHOU-LALMSMART36-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>20</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F649" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G649" t="n">
+        <v>11</v>
+      </c>
+      <c r="H649" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J649" t="n">
+        <v>0</v>
+      </c>
+      <c r="K649" t="n">
+        <v>11</v>
+      </c>
+      <c r="M649" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr"/>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-LALMSMART36-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>3</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F650" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G650" t="n">
+        <v>23</v>
+      </c>
+      <c r="H650" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J650" t="n">
+        <v>0</v>
+      </c>
+      <c r="K650" t="n">
+        <v>23</v>
+      </c>
+      <c r="M650" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr"/>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01LALHOU-LALMSMART36-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>8</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F651" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G651" t="n">
+        <v>59</v>
+      </c>
+      <c r="H651" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J651" t="n">
+        <v>0</v>
+      </c>
+      <c r="K651" t="n">
+        <v>59</v>
+      </c>
+      <c r="M651" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr"/>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-ORLPBANCHERO5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>35</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F652" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G652" t="n">
+        <v>9</v>
+      </c>
+      <c r="H652" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J652" t="n">
+        <v>0</v>
+      </c>
+      <c r="K652" t="n">
+        <v>9</v>
+      </c>
+      <c r="M652" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr"/>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-ORLPBANCHERO5-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>8</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F653" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G653" t="n">
+        <v>19</v>
+      </c>
+      <c r="H653" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J653" t="n">
+        <v>0</v>
+      </c>
+      <c r="K653" t="n">
+        <v>19</v>
+      </c>
+      <c r="M653" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr"/>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01DETORL-ORLPBANCHERO5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>3</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F654" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G654" t="n">
+        <v>7</v>
+      </c>
+      <c r="H654" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J654" t="n">
+        <v>0</v>
+      </c>
+      <c r="K654" t="n">
+        <v>7</v>
+      </c>
+      <c r="M654" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr"/>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY01DETORL-ORLPBANCHERO5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>3</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F655" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G655" t="n">
+        <v>13</v>
+      </c>
+      <c r="H655" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J655" t="n">
+        <v>0</v>
+      </c>
+      <c r="K655" t="n">
+        <v>13</v>
+      </c>
+      <c r="M655" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr"/>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01DETORL-ORLPBANCHERO5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Reed Sheppard</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>8</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F656" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G656" t="n">
+        <v>11</v>
+      </c>
+      <c r="H656" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J656" t="n">
+        <v>0</v>
+      </c>
+      <c r="K656" t="n">
+        <v>11</v>
+      </c>
+      <c r="M656" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr"/>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01LALHOU-HOURSHEPPARD15-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Reed Sheppard</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>25</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F657" t="n">
+        <v>3</v>
+      </c>
+      <c r="G657" t="n">
+        <v>14</v>
+      </c>
+      <c r="H657" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J657" t="n">
+        <v>0</v>
+      </c>
+      <c r="K657" t="n">
+        <v>14</v>
+      </c>
+      <c r="M657" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr"/>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-HOURSHEPPARD15-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>8</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F658" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G658" t="n">
+        <v>28</v>
+      </c>
+      <c r="H658" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J658" t="n">
+        <v>0</v>
+      </c>
+      <c r="K658" t="n">
+        <v>28</v>
+      </c>
+      <c r="M658" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr"/>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01CLETOR-TORRBARRETT9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>35</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F659" t="n">
+        <v>3</v>
+      </c>
+      <c r="G659" t="n">
+        <v>8</v>
+      </c>
+      <c r="H659" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J659" t="n">
+        <v>0</v>
+      </c>
+      <c r="K659" t="n">
+        <v>8</v>
+      </c>
+      <c r="M659" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr"/>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-TORRBARRETT9-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>8</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F660" t="n">
+        <v>3</v>
+      </c>
+      <c r="G660" t="n">
+        <v>8</v>
+      </c>
+      <c r="H660" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J660" t="n">
+        <v>0</v>
+      </c>
+      <c r="K660" t="n">
+        <v>8</v>
+      </c>
+      <c r="M660" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr"/>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01CLETOR-TORRBARRETT9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>3</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F661" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G661" t="n">
+        <v>9</v>
+      </c>
+      <c r="H661" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J661" t="n">
+        <v>0</v>
+      </c>
+      <c r="K661" t="n">
+        <v>9</v>
+      </c>
+      <c r="M661" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr"/>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01CLETOR-TORRBARRETT9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>20</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F662" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G662" t="n">
+        <v>14</v>
+      </c>
+      <c r="H662" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J662" t="n">
+        <v>0</v>
+      </c>
+      <c r="K662" t="n">
+        <v>14</v>
+      </c>
+      <c r="M662" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr"/>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-LALRHACHIMURA28-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>3</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F663" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G663" t="n">
+        <v>16</v>
+      </c>
+      <c r="H663" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J663" t="n">
+        <v>0</v>
+      </c>
+      <c r="K663" t="n">
+        <v>16</v>
+      </c>
+      <c r="M663" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr"/>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY01CLETOR-TORSBARNES4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>3</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F664" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G664" t="n">
+        <v>19</v>
+      </c>
+      <c r="H664" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J664" t="n">
+        <v>0</v>
+      </c>
+      <c r="K664" t="n">
+        <v>19</v>
+      </c>
+      <c r="M664" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr"/>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY01CLETOR-TORSBARNES4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>30</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F665" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G665" t="n">
+        <v>14</v>
+      </c>
+      <c r="H665" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J665" t="n">
+        <v>0</v>
+      </c>
+      <c r="K665" t="n">
+        <v>14</v>
+      </c>
+      <c r="M665" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr"/>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01CLETOR-TORSBARNES4-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>8</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F666" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G666" t="n">
+        <v>50</v>
+      </c>
+      <c r="H666" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J666" t="n">
+        <v>0</v>
+      </c>
+      <c r="K666" t="n">
+        <v>50</v>
+      </c>
+      <c r="M666" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr"/>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01CLETOR-TORSBARNES4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>8</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F667" t="n">
+        <v>40</v>
+      </c>
+      <c r="G667" t="n">
+        <v>58</v>
+      </c>
+      <c r="H667" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J667" t="n">
+        <v>0</v>
+      </c>
+      <c r="K667" t="n">
+        <v>58</v>
+      </c>
+      <c r="M667" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr"/>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01CLETOR-TORSBARNES4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>8</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F668" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G668" t="n">
+        <v>44</v>
+      </c>
+      <c r="H668" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J668" t="n">
+        <v>8</v>
+      </c>
+      <c r="K668" t="n">
+        <v>44</v>
+      </c>
+      <c r="M668" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr"/>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01LALHOU-HOUTEASON17-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Tari Eason</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>25</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F669" t="n">
+        <v>3</v>
+      </c>
+      <c r="G669" t="n">
+        <v>7</v>
+      </c>
+      <c r="H669" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J669" t="n">
+        <v>0</v>
+      </c>
+      <c r="K669" t="n">
+        <v>7</v>
+      </c>
+      <c r="M669" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr"/>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01LALHOU-HOUTEASON17-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>30</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F670" t="n">
+        <v>3</v>
+      </c>
+      <c r="G670" t="n">
+        <v>7</v>
+      </c>
+      <c r="H670" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J670" t="n">
+        <v>0</v>
+      </c>
+      <c r="K670" t="n">
+        <v>7</v>
+      </c>
+      <c r="M670" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr"/>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-DETTHARRIS12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>8</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F671" t="n">
+        <v>3</v>
+      </c>
+      <c r="G671" t="n">
+        <v>7</v>
+      </c>
+      <c r="H671" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J671" t="n">
+        <v>0</v>
+      </c>
+      <c r="K671" t="n">
+        <v>7</v>
+      </c>
+      <c r="M671" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr"/>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY01DETORL-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>8</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F672" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G672" t="n">
+        <v>34</v>
+      </c>
+      <c r="H672" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J672" t="n">
+        <v>0</v>
+      </c>
+      <c r="K672" t="n">
+        <v>34</v>
+      </c>
+      <c r="M672" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr"/>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>20</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F673" t="n">
+        <v>3</v>
+      </c>
+      <c r="G673" t="n">
+        <v>9</v>
+      </c>
+      <c r="H673" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J673" t="n">
+        <v>0</v>
+      </c>
+      <c r="K673" t="n">
+        <v>9</v>
+      </c>
+      <c r="M673" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr"/>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-ORLWCARTER34-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>8</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F674" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G674" t="n">
+        <v>57</v>
+      </c>
+      <c r="H674" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J674" t="n">
+        <v>0</v>
+      </c>
+      <c r="K674" t="n">
+        <v>57</v>
+      </c>
+      <c r="M674" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr"/>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-ORLWCARTER34-8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37244,7 +42122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37580,6 +42458,33 @@
         <v>-0.2</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>87</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>87</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37591,7 +42496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -37637,86 +42542,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.51</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.08</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.35</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -37725,196 +42630,196 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.294</v>
+        <v>0.308</v>
       </c>
       <c r="F6" t="n">
-        <v>9.01</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>17.87</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.067</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-10.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>14</v>
       </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.333</v>
+        <v>0.067</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
         <v>13</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>12</v>
-      </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.083</v>
+        <v>0.333</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.308</v>
+        <v>0.083</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.29</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -37923,108 +42828,108 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.083</v>
+        <v>0.091</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>12</v>
       </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
         <v>11</v>
       </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>7</v>
-      </c>
       <c r="E19" t="n">
-        <v>0.222</v>
+        <v>0.083</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -38033,20 +42938,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.273</v>
+        <v>0.333</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -38055,20 +42960,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.091</v>
+        <v>0.375</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -38077,64 +42982,64 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -38143,20 +43048,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -38165,42 +43070,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -38209,42 +43114,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -38253,64 +43158,64 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>16.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
         <v>8</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>7</v>
-      </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -38319,42 +43224,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jaden Mcdaniels</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.39</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -38363,20 +43268,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -38385,42 +43290,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rj Barrett</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -38429,17 +43334,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -38451,62 +43356,64 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
         <v>6</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -38515,20 +43422,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
         <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -38537,29 +43444,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -38569,11 +43476,9 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
         <v>0</v>
       </c>
@@ -38581,20 +43486,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -38603,42 +43508,42 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>-4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -38691,51 +43596,51 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -38757,17 +43662,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -38779,7 +43684,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Donte Divincenzo</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -38789,9 +43694,11 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
@@ -38799,7 +43706,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -38809,7 +43716,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -38821,21 +43728,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Donte Divincenzo</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
         <v>0</v>
       </c>
@@ -38843,17 +43748,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
         <v>3</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -38865,20 +43770,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -38887,11 +43792,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -38909,21 +43814,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
         <v>0</v>
       </c>
@@ -38931,7 +43834,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -38941,7 +43844,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -38953,19 +43856,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
@@ -38973,19 +43878,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
@@ -38993,7 +43900,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -39013,7 +43920,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -39033,7 +43940,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -39053,7 +43960,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -39073,7 +43980,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -39093,7 +44000,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -39113,7 +44020,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -39133,7 +44040,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -39153,7 +44060,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -39173,7 +44080,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -39193,7 +44100,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -39203,11 +44110,9 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
         <v>0</v>
       </c>
@@ -39215,7 +44120,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -39225,11 +44130,9 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
         <v>0</v>
       </c>
@@ -39237,7 +44140,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -39247,9 +44150,11 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
@@ -39257,7 +44162,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jake Laravia</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -39267,11 +44172,9 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>0</v>
       </c>
@@ -39279,7 +44182,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Jake Laravia</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -39289,9 +44192,11 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
@@ -39299,7 +44204,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -39319,7 +44224,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -39339,7 +44244,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -39359,11 +44264,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Shaedon Sharpe</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -39379,11 +44284,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -39399,7 +44304,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -39419,7 +44324,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Jerami Grant</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -39439,7 +44344,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -39459,7 +44364,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cj Mccollum</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -39479,7 +44384,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -39489,12 +44394,52 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cj Mccollum</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Grayson Allen</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
         <v>-2.85</v>
       </c>
     </row>
@@ -39559,7 +44504,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
@@ -39581,7 +44526,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -39603,7 +44548,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
@@ -39625,7 +44570,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C5" t="n">
         <v>36</v>
@@ -39647,7 +44592,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +55,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,14 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P674"/>
+  <dimension ref="A1:P676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37283,12 +37277,20 @@
       <c r="K588" t="n">
         <v>12</v>
       </c>
-      <c r="M588" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L588" t="n">
+        <v>17</v>
+      </c>
+      <c r="M588" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N588" t="inlineStr"/>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P588" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY01LALHOU-HOUASENGUN28-30</t>
@@ -37339,12 +37341,20 @@
       <c r="K589" t="n">
         <v>14</v>
       </c>
-      <c r="M589" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L589" t="n">
+        <v>2</v>
+      </c>
+      <c r="M589" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N589" t="inlineStr"/>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P589" t="inlineStr">
         <is>
           <t>KXNBABLK-26MAY01LALHOU-HOUASENGUN28-3</t>
@@ -37395,12 +37405,20 @@
       <c r="K590" t="n">
         <v>28</v>
       </c>
-      <c r="M590" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L590" t="n">
+        <v>1</v>
+      </c>
+      <c r="M590" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N590" t="inlineStr"/>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P590" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY01LALHOU-HOUASENGUN28-8</t>
@@ -37451,12 +37469,20 @@
       <c r="K591" t="n">
         <v>73</v>
       </c>
-      <c r="M591" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L591" t="n">
+        <v>11</v>
+      </c>
+      <c r="M591" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N591" t="inlineStr"/>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P591" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY01LALHOU-HOUASENGUN28-8</t>
@@ -37507,12 +37533,22 @@
       <c r="K592" t="n">
         <v>28</v>
       </c>
-      <c r="M592" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N592" t="inlineStr"/>
+      <c r="L592" t="n">
+        <v>0</v>
+      </c>
+      <c r="M592" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N592" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P592" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY01LALHOU-HOUATHOMPSON1-3</t>
@@ -37563,12 +37599,20 @@
       <c r="K593" t="n">
         <v>49</v>
       </c>
-      <c r="M593" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L593" t="n">
+        <v>8</v>
+      </c>
+      <c r="M593" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N593" t="inlineStr"/>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P593" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY01LALHOU-HOUATHOMPSON1-8</t>
@@ -37619,12 +37663,20 @@
       <c r="K594" t="n">
         <v>8</v>
       </c>
-      <c r="M594" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L594" t="n">
+        <v>18</v>
+      </c>
+      <c r="M594" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N594" t="inlineStr"/>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P594" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY01LALHOU-HOUATHOMPSON1-30</t>
@@ -37675,12 +37727,20 @@
       <c r="K595" t="n">
         <v>25</v>
       </c>
-      <c r="M595" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L595" t="n">
+        <v>3</v>
+      </c>
+      <c r="M595" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N595" t="inlineStr"/>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P595" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY01LALHOU-HOUATHOMPSON1-8</t>
@@ -37695,16 +37755,16 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D596" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E596" t="inlineStr">
         <is>
@@ -37712,13 +37772,13 @@
         </is>
       </c>
       <c r="F596" t="n">
-        <v>3.9</v>
+        <v>16.6</v>
       </c>
       <c r="G596" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H596" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I596" t="inlineStr">
         <is>
@@ -37729,17 +37789,25 @@
         <v>0</v>
       </c>
       <c r="K596" t="n">
-        <v>5</v>
-      </c>
-      <c r="M596" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>18</v>
+      </c>
+      <c r="L596" t="n">
+        <v>3</v>
+      </c>
+      <c r="M596" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N596" t="inlineStr"/>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P596" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-ORLABLACK0-25</t>
+          <t>KXNBABLK-26MAY01LALHOU-HOUATHOMPSON1-2</t>
         </is>
       </c>
     </row>
@@ -37756,46 +37824,54 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D597" t="n">
+        <v>25</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F597" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G597" t="n">
+        <v>5</v>
+      </c>
+      <c r="H597" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J597" t="n">
+        <v>0</v>
+      </c>
+      <c r="K597" t="n">
+        <v>5</v>
+      </c>
+      <c r="L597" t="n">
         <v>8</v>
       </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F597" t="n">
-        <v>3</v>
-      </c>
-      <c r="G597" t="n">
-        <v>6</v>
-      </c>
-      <c r="H597" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I597" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J597" t="n">
-        <v>0</v>
-      </c>
-      <c r="K597" t="n">
-        <v>6</v>
-      </c>
-      <c r="M597" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M597" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N597" t="inlineStr"/>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P597" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01DETORL-ORLABLACK0-8</t>
+          <t>KXNBAPTS-26MAY01DETORL-ORLABLACK0-25</t>
         </is>
       </c>
     </row>
@@ -37807,30 +37883,30 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D598" t="n">
+        <v>8</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F598" t="n">
         <v>3</v>
       </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F598" t="n">
-        <v>37.5</v>
-      </c>
       <c r="G598" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H598" t="n">
-        <v>4.5</v>
+        <v>-3</v>
       </c>
       <c r="I598" t="inlineStr">
         <is>
@@ -37841,17 +37917,25 @@
         <v>0</v>
       </c>
       <c r="K598" t="n">
-        <v>33</v>
-      </c>
-      <c r="M598" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>6</v>
+      </c>
+      <c r="L598" t="n">
+        <v>1</v>
+      </c>
+      <c r="M598" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N598" t="inlineStr"/>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P598" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01DETORL-DETATHOMPSON9-3</t>
+          <t>KXNBAAST-26MAY01DETORL-ORLABLACK0-8</t>
         </is>
       </c>
     </row>
@@ -37868,11 +37952,11 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D599" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E599" t="inlineStr">
         <is>
@@ -37880,34 +37964,42 @@
         </is>
       </c>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>37.5</v>
       </c>
       <c r="G599" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H599" t="n">
-        <v>-1</v>
+        <v>4.5</v>
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J599" t="n">
         <v>0</v>
       </c>
       <c r="K599" t="n">
-        <v>4</v>
-      </c>
-      <c r="M599" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>33</v>
+      </c>
+      <c r="L599" t="n">
+        <v>1</v>
+      </c>
+      <c r="M599" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N599" t="inlineStr"/>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P599" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-DETATHOMPSON9-25</t>
+          <t>KXNBASTL-26MAY01DETORL-DETATHOMPSON9-3</t>
         </is>
       </c>
     </row>
@@ -37924,11 +38016,11 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D600" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E600" t="inlineStr">
         <is>
@@ -37939,31 +38031,39 @@
         <v>3</v>
       </c>
       <c r="G600" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H600" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J600" t="n">
         <v>0</v>
       </c>
       <c r="K600" t="n">
-        <v>5</v>
-      </c>
-      <c r="M600" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>4</v>
+      </c>
+      <c r="L600" t="n">
+        <v>4</v>
+      </c>
+      <c r="M600" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N600" t="inlineStr"/>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P600" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01DETORL-DETATHOMPSON9-8</t>
+          <t>KXNBAPTS-26MAY01DETORL-DETATHOMPSON9-25</t>
         </is>
       </c>
     </row>
@@ -37980,7 +38080,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D601" t="n">
@@ -37992,34 +38092,42 @@
         </is>
       </c>
       <c r="F601" t="n">
-        <v>42.2</v>
+        <v>3</v>
       </c>
       <c r="G601" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H601" t="n">
-        <v>-4.8</v>
+        <v>-2</v>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J601" t="n">
         <v>0</v>
       </c>
       <c r="K601" t="n">
-        <v>47</v>
-      </c>
-      <c r="M601" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L601" t="n">
+        <v>6</v>
+      </c>
+      <c r="M601" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N601" t="inlineStr"/>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P601" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01DETORL-DETATHOMPSON9-8</t>
+          <t>KXNBAAST-26MAY01DETORL-DETATHOMPSON9-8</t>
         </is>
       </c>
     </row>
@@ -38031,16 +38139,16 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D602" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E602" t="inlineStr">
         <is>
@@ -38048,34 +38156,42 @@
         </is>
       </c>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>42.2</v>
       </c>
       <c r="G602" t="n">
+        <v>47</v>
+      </c>
+      <c r="H602" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J602" t="n">
+        <v>0</v>
+      </c>
+      <c r="K602" t="n">
+        <v>47</v>
+      </c>
+      <c r="L602" t="n">
         <v>10</v>
       </c>
-      <c r="H602" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="J602" t="n">
-        <v>0</v>
-      </c>
-      <c r="K602" t="n">
-        <v>10</v>
-      </c>
-      <c r="M602" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M602" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N602" t="inlineStr"/>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P602" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-LALAREAVES15-35</t>
+          <t>KXNBAREB-26MAY01DETORL-DETATHOMPSON9-8</t>
         </is>
       </c>
     </row>
@@ -38092,11 +38208,11 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D603" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E603" t="inlineStr">
         <is>
@@ -38107,10 +38223,10 @@
         <v>3</v>
       </c>
       <c r="G603" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H603" t="n">
-        <v>-23</v>
+        <v>-7</v>
       </c>
       <c r="I603" t="inlineStr">
         <is>
@@ -38121,17 +38237,25 @@
         <v>0</v>
       </c>
       <c r="K603" t="n">
-        <v>26</v>
-      </c>
-      <c r="M603" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>10</v>
+      </c>
+      <c r="L603" t="n">
+        <v>15</v>
+      </c>
+      <c r="M603" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N603" t="inlineStr"/>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P603" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01LALHOU-LALAREAVES15-8</t>
+          <t>KXNBAPTS-26MAY01LALHOU-LALAREAVES15-35</t>
         </is>
       </c>
     </row>
@@ -38143,12 +38267,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D604" t="n">
@@ -38160,13 +38284,13 @@
         </is>
       </c>
       <c r="F604" t="n">
-        <v>29.4</v>
+        <v>3</v>
       </c>
       <c r="G604" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H604" t="n">
-        <v>-0.6</v>
+        <v>-23</v>
       </c>
       <c r="I604" t="inlineStr">
         <is>
@@ -38177,17 +38301,25 @@
         <v>0</v>
       </c>
       <c r="K604" t="n">
-        <v>30</v>
-      </c>
-      <c r="M604" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>26</v>
+      </c>
+      <c r="L604" t="n">
+        <v>2</v>
+      </c>
+      <c r="M604" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N604" t="inlineStr"/>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P604" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01DETORL-DETCCUNNINGHAM2-8</t>
+          <t>KXNBAAST-26MAY01LALHOU-LALAREAVES15-8</t>
         </is>
       </c>
     </row>
@@ -38204,11 +38336,11 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D605" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E605" t="inlineStr">
         <is>
@@ -38216,34 +38348,42 @@
         </is>
       </c>
       <c r="F605" t="n">
-        <v>58.9</v>
+        <v>29.4</v>
       </c>
       <c r="G605" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H605" t="n">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J605" t="n">
         <v>0</v>
       </c>
       <c r="K605" t="n">
-        <v>60</v>
-      </c>
-      <c r="M605" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>30</v>
+      </c>
+      <c r="L605" t="n">
+        <v>10</v>
+      </c>
+      <c r="M605" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N605" t="inlineStr"/>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P605" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01DETORL-DETCCUNNINGHAM2-9</t>
+          <t>KXNBAREB-26MAY01DETORL-DETCCUNNINGHAM2-8</t>
         </is>
       </c>
     </row>
@@ -38260,11 +38400,11 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D606" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E606" t="inlineStr">
         <is>
@@ -38272,34 +38412,42 @@
         </is>
       </c>
       <c r="F606" t="n">
-        <v>11.2</v>
+        <v>58.9</v>
       </c>
       <c r="G606" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H606" t="n">
-        <v>-2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J606" t="n">
         <v>0</v>
       </c>
       <c r="K606" t="n">
-        <v>14</v>
-      </c>
-      <c r="M606" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>60</v>
+      </c>
+      <c r="L606" t="n">
+        <v>3</v>
+      </c>
+      <c r="M606" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N606" t="inlineStr"/>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P606" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-DETCCUNNINGHAM2-40</t>
+          <t>KXNBAAST-26MAY01DETORL-DETCCUNNINGHAM2-9</t>
         </is>
       </c>
     </row>
@@ -38316,11 +38464,11 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D607" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E607" t="inlineStr">
         <is>
@@ -38328,34 +38476,42 @@
         </is>
       </c>
       <c r="F607" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="G607" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H607" t="n">
-        <v>-7.2</v>
+        <v>-2.9</v>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J607" t="n">
         <v>0</v>
       </c>
       <c r="K607" t="n">
-        <v>16</v>
-      </c>
-      <c r="M607" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>14</v>
+      </c>
+      <c r="L607" t="n">
+        <v>32</v>
+      </c>
+      <c r="M607" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N607" t="inlineStr"/>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P607" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01DETORL-DETCCUNNINGHAM2-3</t>
+          <t>KXNBAPTS-26MAY01DETORL-DETCCUNNINGHAM2-40</t>
         </is>
       </c>
     </row>
@@ -38367,12 +38523,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D608" t="n">
@@ -38384,13 +38540,13 @@
         </is>
       </c>
       <c r="F608" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G608" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H608" t="n">
-        <v>-1.5</v>
+        <v>-7.2</v>
       </c>
       <c r="I608" t="inlineStr">
         <is>
@@ -38401,17 +38557,25 @@
         <v>0</v>
       </c>
       <c r="K608" t="n">
-        <v>13</v>
-      </c>
-      <c r="M608" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>16</v>
+      </c>
+      <c r="L608" t="n">
+        <v>4</v>
+      </c>
+      <c r="M608" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N608" t="inlineStr"/>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P608" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY01LALHOU-LALDAYTON5-3</t>
+          <t>KXNBASTL-26MAY01DETORL-DETCCUNNINGHAM2-3</t>
         </is>
       </c>
     </row>
@@ -38428,11 +38592,11 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D609" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E609" t="inlineStr">
         <is>
@@ -38440,13 +38604,13 @@
         </is>
       </c>
       <c r="F609" t="n">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="G609" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H609" t="n">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="I609" t="inlineStr">
         <is>
@@ -38457,17 +38621,25 @@
         <v>0</v>
       </c>
       <c r="K609" t="n">
-        <v>5</v>
-      </c>
-      <c r="M609" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>13</v>
+      </c>
+      <c r="L609" t="n">
+        <v>1</v>
+      </c>
+      <c r="M609" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N609" t="inlineStr"/>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P609" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-LALDAYTON5-25</t>
+          <t>KXNBABLK-26MAY01LALHOU-LALDAYTON5-3</t>
         </is>
       </c>
     </row>
@@ -38484,11 +38656,11 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D610" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E610" t="inlineStr">
         <is>
@@ -38496,34 +38668,42 @@
         </is>
       </c>
       <c r="F610" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="G610" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="H610" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J610" t="n">
         <v>0</v>
       </c>
       <c r="K610" t="n">
-        <v>53</v>
-      </c>
-      <c r="M610" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L610" t="n">
+        <v>7</v>
+      </c>
+      <c r="M610" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N610" t="inlineStr"/>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P610" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01LALHOU-LALDAYTON5-9</t>
+          <t>KXNBAPTS-26MAY01LALHOU-LALDAYTON5-25</t>
         </is>
       </c>
     </row>
@@ -38535,16 +38715,16 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D611" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E611" t="inlineStr">
         <is>
@@ -38552,34 +38732,42 @@
         </is>
       </c>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="G611" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="H611" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J611" t="n">
         <v>0</v>
       </c>
       <c r="K611" t="n">
-        <v>5</v>
-      </c>
-      <c r="M611" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>53</v>
+      </c>
+      <c r="L611" t="n">
+        <v>16</v>
+      </c>
+      <c r="M611" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N611" t="inlineStr"/>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P611" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-CLEDSCHRODER8-20</t>
+          <t>KXNBAREB-26MAY01LALHOU-LALDAYTON5-9</t>
         </is>
       </c>
     </row>
@@ -38596,11 +38784,11 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D612" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E612" t="inlineStr">
         <is>
@@ -38618,7 +38806,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J612" t="n">
@@ -38627,15 +38815,23 @@
       <c r="K612" t="n">
         <v>5</v>
       </c>
-      <c r="M612" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L612" t="n">
+        <v>7</v>
+      </c>
+      <c r="M612" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N612" t="inlineStr"/>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P612" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01CLETOR-CLEDSCHRODER8-10</t>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEDSCHRODER8-20</t>
         </is>
       </c>
     </row>
@@ -38647,16 +38843,16 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D613" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E613" t="inlineStr">
         <is>
@@ -38664,13 +38860,13 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="G613" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H613" t="n">
-        <v>-3.4</v>
+        <v>-2</v>
       </c>
       <c r="I613" t="inlineStr">
         <is>
@@ -38681,17 +38877,25 @@
         <v>0</v>
       </c>
       <c r="K613" t="n">
-        <v>11</v>
-      </c>
-      <c r="M613" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L613" t="n">
+        <v>1</v>
+      </c>
+      <c r="M613" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N613" t="inlineStr"/>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P613" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-ORLDBANE3-30</t>
+          <t>KXNBAAST-26MAY01CLETOR-CLEDSCHRODER8-10</t>
         </is>
       </c>
     </row>
@@ -38703,16 +38907,16 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D614" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E614" t="inlineStr">
         <is>
@@ -38720,13 +38924,13 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>10.3</v>
+        <v>7.6</v>
       </c>
       <c r="G614" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H614" t="n">
-        <v>-1.7</v>
+        <v>-3.4</v>
       </c>
       <c r="I614" t="inlineStr">
         <is>
@@ -38737,17 +38941,25 @@
         <v>0</v>
       </c>
       <c r="K614" t="n">
-        <v>12</v>
-      </c>
-      <c r="M614" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>11</v>
+      </c>
+      <c r="L614" t="n">
+        <v>17</v>
+      </c>
+      <c r="M614" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N614" t="inlineStr"/>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P614" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01CLETOR-CLEDMITCHELL45-8</t>
+          <t>KXNBAPTS-26MAY01DETORL-ORLDBANE3-30</t>
         </is>
       </c>
     </row>
@@ -38764,7 +38976,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D615" t="n">
@@ -38776,13 +38988,13 @@
         </is>
       </c>
       <c r="F615" t="n">
-        <v>6.4</v>
+        <v>10.3</v>
       </c>
       <c r="G615" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H615" t="n">
-        <v>-3.6</v>
+        <v>-1.7</v>
       </c>
       <c r="I615" t="inlineStr">
         <is>
@@ -38793,17 +39005,25 @@
         <v>0</v>
       </c>
       <c r="K615" t="n">
-        <v>10</v>
-      </c>
-      <c r="M615" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>12</v>
+      </c>
+      <c r="L615" t="n">
+        <v>2</v>
+      </c>
+      <c r="M615" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N615" t="inlineStr"/>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P615" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01CLETOR-CLEDMITCHELL45-8</t>
+          <t>KXNBAAST-26MAY01CLETOR-CLEDMITCHELL45-8</t>
         </is>
       </c>
     </row>
@@ -38820,11 +39040,11 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D616" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
@@ -38832,34 +39052,42 @@
         </is>
       </c>
       <c r="F616" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="G616" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H616" t="n">
-        <v>-5</v>
+        <v>-3.6</v>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J616" t="n">
         <v>0</v>
       </c>
       <c r="K616" t="n">
-        <v>8</v>
-      </c>
-      <c r="M616" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>10</v>
+      </c>
+      <c r="L616" t="n">
+        <v>5</v>
+      </c>
+      <c r="M616" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N616" t="inlineStr"/>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P616" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-CLEDMITCHELL45-40</t>
+          <t>KXNBAREB-26MAY01CLETOR-CLEDMITCHELL45-8</t>
         </is>
       </c>
     </row>
@@ -38876,46 +39104,54 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D617" t="n">
+        <v>40</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F617" t="n">
         <v>3</v>
       </c>
-      <c r="E617" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F617" t="n">
-        <v>6.5</v>
-      </c>
       <c r="G617" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H617" t="n">
-        <v>-10.5</v>
+        <v>-5</v>
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J617" t="n">
         <v>0</v>
       </c>
       <c r="K617" t="n">
-        <v>17</v>
-      </c>
-      <c r="M617" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L617" t="n">
+        <v>24</v>
+      </c>
+      <c r="M617" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N617" t="inlineStr"/>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P617" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01CLETOR-CLEDMITCHELL45-3</t>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEDMITCHELL45-40</t>
         </is>
       </c>
     </row>
@@ -38927,16 +39163,16 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D618" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
@@ -38944,34 +39180,42 @@
         </is>
       </c>
       <c r="F618" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="G618" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H618" t="n">
-        <v>-4.7</v>
+        <v>-10.5</v>
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J618" t="n">
         <v>0</v>
       </c>
       <c r="K618" t="n">
-        <v>8</v>
-      </c>
-      <c r="M618" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>17</v>
+      </c>
+      <c r="L618" t="n">
+        <v>0</v>
+      </c>
+      <c r="M618" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N618" t="inlineStr"/>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P618" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-DETDROBINSON55-20</t>
+          <t>KXNBASTL-26MAY01CLETOR-CLEDMITCHELL45-3</t>
         </is>
       </c>
     </row>
@@ -38983,7 +39227,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -38992,7 +39236,7 @@
         </is>
       </c>
       <c r="D619" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
@@ -39000,34 +39244,42 @@
         </is>
       </c>
       <c r="F619" t="n">
-        <v>15.6</v>
+        <v>3.3</v>
       </c>
       <c r="G619" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H619" t="n">
-        <v>4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J619" t="n">
         <v>0</v>
       </c>
       <c r="K619" t="n">
-        <v>11</v>
-      </c>
-      <c r="M619" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L619" t="n">
+        <v>14</v>
+      </c>
+      <c r="M619" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N619" t="inlineStr"/>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P619" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-CLEEMOBLEY4-25</t>
+          <t>KXNBAPTS-26MAY01DETORL-DETDROBINSON55-20</t>
         </is>
       </c>
     </row>
@@ -39044,11 +39296,11 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D620" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
@@ -39056,34 +39308,42 @@
         </is>
       </c>
       <c r="F620" t="n">
-        <v>53.4</v>
+        <v>15.6</v>
       </c>
       <c r="G620" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="H620" t="n">
-        <v>-0.6</v>
+        <v>4.6</v>
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J620" t="n">
         <v>0</v>
       </c>
       <c r="K620" t="n">
-        <v>54</v>
-      </c>
-      <c r="M620" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>11</v>
+      </c>
+      <c r="L620" t="n">
+        <v>26</v>
+      </c>
+      <c r="M620" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N620" t="inlineStr"/>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P620" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01CLETOR-CLEEMOBLEY4-9</t>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEEMOBLEY4-25</t>
         </is>
       </c>
     </row>
@@ -39100,11 +39360,11 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D621" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E621" t="inlineStr">
         <is>
@@ -39112,34 +39372,42 @@
         </is>
       </c>
       <c r="F621" t="n">
-        <v>25.4</v>
+        <v>53.4</v>
       </c>
       <c r="G621" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="H621" t="n">
-        <v>-1.6</v>
+        <v>-0.6</v>
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J621" t="n">
         <v>0</v>
       </c>
       <c r="K621" t="n">
-        <v>27</v>
-      </c>
-      <c r="M621" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>54</v>
+      </c>
+      <c r="L621" t="n">
+        <v>14</v>
+      </c>
+      <c r="M621" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N621" t="inlineStr"/>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P621" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY01CLETOR-CLEEMOBLEY4-3</t>
+          <t>KXNBAREB-26MAY01CLETOR-CLEEMOBLEY4-9</t>
         </is>
       </c>
     </row>
@@ -39156,7 +39424,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D622" t="n">
@@ -39168,13 +39436,13 @@
         </is>
       </c>
       <c r="F622" t="n">
-        <v>3.2</v>
+        <v>25.4</v>
       </c>
       <c r="G622" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H622" t="n">
-        <v>-4.8</v>
+        <v>-1.6</v>
       </c>
       <c r="I622" t="inlineStr">
         <is>
@@ -39185,17 +39453,25 @@
         <v>0</v>
       </c>
       <c r="K622" t="n">
-        <v>8</v>
-      </c>
-      <c r="M622" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>27</v>
+      </c>
+      <c r="L622" t="n">
+        <v>0</v>
+      </c>
+      <c r="M622" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N622" t="inlineStr"/>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P622" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01CLETOR-CLEEMOBLEY4-3</t>
+          <t>KXNBABLK-26MAY01CLETOR-CLEEMOBLEY4-3</t>
         </is>
       </c>
     </row>
@@ -39207,16 +39483,16 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D623" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E623" t="inlineStr">
         <is>
@@ -39224,34 +39500,42 @@
         </is>
       </c>
       <c r="F623" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G623" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H623" t="n">
-        <v>-4</v>
+        <v>-4.8</v>
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J623" t="n">
         <v>0</v>
       </c>
       <c r="K623" t="n">
-        <v>7</v>
-      </c>
-      <c r="M623" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L623" t="n">
+        <v>1</v>
+      </c>
+      <c r="M623" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N623" t="inlineStr"/>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P623" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-HOUJSMITH10-30</t>
+          <t>KXNBASTL-26MAY01CLETOR-CLEEMOBLEY4-3</t>
         </is>
       </c>
     </row>
@@ -39268,11 +39552,11 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D624" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
@@ -39280,34 +39564,42 @@
         </is>
       </c>
       <c r="F624" t="n">
-        <v>35.9</v>
+        <v>3</v>
       </c>
       <c r="G624" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="H624" t="n">
-        <v>-11.1</v>
+        <v>-4</v>
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J624" t="n">
         <v>0</v>
       </c>
       <c r="K624" t="n">
-        <v>47</v>
-      </c>
-      <c r="M624" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>7</v>
+      </c>
+      <c r="L624" t="n">
+        <v>9</v>
+      </c>
+      <c r="M624" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N624" t="inlineStr"/>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P624" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01LALHOU-HOUJSMITH10-8</t>
+          <t>KXNBAPTS-26MAY01LALHOU-HOUJSMITH10-30</t>
         </is>
       </c>
     </row>
@@ -39319,7 +39611,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -39336,13 +39628,13 @@
         </is>
       </c>
       <c r="F625" t="n">
-        <v>25.1</v>
+        <v>35.9</v>
       </c>
       <c r="G625" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="H625" t="n">
-        <v>2.1</v>
+        <v>-11.1</v>
       </c>
       <c r="I625" t="inlineStr">
         <is>
@@ -39353,17 +39645,25 @@
         <v>0</v>
       </c>
       <c r="K625" t="n">
-        <v>23</v>
-      </c>
-      <c r="M625" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>47</v>
+      </c>
+      <c r="L625" t="n">
+        <v>12</v>
+      </c>
+      <c r="M625" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N625" t="inlineStr"/>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P625" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01CLETOR-TORJPOELTL19-8</t>
+          <t>KXNBAREB-26MAY01LALHOU-HOUJSMITH10-8</t>
         </is>
       </c>
     </row>
@@ -39380,7 +39680,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D626" t="n">
@@ -39392,34 +39692,42 @@
         </is>
       </c>
       <c r="F626" t="n">
-        <v>3</v>
+        <v>25.1</v>
       </c>
       <c r="G626" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H626" t="n">
-        <v>-2</v>
+        <v>2.1</v>
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J626" t="n">
         <v>0</v>
       </c>
       <c r="K626" t="n">
-        <v>5</v>
-      </c>
-      <c r="M626" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>23</v>
+      </c>
+      <c r="L626" t="n">
+        <v>4</v>
+      </c>
+      <c r="M626" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N626" t="inlineStr"/>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P626" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01CLETOR-TORJPOELTL19-8</t>
+          <t>KXNBAREB-26MAY01CLETOR-TORJPOELTL19-8</t>
         </is>
       </c>
     </row>
@@ -39436,11 +39744,11 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D627" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E627" t="inlineStr">
         <is>
@@ -39451,31 +39759,39 @@
         <v>3</v>
       </c>
       <c r="G627" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H627" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J627" t="n">
         <v>0</v>
       </c>
       <c r="K627" t="n">
-        <v>6</v>
-      </c>
-      <c r="M627" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L627" t="n">
+        <v>1</v>
+      </c>
+      <c r="M627" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N627" t="inlineStr"/>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P627" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-TORJPOELTL19-20</t>
+          <t>KXNBAAST-26MAY01CLETOR-TORJPOELTL19-8</t>
         </is>
       </c>
     </row>
@@ -39487,16 +39803,16 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D628" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E628" t="inlineStr">
         <is>
@@ -39504,34 +39820,42 @@
         </is>
       </c>
       <c r="F628" t="n">
-        <v>81.3</v>
+        <v>3</v>
       </c>
       <c r="G628" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="H628" t="n">
-        <v>13.4</v>
+        <v>-3</v>
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J628" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K628" t="n">
-        <v>68</v>
-      </c>
-      <c r="M628" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>6</v>
+      </c>
+      <c r="L628" t="n">
+        <v>2</v>
+      </c>
+      <c r="M628" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N628" t="inlineStr"/>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P628" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01DETORL-DETJDUREN0-8</t>
+          <t>KXNBAPTS-26MAY01CLETOR-TORJPOELTL19-20</t>
         </is>
       </c>
     </row>
@@ -39548,11 +39872,11 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D629" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E629" t="inlineStr">
         <is>
@@ -39560,34 +39884,44 @@
         </is>
       </c>
       <c r="F629" t="n">
-        <v>15.6</v>
+        <v>81.3</v>
       </c>
       <c r="G629" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="H629" t="n">
-        <v>9.6</v>
+        <v>13.4</v>
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J629" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K629" t="n">
-        <v>6</v>
-      </c>
-      <c r="M629" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N629" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="L629" t="n">
+        <v>9</v>
+      </c>
+      <c r="M629" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N629" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P629" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-DETJDUREN0-25</t>
+          <t>KXNBAREB-26MAY01DETORL-DETJDUREN0-8</t>
         </is>
       </c>
     </row>
@@ -39604,46 +39938,56 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D630" t="n">
+        <v>25</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F630" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G630" t="n">
+        <v>6</v>
+      </c>
+      <c r="H630" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J630" t="n">
+        <v>31</v>
+      </c>
+      <c r="K630" t="n">
+        <v>6</v>
+      </c>
+      <c r="L630" t="n">
         <v>8</v>
       </c>
-      <c r="E630" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F630" t="n">
-        <v>3</v>
-      </c>
-      <c r="G630" t="n">
-        <v>4</v>
-      </c>
-      <c r="H630" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I630" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J630" t="n">
-        <v>0</v>
-      </c>
-      <c r="K630" t="n">
-        <v>4</v>
-      </c>
-      <c r="M630" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N630" t="inlineStr"/>
+      <c r="M630" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N630" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P630" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01DETORL-DETJDUREN0-8</t>
+          <t>KXNBAPTS-26MAY01DETORL-DETJDUREN0-25</t>
         </is>
       </c>
     </row>
@@ -39660,25 +40004,25 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D631" t="n">
+        <v>8</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
         <v>3</v>
       </c>
-      <c r="E631" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F631" t="n">
-        <v>7.7</v>
-      </c>
       <c r="G631" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H631" t="n">
-        <v>-7.3</v>
+        <v>-1</v>
       </c>
       <c r="I631" t="inlineStr">
         <is>
@@ -39689,17 +40033,25 @@
         <v>0</v>
       </c>
       <c r="K631" t="n">
-        <v>15</v>
-      </c>
-      <c r="M631" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>4</v>
+      </c>
+      <c r="L631" t="n">
+        <v>1</v>
+      </c>
+      <c r="M631" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N631" t="inlineStr"/>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P631" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY01DETORL-DETJDUREN0-3</t>
+          <t>KXNBAAST-26MAY01DETORL-DETJDUREN0-8</t>
         </is>
       </c>
     </row>
@@ -39711,12 +40063,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D632" t="n">
@@ -39728,13 +40080,13 @@
         </is>
       </c>
       <c r="F632" t="n">
-        <v>27.8</v>
+        <v>7.7</v>
       </c>
       <c r="G632" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H632" t="n">
-        <v>0.8</v>
+        <v>-7.3</v>
       </c>
       <c r="I632" t="inlineStr">
         <is>
@@ -39745,17 +40097,25 @@
         <v>0</v>
       </c>
       <c r="K632" t="n">
-        <v>27</v>
-      </c>
-      <c r="M632" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>15</v>
+      </c>
+      <c r="L632" t="n">
+        <v>0</v>
+      </c>
+      <c r="M632" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N632" t="inlineStr"/>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P632" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01DETORL-ORLJSUGGS4-3</t>
+          <t>KXNBABLK-26MAY01DETORL-DETJDUREN0-3</t>
         </is>
       </c>
     </row>
@@ -39772,11 +40132,11 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D633" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
@@ -39784,34 +40144,42 @@
         </is>
       </c>
       <c r="F633" t="n">
-        <v>11.3</v>
+        <v>27.8</v>
       </c>
       <c r="G633" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H633" t="n">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J633" t="n">
         <v>0</v>
       </c>
       <c r="K633" t="n">
-        <v>12</v>
-      </c>
-      <c r="M633" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>27</v>
+      </c>
+      <c r="L633" t="n">
+        <v>1</v>
+      </c>
+      <c r="M633" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N633" t="inlineStr"/>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P633" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01DETORL-ORLJSUGGS4-8</t>
+          <t>KXNBASTL-26MAY01DETORL-ORLJSUGGS4-3</t>
         </is>
       </c>
     </row>
@@ -39828,7 +40196,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D634" t="n">
@@ -39840,34 +40208,42 @@
         </is>
       </c>
       <c r="F634" t="n">
-        <v>6.4</v>
+        <v>11.3</v>
       </c>
       <c r="G634" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H634" t="n">
-        <v>-2.6</v>
+        <v>-0.7</v>
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J634" t="n">
         <v>0</v>
       </c>
       <c r="K634" t="n">
-        <v>9</v>
-      </c>
-      <c r="M634" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>12</v>
+      </c>
+      <c r="L634" t="n">
+        <v>7</v>
+      </c>
+      <c r="M634" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N634" t="inlineStr"/>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P634" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01DETORL-ORLJSUGGS4-8</t>
+          <t>KXNBAAST-26MAY01DETORL-ORLJSUGGS4-8</t>
         </is>
       </c>
     </row>
@@ -39884,11 +40260,11 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D635" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
@@ -39896,34 +40272,42 @@
         </is>
       </c>
       <c r="F635" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="G635" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H635" t="n">
-        <v>-5</v>
+        <v>-2.6</v>
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J635" t="n">
         <v>0</v>
       </c>
       <c r="K635" t="n">
-        <v>8</v>
-      </c>
-      <c r="M635" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>9</v>
+      </c>
+      <c r="L635" t="n">
+        <v>7</v>
+      </c>
+      <c r="M635" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N635" t="inlineStr"/>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P635" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-ORLJSUGGS4-25</t>
+          <t>KXNBAREB-26MAY01DETORL-ORLJSUGGS4-8</t>
         </is>
       </c>
     </row>
@@ -39935,30 +40319,30 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D636" t="n">
+        <v>25</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F636" t="n">
+        <v>3</v>
+      </c>
+      <c r="G636" t="n">
         <v>8</v>
       </c>
-      <c r="E636" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F636" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="G636" t="n">
-        <v>14</v>
-      </c>
       <c r="H636" t="n">
-        <v>1.9</v>
+        <v>-5</v>
       </c>
       <c r="I636" t="inlineStr">
         <is>
@@ -39969,17 +40353,25 @@
         <v>0</v>
       </c>
       <c r="K636" t="n">
-        <v>14</v>
-      </c>
-      <c r="M636" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L636" t="n">
+        <v>7</v>
+      </c>
+      <c r="M636" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N636" t="inlineStr"/>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P636" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01CLETOR-CLEJHARDEN1-8</t>
+          <t>KXNBAPTS-26MAY01DETORL-ORLJSUGGS4-25</t>
         </is>
       </c>
     </row>
@@ -39996,7 +40388,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D637" t="n">
@@ -40008,34 +40400,42 @@
         </is>
       </c>
       <c r="F637" t="n">
-        <v>35</v>
+        <v>15.9</v>
       </c>
       <c r="G637" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H637" t="n">
-        <v>-7</v>
+        <v>1.9</v>
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J637" t="n">
         <v>0</v>
       </c>
       <c r="K637" t="n">
-        <v>42</v>
-      </c>
-      <c r="M637" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>14</v>
+      </c>
+      <c r="L637" t="n">
+        <v>9</v>
+      </c>
+      <c r="M637" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N637" t="inlineStr"/>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P637" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01CLETOR-CLEJHARDEN1-8</t>
+          <t>KXNBAREB-26MAY01CLETOR-CLEJHARDEN1-8</t>
         </is>
       </c>
     </row>
@@ -40052,11 +40452,11 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D638" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E638" t="inlineStr">
         <is>
@@ -40064,34 +40464,42 @@
         </is>
       </c>
       <c r="F638" t="n">
-        <v>9.4</v>
+        <v>35</v>
       </c>
       <c r="G638" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H638" t="n">
-        <v>-7.6</v>
+        <v>-7</v>
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J638" t="n">
         <v>0</v>
       </c>
       <c r="K638" t="n">
-        <v>17</v>
-      </c>
-      <c r="M638" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>42</v>
+      </c>
+      <c r="L638" t="n">
+        <v>9</v>
+      </c>
+      <c r="M638" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N638" t="inlineStr"/>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P638" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01CLETOR-CLEJHARDEN1-3</t>
+          <t>KXNBAAST-26MAY01CLETOR-CLEJHARDEN1-8</t>
         </is>
       </c>
     </row>
@@ -40108,11 +40516,11 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D639" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E639" t="inlineStr">
         <is>
@@ -40120,34 +40528,42 @@
         </is>
       </c>
       <c r="F639" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="G639" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H639" t="n">
-        <v>-9.1</v>
+        <v>-7.6</v>
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J639" t="n">
         <v>0</v>
       </c>
       <c r="K639" t="n">
-        <v>15</v>
-      </c>
-      <c r="M639" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>17</v>
+      </c>
+      <c r="L639" t="n">
+        <v>2</v>
+      </c>
+      <c r="M639" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N639" t="inlineStr"/>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P639" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-CLEJHARDEN1-30</t>
+          <t>KXNBASTL-26MAY01CLETOR-CLEJHARDEN1-3</t>
         </is>
       </c>
     </row>
@@ -40159,7 +40575,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -40168,7 +40584,7 @@
         </is>
       </c>
       <c r="D640" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E640" t="inlineStr">
         <is>
@@ -40176,34 +40592,42 @@
         </is>
       </c>
       <c r="F640" t="n">
-        <v>20.6</v>
+        <v>5.9</v>
       </c>
       <c r="G640" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H640" t="n">
-        <v>13.6</v>
+        <v>-9.1</v>
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J640" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K640" t="n">
-        <v>7</v>
-      </c>
-      <c r="M640" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>15</v>
+      </c>
+      <c r="L640" t="n">
+        <v>16</v>
+      </c>
+      <c r="M640" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N640" t="inlineStr"/>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P640" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-CLEJALLEN31-20</t>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEJHARDEN1-30</t>
         </is>
       </c>
     </row>
@@ -40220,11 +40644,11 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D641" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E641" t="inlineStr">
         <is>
@@ -40232,13 +40656,13 @@
         </is>
       </c>
       <c r="F641" t="n">
-        <v>61.4</v>
+        <v>20.6</v>
       </c>
       <c r="G641" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H641" t="n">
-        <v>9.4</v>
+        <v>13.6</v>
       </c>
       <c r="I641" t="inlineStr">
         <is>
@@ -40246,20 +40670,30 @@
         </is>
       </c>
       <c r="J641" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K641" t="n">
-        <v>52</v>
-      </c>
-      <c r="M641" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N641" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L641" t="n">
+        <v>14</v>
+      </c>
+      <c r="M641" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N641" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P641" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01CLETOR-CLEJALLEN31-8</t>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEJALLEN31-20</t>
         </is>
       </c>
     </row>
@@ -40276,11 +40710,11 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D642" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E642" t="inlineStr">
         <is>
@@ -40288,34 +40722,42 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>19.6</v>
+        <v>61.4</v>
       </c>
       <c r="G642" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H642" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J642" t="n">
         <v>0</v>
       </c>
       <c r="K642" t="n">
-        <v>16</v>
-      </c>
-      <c r="M642" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>52</v>
+      </c>
+      <c r="L642" t="n">
+        <v>7</v>
+      </c>
+      <c r="M642" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N642" t="inlineStr"/>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P642" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY01CLETOR-CLEJALLEN31-3</t>
+          <t>KXNBAREB-26MAY01CLETOR-CLEJALLEN31-8</t>
         </is>
       </c>
     </row>
@@ -40327,16 +40769,16 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D643" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E643" t="inlineStr">
         <is>
@@ -40344,13 +40786,13 @@
         </is>
       </c>
       <c r="F643" t="n">
-        <v>3.1</v>
+        <v>19.6</v>
       </c>
       <c r="G643" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H643" t="n">
-        <v>-1.9</v>
+        <v>3.6</v>
       </c>
       <c r="I643" t="inlineStr">
         <is>
@@ -40361,17 +40803,25 @@
         <v>0</v>
       </c>
       <c r="K643" t="n">
-        <v>5</v>
-      </c>
-      <c r="M643" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>16</v>
+      </c>
+      <c r="L643" t="n">
+        <v>2</v>
+      </c>
+      <c r="M643" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N643" t="inlineStr"/>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P643" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-CLEJTYSON20-20</t>
+          <t>KXNBABLK-26MAY01CLETOR-CLEJALLEN31-3</t>
         </is>
       </c>
     </row>
@@ -40383,7 +40833,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -40392,7 +40842,7 @@
         </is>
       </c>
       <c r="D644" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
@@ -40400,34 +40850,42 @@
         </is>
       </c>
       <c r="F644" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G644" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H644" t="n">
-        <v>-6</v>
+        <v>-1.9</v>
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J644" t="n">
         <v>0</v>
       </c>
       <c r="K644" t="n">
-        <v>9</v>
-      </c>
-      <c r="M644" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L644" t="n">
+        <v>5</v>
+      </c>
+      <c r="M644" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N644" t="inlineStr"/>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P644" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-LALLJAMES23-35</t>
+          <t>KXNBAPTS-26MAY01CLETOR-CLEJTYSON20-20</t>
         </is>
       </c>
     </row>
@@ -40444,46 +40902,54 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D645" t="n">
+        <v>35</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F645" t="n">
         <v>3</v>
       </c>
-      <c r="E645" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F645" t="n">
-        <v>3.2</v>
-      </c>
       <c r="G645" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H645" t="n">
-        <v>-14.8</v>
+        <v>-6</v>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J645" t="n">
         <v>0</v>
       </c>
       <c r="K645" t="n">
-        <v>18</v>
-      </c>
-      <c r="M645" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>9</v>
+      </c>
+      <c r="L645" t="n">
+        <v>28</v>
+      </c>
+      <c r="M645" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N645" t="inlineStr"/>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P645" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01LALHOU-LALLJAMES23-3</t>
+          <t>KXNBAPTS-26MAY01LALHOU-LALLJAMES23-35</t>
         </is>
       </c>
     </row>
@@ -40500,11 +40966,11 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D646" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E646" t="inlineStr">
         <is>
@@ -40512,34 +40978,42 @@
         </is>
       </c>
       <c r="F646" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="G646" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H646" t="n">
-        <v>-35.6</v>
+        <v>-14.8</v>
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J646" t="n">
         <v>0</v>
       </c>
       <c r="K646" t="n">
-        <v>42</v>
-      </c>
-      <c r="M646" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>18</v>
+      </c>
+      <c r="L646" t="n">
+        <v>0</v>
+      </c>
+      <c r="M646" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N646" t="inlineStr"/>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P646" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01LALHOU-LALLJAMES23-8</t>
+          <t>KXNBASTL-26MAY01LALHOU-LALLJAMES23-3</t>
         </is>
       </c>
     </row>
@@ -40556,7 +41030,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D647" t="n">
@@ -40568,13 +41042,13 @@
         </is>
       </c>
       <c r="F647" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="G647" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="H647" t="n">
-        <v>-53</v>
+        <v>-35.6</v>
       </c>
       <c r="I647" t="inlineStr">
         <is>
@@ -40585,17 +41059,25 @@
         <v>0</v>
       </c>
       <c r="K647" t="n">
-        <v>56</v>
-      </c>
-      <c r="M647" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>42</v>
+      </c>
+      <c r="L647" t="n">
+        <v>7</v>
+      </c>
+      <c r="M647" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N647" t="inlineStr"/>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P647" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01LALHOU-LALLJAMES23-8</t>
+          <t>KXNBAREB-26MAY01LALHOU-LALLJAMES23-8</t>
         </is>
       </c>
     </row>
@@ -40607,7 +41089,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -40624,34 +41106,42 @@
         </is>
       </c>
       <c r="F648" t="n">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="G648" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="H648" t="n">
-        <v>4.5</v>
+        <v>-53</v>
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J648" t="n">
         <v>0</v>
       </c>
       <c r="K648" t="n">
-        <v>7</v>
-      </c>
-      <c r="M648" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>56</v>
+      </c>
+      <c r="L648" t="n">
+        <v>8</v>
+      </c>
+      <c r="M648" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N648" t="inlineStr"/>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P648" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01LALHOU-LALMSMART36-8</t>
+          <t>KXNBAAST-26MAY01LALHOU-LALLJAMES23-8</t>
         </is>
       </c>
     </row>
@@ -40663,16 +41153,16 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D649" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
@@ -40680,13 +41170,13 @@
         </is>
       </c>
       <c r="F649" t="n">
-        <v>14.4</v>
+        <v>4.3</v>
       </c>
       <c r="G649" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H649" t="n">
-        <v>3.4</v>
+        <v>-43.7</v>
       </c>
       <c r="I649" t="inlineStr">
         <is>
@@ -40697,17 +41187,25 @@
         <v>0</v>
       </c>
       <c r="K649" t="n">
-        <v>11</v>
-      </c>
-      <c r="M649" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>48</v>
+      </c>
+      <c r="L649" t="n">
+        <v>0</v>
+      </c>
+      <c r="M649" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N649" t="inlineStr"/>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P649" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-LALMSMART36-20</t>
+          <t>KXNBABLK-26MAY01LALHOU-LALLJAMES23-2</t>
         </is>
       </c>
     </row>
@@ -40724,11 +41222,11 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D650" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
@@ -40736,13 +41234,13 @@
         </is>
       </c>
       <c r="F650" t="n">
-        <v>23.6</v>
+        <v>11.5</v>
       </c>
       <c r="G650" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H650" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="I650" t="inlineStr">
         <is>
@@ -40753,17 +41251,25 @@
         <v>0</v>
       </c>
       <c r="K650" t="n">
-        <v>23</v>
-      </c>
-      <c r="M650" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>7</v>
+      </c>
+      <c r="L650" t="n">
+        <v>1</v>
+      </c>
+      <c r="M650" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N650" t="inlineStr"/>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P650" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01LALHOU-LALMSMART36-3</t>
+          <t>KXNBAAST-26MAY01LALHOU-LALMSMART36-8</t>
         </is>
       </c>
     </row>
@@ -40775,16 +41281,16 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D651" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E651" t="inlineStr">
         <is>
@@ -40792,34 +41298,42 @@
         </is>
       </c>
       <c r="F651" t="n">
-        <v>67.2</v>
+        <v>14.4</v>
       </c>
       <c r="G651" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H651" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J651" t="n">
         <v>0</v>
       </c>
       <c r="K651" t="n">
-        <v>59</v>
-      </c>
-      <c r="M651" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>11</v>
+      </c>
+      <c r="L651" t="n">
+        <v>7</v>
+      </c>
+      <c r="M651" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N651" t="inlineStr"/>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P651" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01DETORL-ORLPBANCHERO5-8</t>
+          <t>KXNBAPTS-26MAY01LALHOU-LALMSMART36-20</t>
         </is>
       </c>
     </row>
@@ -40831,16 +41345,16 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D652" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
@@ -40848,34 +41362,42 @@
         </is>
       </c>
       <c r="F652" t="n">
-        <v>12.9</v>
+        <v>23.6</v>
       </c>
       <c r="G652" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H652" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J652" t="n">
         <v>0</v>
       </c>
       <c r="K652" t="n">
-        <v>9</v>
-      </c>
-      <c r="M652" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>23</v>
+      </c>
+      <c r="L652" t="n">
+        <v>2</v>
+      </c>
+      <c r="M652" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N652" t="inlineStr"/>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P652" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-ORLPBANCHERO5-35</t>
+          <t>KXNBASTL-26MAY01LALHOU-LALMSMART36-3</t>
         </is>
       </c>
     </row>
@@ -40892,7 +41414,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D653" t="n">
@@ -40904,13 +41426,13 @@
         </is>
       </c>
       <c r="F653" t="n">
-        <v>20.8</v>
+        <v>67.2</v>
       </c>
       <c r="G653" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="H653" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I653" t="inlineStr">
         <is>
@@ -40921,17 +41443,25 @@
         <v>0</v>
       </c>
       <c r="K653" t="n">
-        <v>19</v>
-      </c>
-      <c r="M653" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>59</v>
+      </c>
+      <c r="L653" t="n">
+        <v>10</v>
+      </c>
+      <c r="M653" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N653" t="inlineStr"/>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P653" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01DETORL-ORLPBANCHERO5-8</t>
+          <t>KXNBAREB-26MAY01DETORL-ORLPBANCHERO5-8</t>
         </is>
       </c>
     </row>
@@ -40948,11 +41478,11 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D654" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
@@ -40960,34 +41490,42 @@
         </is>
       </c>
       <c r="F654" t="n">
-        <v>4.3</v>
+        <v>12.9</v>
       </c>
       <c r="G654" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H654" t="n">
-        <v>-2.7</v>
+        <v>3.9</v>
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J654" t="n">
         <v>0</v>
       </c>
       <c r="K654" t="n">
-        <v>7</v>
-      </c>
-      <c r="M654" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>9</v>
+      </c>
+      <c r="L654" t="n">
+        <v>17</v>
+      </c>
+      <c r="M654" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N654" t="inlineStr"/>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P654" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY01DETORL-ORLPBANCHERO5-3</t>
+          <t>KXNBAPTS-26MAY01DETORL-ORLPBANCHERO5-35</t>
         </is>
       </c>
     </row>
@@ -41004,11 +41542,11 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D655" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E655" t="inlineStr">
         <is>
@@ -41016,34 +41554,42 @@
         </is>
       </c>
       <c r="F655" t="n">
-        <v>9.199999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="G655" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H655" t="n">
-        <v>-3.8</v>
+        <v>1.8</v>
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J655" t="n">
         <v>0</v>
       </c>
       <c r="K655" t="n">
-        <v>13</v>
-      </c>
-      <c r="M655" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>19</v>
+      </c>
+      <c r="L655" t="n">
+        <v>6</v>
+      </c>
+      <c r="M655" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N655" t="inlineStr"/>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P655" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01DETORL-ORLPBANCHERO5-3</t>
+          <t>KXNBAAST-26MAY01DETORL-ORLPBANCHERO5-8</t>
         </is>
       </c>
     </row>
@@ -41055,16 +41601,16 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D656" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E656" t="inlineStr">
         <is>
@@ -41072,13 +41618,13 @@
         </is>
       </c>
       <c r="F656" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="G656" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H656" t="n">
-        <v>-5.3</v>
+        <v>-2.7</v>
       </c>
       <c r="I656" t="inlineStr">
         <is>
@@ -41089,17 +41635,25 @@
         <v>0</v>
       </c>
       <c r="K656" t="n">
-        <v>11</v>
-      </c>
-      <c r="M656" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>7</v>
+      </c>
+      <c r="L656" t="n">
+        <v>0</v>
+      </c>
+      <c r="M656" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N656" t="inlineStr"/>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P656" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01LALHOU-HOURSHEPPARD15-8</t>
+          <t>KXNBABLK-26MAY01DETORL-ORLPBANCHERO5-3</t>
         </is>
       </c>
     </row>
@@ -41111,16 +41665,16 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D657" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E657" t="inlineStr">
         <is>
@@ -41128,34 +41682,42 @@
         </is>
       </c>
       <c r="F657" t="n">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G657" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H657" t="n">
-        <v>-11</v>
+        <v>-3.8</v>
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J657" t="n">
         <v>0</v>
       </c>
       <c r="K657" t="n">
-        <v>14</v>
-      </c>
-      <c r="M657" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>13</v>
+      </c>
+      <c r="L657" t="n">
+        <v>2</v>
+      </c>
+      <c r="M657" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N657" t="inlineStr"/>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P657" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-HOURSHEPPARD15-25</t>
+          <t>KXNBASTL-26MAY01DETORL-ORLPBANCHERO5-3</t>
         </is>
       </c>
     </row>
@@ -41167,12 +41729,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Rj Barrett</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D658" t="n">
@@ -41184,34 +41746,42 @@
         </is>
       </c>
       <c r="F658" t="n">
-        <v>30.8</v>
+        <v>5.7</v>
       </c>
       <c r="G658" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H658" t="n">
-        <v>2.8</v>
+        <v>-5.3</v>
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J658" t="n">
         <v>0</v>
       </c>
       <c r="K658" t="n">
-        <v>28</v>
-      </c>
-      <c r="M658" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>11</v>
+      </c>
+      <c r="L658" t="n">
+        <v>1</v>
+      </c>
+      <c r="M658" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N658" t="inlineStr"/>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P658" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01CLETOR-TORRBARRETT9-8</t>
+          <t>KXNBAAST-26MAY01LALHOU-HOURSHEPPARD15-8</t>
         </is>
       </c>
     </row>
@@ -41223,7 +41793,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Rj Barrett</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -41232,7 +41802,7 @@
         </is>
       </c>
       <c r="D659" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
@@ -41243,31 +41813,39 @@
         <v>3</v>
       </c>
       <c r="G659" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H659" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J659" t="n">
         <v>0</v>
       </c>
       <c r="K659" t="n">
-        <v>8</v>
-      </c>
-      <c r="M659" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>14</v>
+      </c>
+      <c r="L659" t="n">
+        <v>10</v>
+      </c>
+      <c r="M659" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N659" t="inlineStr"/>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P659" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-TORRBARRETT9-35</t>
+          <t>KXNBAPTS-26MAY01LALHOU-HOURSHEPPARD15-25</t>
         </is>
       </c>
     </row>
@@ -41284,7 +41862,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D660" t="n">
@@ -41296,13 +41874,13 @@
         </is>
       </c>
       <c r="F660" t="n">
-        <v>3</v>
+        <v>30.8</v>
       </c>
       <c r="G660" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H660" t="n">
-        <v>-5</v>
+        <v>2.8</v>
       </c>
       <c r="I660" t="inlineStr">
         <is>
@@ -41313,17 +41891,25 @@
         <v>0</v>
       </c>
       <c r="K660" t="n">
-        <v>8</v>
-      </c>
-      <c r="M660" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>28</v>
+      </c>
+      <c r="L660" t="n">
+        <v>9</v>
+      </c>
+      <c r="M660" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N660" t="inlineStr"/>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P660" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01CLETOR-TORRBARRETT9-8</t>
+          <t>KXNBAREB-26MAY01CLETOR-TORRBARRETT9-8</t>
         </is>
       </c>
     </row>
@@ -41340,46 +41926,54 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D661" t="n">
+        <v>35</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F661" t="n">
         <v>3</v>
       </c>
-      <c r="E661" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F661" t="n">
-        <v>3.2</v>
-      </c>
       <c r="G661" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H661" t="n">
-        <v>-5.8</v>
+        <v>-5</v>
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J661" t="n">
         <v>0</v>
       </c>
       <c r="K661" t="n">
-        <v>9</v>
-      </c>
-      <c r="M661" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L661" t="n">
+        <v>24</v>
+      </c>
+      <c r="M661" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N661" t="inlineStr"/>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P661" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01CLETOR-TORRBARRETT9-3</t>
+          <t>KXNBAPTS-26MAY01CLETOR-TORRBARRETT9-35</t>
         </is>
       </c>
     </row>
@@ -41391,16 +41985,16 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D662" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E662" t="inlineStr">
         <is>
@@ -41408,13 +42002,13 @@
         </is>
       </c>
       <c r="F662" t="n">
-        <v>15.2</v>
+        <v>3</v>
       </c>
       <c r="G662" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H662" t="n">
-        <v>1.2</v>
+        <v>-5</v>
       </c>
       <c r="I662" t="inlineStr">
         <is>
@@ -41425,17 +42019,25 @@
         <v>0</v>
       </c>
       <c r="K662" t="n">
-        <v>14</v>
-      </c>
-      <c r="M662" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L662" t="n">
+        <v>3</v>
+      </c>
+      <c r="M662" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N662" t="inlineStr"/>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P662" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-LALRHACHIMURA28-20</t>
+          <t>KXNBAAST-26MAY01CLETOR-TORRBARRETT9-8</t>
         </is>
       </c>
     </row>
@@ -41447,12 +42049,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D663" t="n">
@@ -41464,13 +42066,13 @@
         </is>
       </c>
       <c r="F663" t="n">
-        <v>23.5</v>
+        <v>3.2</v>
       </c>
       <c r="G663" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H663" t="n">
-        <v>7.5</v>
+        <v>-5.8</v>
       </c>
       <c r="I663" t="inlineStr">
         <is>
@@ -41481,17 +42083,25 @@
         <v>0</v>
       </c>
       <c r="K663" t="n">
-        <v>16</v>
-      </c>
-      <c r="M663" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>9</v>
+      </c>
+      <c r="L663" t="n">
+        <v>1</v>
+      </c>
+      <c r="M663" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N663" t="inlineStr"/>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P663" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY01CLETOR-TORSBARNES4-3</t>
+          <t>KXNBASTL-26MAY01CLETOR-TORRBARRETT9-3</t>
         </is>
       </c>
     </row>
@@ -41503,16 +42113,16 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D664" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E664" t="inlineStr">
         <is>
@@ -41520,34 +42130,42 @@
         </is>
       </c>
       <c r="F664" t="n">
-        <v>12.5</v>
+        <v>15.2</v>
       </c>
       <c r="G664" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H664" t="n">
-        <v>-6.5</v>
+        <v>1.2</v>
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J664" t="n">
         <v>0</v>
       </c>
       <c r="K664" t="n">
-        <v>19</v>
-      </c>
-      <c r="M664" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>14</v>
+      </c>
+      <c r="L664" t="n">
+        <v>21</v>
+      </c>
+      <c r="M664" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N664" t="inlineStr"/>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P664" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY01CLETOR-TORSBARNES4-3</t>
+          <t>KXNBAPTS-26MAY01LALHOU-LALRHACHIMURA28-20</t>
         </is>
       </c>
     </row>
@@ -41564,11 +42182,11 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D665" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E665" t="inlineStr">
         <is>
@@ -41576,34 +42194,42 @@
         </is>
       </c>
       <c r="F665" t="n">
-        <v>5.1</v>
+        <v>23.5</v>
       </c>
       <c r="G665" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H665" t="n">
-        <v>-8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J665" t="n">
         <v>0</v>
       </c>
       <c r="K665" t="n">
-        <v>14</v>
-      </c>
-      <c r="M665" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>16</v>
+      </c>
+      <c r="L665" t="n">
+        <v>3</v>
+      </c>
+      <c r="M665" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N665" t="inlineStr"/>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P665" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01CLETOR-TORSBARNES4-30</t>
+          <t>KXNBABLK-26MAY01CLETOR-TORSBARNES4-3</t>
         </is>
       </c>
     </row>
@@ -41620,11 +42246,11 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D666" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E666" t="inlineStr">
         <is>
@@ -41632,34 +42258,42 @@
         </is>
       </c>
       <c r="F666" t="n">
-        <v>34.7</v>
+        <v>12.5</v>
       </c>
       <c r="G666" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H666" t="n">
-        <v>-15.3</v>
+        <v>-6.5</v>
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J666" t="n">
         <v>0</v>
       </c>
       <c r="K666" t="n">
-        <v>50</v>
-      </c>
-      <c r="M666" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>19</v>
+      </c>
+      <c r="L666" t="n">
+        <v>3</v>
+      </c>
+      <c r="M666" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N666" t="inlineStr"/>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P666" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01CLETOR-TORSBARNES4-8</t>
+          <t>KXNBASTL-26MAY01CLETOR-TORSBARNES4-3</t>
         </is>
       </c>
     </row>
@@ -41676,11 +42310,11 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D667" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E667" t="inlineStr">
         <is>
@@ -41688,34 +42322,42 @@
         </is>
       </c>
       <c r="F667" t="n">
-        <v>40</v>
+        <v>5.1</v>
       </c>
       <c r="G667" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="H667" t="n">
-        <v>-18</v>
+        <v>-8.9</v>
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J667" t="n">
         <v>0</v>
       </c>
       <c r="K667" t="n">
-        <v>58</v>
-      </c>
-      <c r="M667" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>14</v>
+      </c>
+      <c r="L667" t="n">
+        <v>25</v>
+      </c>
+      <c r="M667" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N667" t="inlineStr"/>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P667" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01CLETOR-TORSBARNES4-8</t>
+          <t>KXNBAPTS-26MAY01CLETOR-TORSBARNES4-30</t>
         </is>
       </c>
     </row>
@@ -41727,7 +42369,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -41744,13 +42386,13 @@
         </is>
       </c>
       <c r="F668" t="n">
-        <v>54.8</v>
+        <v>34.7</v>
       </c>
       <c r="G668" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H668" t="n">
-        <v>10.8</v>
+        <v>-15.3</v>
       </c>
       <c r="I668" t="inlineStr">
         <is>
@@ -41758,20 +42400,28 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K668" t="n">
-        <v>44</v>
-      </c>
-      <c r="M668" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>50</v>
+      </c>
+      <c r="L668" t="n">
+        <v>7</v>
+      </c>
+      <c r="M668" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N668" t="inlineStr"/>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P668" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01LALHOU-HOUTEASON17-8</t>
+          <t>KXNBAREB-26MAY01CLETOR-TORSBARNES4-8</t>
         </is>
       </c>
     </row>
@@ -41783,16 +42433,16 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D669" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E669" t="inlineStr">
         <is>
@@ -41800,34 +42450,42 @@
         </is>
       </c>
       <c r="F669" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="G669" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="H669" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J669" t="n">
         <v>0</v>
       </c>
       <c r="K669" t="n">
-        <v>7</v>
-      </c>
-      <c r="M669" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>58</v>
+      </c>
+      <c r="L669" t="n">
+        <v>14</v>
+      </c>
+      <c r="M669" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N669" t="inlineStr"/>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P669" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01LALHOU-HOUTEASON17-25</t>
+          <t>KXNBAAST-26MAY01CLETOR-TORSBARNES4-8</t>
         </is>
       </c>
     </row>
@@ -41839,16 +42497,16 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D670" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E670" t="inlineStr">
         <is>
@@ -41856,13 +42514,13 @@
         </is>
       </c>
       <c r="F670" t="n">
-        <v>3</v>
+        <v>54.8</v>
       </c>
       <c r="G670" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="H670" t="n">
-        <v>-4</v>
+        <v>10.8</v>
       </c>
       <c r="I670" t="inlineStr">
         <is>
@@ -41870,20 +42528,30 @@
         </is>
       </c>
       <c r="J670" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K670" t="n">
-        <v>7</v>
-      </c>
-      <c r="M670" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N670" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="L670" t="n">
+        <v>5</v>
+      </c>
+      <c r="M670" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N670" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P670" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-DETTHARRIS12-30</t>
+          <t>KXNBAREB-26MAY01LALHOU-HOUTEASON17-8</t>
         </is>
       </c>
     </row>
@@ -41895,16 +42563,16 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D671" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E671" t="inlineStr">
         <is>
@@ -41931,15 +42599,23 @@
       <c r="K671" t="n">
         <v>7</v>
       </c>
-      <c r="M671" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L671" t="n">
+        <v>14</v>
+      </c>
+      <c r="M671" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N671" t="inlineStr"/>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P671" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY01DETORL-DETTHARRIS12-8</t>
+          <t>KXNBAPTS-26MAY01LALHOU-HOUTEASON17-25</t>
         </is>
       </c>
     </row>
@@ -41956,11 +42632,11 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D672" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E672" t="inlineStr">
         <is>
@@ -41968,13 +42644,13 @@
         </is>
       </c>
       <c r="F672" t="n">
-        <v>26.3</v>
+        <v>3</v>
       </c>
       <c r="G672" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H672" t="n">
-        <v>-7.7</v>
+        <v>-4</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -41985,17 +42661,25 @@
         <v>0</v>
       </c>
       <c r="K672" t="n">
-        <v>34</v>
-      </c>
-      <c r="M672" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>7</v>
+      </c>
+      <c r="L672" t="n">
+        <v>22</v>
+      </c>
+      <c r="M672" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N672" t="inlineStr"/>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P672" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY01DETORL-DETTHARRIS12-8</t>
+          <t>KXNBAPTS-26MAY01DETORL-DETTHARRIS12-30</t>
         </is>
       </c>
     </row>
@@ -42007,16 +42691,16 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D673" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E673" t="inlineStr">
         <is>
@@ -42027,31 +42711,39 @@
         <v>3</v>
       </c>
       <c r="G673" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H673" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J673" t="n">
         <v>0</v>
       </c>
       <c r="K673" t="n">
-        <v>9</v>
-      </c>
-      <c r="M673" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>7</v>
+      </c>
+      <c r="L673" t="n">
+        <v>0</v>
+      </c>
+      <c r="M673" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N673" t="inlineStr"/>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="P673" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY01DETORL-ORLWCARTER34-20</t>
+          <t>KXNBAAST-26MAY01DETORL-DETTHARRIS12-8</t>
         </is>
       </c>
     </row>
@@ -42063,7 +42755,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -42080,32 +42772,168 @@
         </is>
       </c>
       <c r="F674" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G674" t="n">
+        <v>34</v>
+      </c>
+      <c r="H674" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J674" t="n">
+        <v>0</v>
+      </c>
+      <c r="K674" t="n">
+        <v>34</v>
+      </c>
+      <c r="L674" t="n">
+        <v>10</v>
+      </c>
+      <c r="M674" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr"/>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY01DETORL-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>20</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F675" t="n">
+        <v>3</v>
+      </c>
+      <c r="G675" t="n">
+        <v>9</v>
+      </c>
+      <c r="H675" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J675" t="n">
+        <v>0</v>
+      </c>
+      <c r="K675" t="n">
+        <v>9</v>
+      </c>
+      <c r="L675" t="n">
+        <v>9</v>
+      </c>
+      <c r="M675" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr"/>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY01DETORL-ORLWCARTER34-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>8</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F676" t="n">
         <v>38.1</v>
       </c>
-      <c r="G674" t="n">
+      <c r="G676" t="n">
         <v>57</v>
       </c>
-      <c r="H674" t="n">
+      <c r="H676" t="n">
         <v>-18.9</v>
       </c>
-      <c r="I674" t="inlineStr">
+      <c r="I676" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="J674" t="n">
-        <v>0</v>
-      </c>
-      <c r="K674" t="n">
+      <c r="J676" t="n">
+        <v>0</v>
+      </c>
+      <c r="K676" t="n">
         <v>57</v>
       </c>
-      <c r="M674" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N674" t="inlineStr"/>
-      <c r="P674" t="inlineStr">
+      <c r="L676" t="n">
+        <v>0</v>
+      </c>
+      <c r="M676" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr"/>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY01DETORL-ORLWCARTER34-8</t>
         </is>
@@ -42465,25 +43293,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.06</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -42546,13 +43378,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -42568,19 +43400,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.294</v>
+        <v>0.318</v>
       </c>
       <c r="F3" t="n">
-        <v>9.01</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="4">
@@ -42615,13 +43447,13 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -42637,13 +43469,13 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.308</v>
+        <v>0.278</v>
       </c>
       <c r="F6" t="n">
         <v>-4.29</v>
@@ -42769,13 +43601,13 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="F12" t="n">
         <v>-2.38</v>
@@ -42794,10 +43626,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0.083</v>
+        <v>0.062</v>
       </c>
       <c r="F13" t="n">
         <v>-0.58</v>
@@ -42813,13 +43645,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.312</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -42835,13 +43667,13 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -42857,13 +43689,13 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -42879,13 +43711,13 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.091</v>
+        <v>0.143</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -42948,10 +43780,10 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -43014,7 +43846,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -43033,13 +43865,13 @@
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -43055,10 +43887,10 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
         <v>0.25</v>
@@ -43099,13 +43931,13 @@
         <v>11</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>0.429</v>
+        <v>0.455</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -43124,13 +43956,13 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="F28" t="n">
-        <v>16.95</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="29">
@@ -43143,13 +43975,13 @@
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -43168,7 +44000,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -43300,13 +44132,13 @@
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>0.333</v>
+        <v>0.222</v>
       </c>
       <c r="F36" t="n">
-        <v>-4.76</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="37">
@@ -43322,10 +44154,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>0.167</v>
+        <v>0.111</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -43366,7 +44198,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -43432,10 +44264,10 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -43603,13 +44435,13 @@
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -43694,7 +44526,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -43716,7 +44548,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -43758,7 +44590,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -43802,7 +44634,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -43821,14 +44653,16 @@
         <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="61">
@@ -44294,9 +45128,11 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
@@ -44507,13 +45343,13 @@
         <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E2" t="n">
-        <v>0.122</v>
+        <v>0.128</v>
       </c>
       <c r="F2" t="n">
         <v>-11.75</v>
@@ -44526,16 +45362,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>0.143</v>
+        <v>0.159</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -44551,16 +45387,16 @@
         <v>258</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="E4" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>3.94</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="5">
@@ -44573,16 +45409,16 @@
         <v>162</v>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E5" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="F5" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -44595,16 +45431,16 @@
         <v>86</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2</v>
+        <v>-1.88</v>
       </c>
     </row>
   </sheetData>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P676"/>
+  <dimension ref="A1:P715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42939,6 +42945,2190 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>8</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F677" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G677" t="n">
+        <v>6</v>
+      </c>
+      <c r="H677" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J677" t="n">
+        <v>0</v>
+      </c>
+      <c r="K677" t="n">
+        <v>6</v>
+      </c>
+      <c r="M677" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr"/>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-BOSDWHITE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>20</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F678" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G678" t="n">
+        <v>10</v>
+      </c>
+      <c r="H678" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J678" t="n">
+        <v>0</v>
+      </c>
+      <c r="K678" t="n">
+        <v>10</v>
+      </c>
+      <c r="M678" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr"/>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSDWHITE9-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Derrick White</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>3</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F679" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G679" t="n">
+        <v>21</v>
+      </c>
+      <c r="H679" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J679" t="n">
+        <v>0</v>
+      </c>
+      <c r="K679" t="n">
+        <v>21</v>
+      </c>
+      <c r="M679" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr"/>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-BOSDWHITE9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>8</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F680" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G680" t="n">
+        <v>8</v>
+      </c>
+      <c r="H680" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J680" t="n">
+        <v>0</v>
+      </c>
+      <c r="K680" t="n">
+        <v>8</v>
+      </c>
+      <c r="M680" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr"/>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-BOSJBROWN7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>35</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F681" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G681" t="n">
+        <v>14</v>
+      </c>
+      <c r="H681" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J681" t="n">
+        <v>0</v>
+      </c>
+      <c r="K681" t="n">
+        <v>14</v>
+      </c>
+      <c r="M681" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr"/>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSJBROWN7-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>8</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F682" t="n">
+        <v>28</v>
+      </c>
+      <c r="G682" t="n">
+        <v>29</v>
+      </c>
+      <c r="H682" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J682" t="n">
+        <v>0</v>
+      </c>
+      <c r="K682" t="n">
+        <v>29</v>
+      </c>
+      <c r="M682" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr"/>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-BOSJBROWN7-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Jaylen Brown</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>3</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F683" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G683" t="n">
+        <v>12</v>
+      </c>
+      <c r="H683" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J683" t="n">
+        <v>0</v>
+      </c>
+      <c r="K683" t="n">
+        <v>12</v>
+      </c>
+      <c r="M683" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr"/>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-BOSJBROWN7-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>8</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F684" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="G684" t="n">
+        <v>25</v>
+      </c>
+      <c r="H684" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J684" t="n">
+        <v>0</v>
+      </c>
+      <c r="K684" t="n">
+        <v>25</v>
+      </c>
+      <c r="M684" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr"/>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-BOSJTATUM0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>16</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F685" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G685" t="n">
+        <v>10</v>
+      </c>
+      <c r="H685" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J685" t="n">
+        <v>0</v>
+      </c>
+      <c r="K685" t="n">
+        <v>10</v>
+      </c>
+      <c r="M685" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr"/>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-BOSJTATUM0-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>3</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F686" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G686" t="n">
+        <v>14</v>
+      </c>
+      <c r="H686" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J686" t="n">
+        <v>0</v>
+      </c>
+      <c r="K686" t="n">
+        <v>14</v>
+      </c>
+      <c r="M686" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr"/>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-BOSJTATUM0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Jayson Tatum</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>35</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>3</v>
+      </c>
+      <c r="G687" t="n">
+        <v>11</v>
+      </c>
+      <c r="H687" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J687" t="n">
+        <v>0</v>
+      </c>
+      <c r="K687" t="n">
+        <v>11</v>
+      </c>
+      <c r="M687" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr"/>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSJTATUM0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>9</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F688" t="n">
+        <v>56</v>
+      </c>
+      <c r="G688" t="n">
+        <v>47</v>
+      </c>
+      <c r="H688" t="n">
+        <v>9</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J688" t="n">
+        <v>0</v>
+      </c>
+      <c r="K688" t="n">
+        <v>47</v>
+      </c>
+      <c r="M688" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr"/>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-PHIJEMBIID21-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>3</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F689" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="G689" t="n">
+        <v>14</v>
+      </c>
+      <c r="H689" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J689" t="n">
+        <v>0</v>
+      </c>
+      <c r="K689" t="n">
+        <v>14</v>
+      </c>
+      <c r="M689" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr"/>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY02PHIBOS-PHIJEMBIID21-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>35</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G690" t="n">
+        <v>18</v>
+      </c>
+      <c r="H690" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J690" t="n">
+        <v>0</v>
+      </c>
+      <c r="K690" t="n">
+        <v>18</v>
+      </c>
+      <c r="M690" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr"/>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHIJEMBIID21-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>3</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F691" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G691" t="n">
+        <v>14</v>
+      </c>
+      <c r="H691" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J691" t="n">
+        <v>0</v>
+      </c>
+      <c r="K691" t="n">
+        <v>14</v>
+      </c>
+      <c r="M691" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr"/>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-PHIJEMBIID21-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>8</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F692" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G692" t="n">
+        <v>19</v>
+      </c>
+      <c r="H692" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J692" t="n">
+        <v>0</v>
+      </c>
+      <c r="K692" t="n">
+        <v>19</v>
+      </c>
+      <c r="M692" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr"/>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-PHIKOUBRE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>3</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F693" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G693" t="n">
+        <v>15</v>
+      </c>
+      <c r="H693" t="n">
+        <v>3</v>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J693" t="n">
+        <v>0</v>
+      </c>
+      <c r="K693" t="n">
+        <v>15</v>
+      </c>
+      <c r="M693" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr"/>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-PHIKOUBRE9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>25</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F694" t="n">
+        <v>3</v>
+      </c>
+      <c r="G694" t="n">
+        <v>5</v>
+      </c>
+      <c r="H694" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J694" t="n">
+        <v>0</v>
+      </c>
+      <c r="K694" t="n">
+        <v>5</v>
+      </c>
+      <c r="M694" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr"/>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHIKOUBRE9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>8</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F695" t="n">
+        <v>3</v>
+      </c>
+      <c r="G695" t="n">
+        <v>5</v>
+      </c>
+      <c r="H695" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J695" t="n">
+        <v>0</v>
+      </c>
+      <c r="K695" t="n">
+        <v>5</v>
+      </c>
+      <c r="M695" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr"/>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-PHIKOUBRE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>8</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F696" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G696" t="n">
+        <v>49</v>
+      </c>
+      <c r="H696" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J696" t="n">
+        <v>13</v>
+      </c>
+      <c r="K696" t="n">
+        <v>49</v>
+      </c>
+      <c r="M696" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr"/>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-BOSNQUETA88-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>3</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F697" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="G697" t="n">
+        <v>13</v>
+      </c>
+      <c r="H697" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J697" t="n">
+        <v>0</v>
+      </c>
+      <c r="K697" t="n">
+        <v>13</v>
+      </c>
+      <c r="M697" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr"/>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY02PHIBOS-BOSNQUETA88-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Neemias Queta</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>20</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F698" t="n">
+        <v>3</v>
+      </c>
+      <c r="G698" t="n">
+        <v>6</v>
+      </c>
+      <c r="H698" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J698" t="n">
+        <v>0</v>
+      </c>
+      <c r="K698" t="n">
+        <v>6</v>
+      </c>
+      <c r="M698" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr"/>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSNQUETA88-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>8</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F699" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G699" t="n">
+        <v>15</v>
+      </c>
+      <c r="H699" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J699" t="n">
+        <v>16</v>
+      </c>
+      <c r="K699" t="n">
+        <v>15</v>
+      </c>
+      <c r="M699" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr"/>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-BOSNVUCEVIC4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Nikola Vucevic</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>20</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F700" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G700" t="n">
+        <v>5</v>
+      </c>
+      <c r="H700" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J700" t="n">
+        <v>0</v>
+      </c>
+      <c r="K700" t="n">
+        <v>5</v>
+      </c>
+      <c r="M700" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr"/>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSNVUCEVIC4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>8</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F701" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G701" t="n">
+        <v>19</v>
+      </c>
+      <c r="H701" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J701" t="n">
+        <v>0</v>
+      </c>
+      <c r="K701" t="n">
+        <v>19</v>
+      </c>
+      <c r="M701" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr"/>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>8</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F702" t="n">
+        <v>3</v>
+      </c>
+      <c r="G702" t="n">
+        <v>4</v>
+      </c>
+      <c r="H702" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J702" t="n">
+        <v>0</v>
+      </c>
+      <c r="K702" t="n">
+        <v>4</v>
+      </c>
+      <c r="M702" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr"/>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>3</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G703" t="n">
+        <v>19</v>
+      </c>
+      <c r="H703" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J703" t="n">
+        <v>0</v>
+      </c>
+      <c r="K703" t="n">
+        <v>19</v>
+      </c>
+      <c r="M703" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr"/>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-PHIPGEORGE8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>25</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F704" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G704" t="n">
+        <v>13</v>
+      </c>
+      <c r="H704" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J704" t="n">
+        <v>0</v>
+      </c>
+      <c r="K704" t="n">
+        <v>13</v>
+      </c>
+      <c r="M704" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr"/>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHIPGEORGE8-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>25</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F705" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G705" t="n">
+        <v>9</v>
+      </c>
+      <c r="H705" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J705" t="n">
+        <v>26</v>
+      </c>
+      <c r="K705" t="n">
+        <v>9</v>
+      </c>
+      <c r="M705" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr"/>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSPPRITCHARD11-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>8</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G706" t="n">
+        <v>5</v>
+      </c>
+      <c r="H706" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J706" t="n">
+        <v>0</v>
+      </c>
+      <c r="K706" t="n">
+        <v>5</v>
+      </c>
+      <c r="M706" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr"/>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-BOSPPRITCHARD11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>8</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F707" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G707" t="n">
+        <v>9</v>
+      </c>
+      <c r="H707" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J707" t="n">
+        <v>0</v>
+      </c>
+      <c r="K707" t="n">
+        <v>9</v>
+      </c>
+      <c r="M707" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr"/>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-BOSPPRITCHARD11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Sam Hauser</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>20</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F708" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G708" t="n">
+        <v>6</v>
+      </c>
+      <c r="H708" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J708" t="n">
+        <v>0</v>
+      </c>
+      <c r="K708" t="n">
+        <v>6</v>
+      </c>
+      <c r="M708" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr"/>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSSHAUSER30-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>8</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F709" t="n">
+        <v>34</v>
+      </c>
+      <c r="G709" t="n">
+        <v>34</v>
+      </c>
+      <c r="H709" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J709" t="n">
+        <v>0</v>
+      </c>
+      <c r="K709" t="n">
+        <v>34</v>
+      </c>
+      <c r="M709" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr"/>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-PHITMAXEY0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>3</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F710" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G710" t="n">
+        <v>16</v>
+      </c>
+      <c r="H710" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J710" t="n">
+        <v>0</v>
+      </c>
+      <c r="K710" t="n">
+        <v>16</v>
+      </c>
+      <c r="M710" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr"/>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-PHITMAXEY0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>35</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F711" t="n">
+        <v>3</v>
+      </c>
+      <c r="G711" t="n">
+        <v>13</v>
+      </c>
+      <c r="H711" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J711" t="n">
+        <v>0</v>
+      </c>
+      <c r="K711" t="n">
+        <v>13</v>
+      </c>
+      <c r="M711" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr"/>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHITMAXEY0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>20</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F712" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G712" t="n">
+        <v>9</v>
+      </c>
+      <c r="H712" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J712" t="n">
+        <v>38</v>
+      </c>
+      <c r="K712" t="n">
+        <v>9</v>
+      </c>
+      <c r="M712" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr"/>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHIVEDGECOMBE77-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>8</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F713" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G713" t="n">
+        <v>28</v>
+      </c>
+      <c r="H713" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J713" t="n">
+        <v>13</v>
+      </c>
+      <c r="K713" t="n">
+        <v>28</v>
+      </c>
+      <c r="M713" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr"/>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>8</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F714" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G714" t="n">
+        <v>6</v>
+      </c>
+      <c r="H714" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J714" t="n">
+        <v>0</v>
+      </c>
+      <c r="K714" t="n">
+        <v>6</v>
+      </c>
+      <c r="M714" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr"/>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>3</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G715" t="n">
+        <v>12</v>
+      </c>
+      <c r="H715" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J715" t="n">
+        <v>0</v>
+      </c>
+      <c r="K715" t="n">
+        <v>12</v>
+      </c>
+      <c r="M715" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr"/>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY02PHIBOS-PHIVEDGECOMBE77-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42950,7 +45140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43316,6 +45506,33 @@
       <c r="I11" t="n">
         <v>-0.06</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>39</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43422,7 +45639,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -43440,86 +45657,86 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.278</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.08</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -43532,7 +45749,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -43550,73 +45767,73 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.067</v>
+        <v>0.312</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.133</v>
+        <v>0.278</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.38</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -43626,19 +45843,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.062</v>
+        <v>0.083</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -43654,48 +45871,48 @@
         <v>0.312</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
         <v>15</v>
       </c>
-      <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
       <c r="E15" t="n">
-        <v>0.533</v>
+        <v>0.062</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.312</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -43704,64 +45921,64 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.143</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.083</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -43770,20 +45987,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.25</v>
+        <v>0.143</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -43792,20 +46009,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -43814,23 +46031,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="F22" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -43902,42 +46119,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>11</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>11</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.455</v>
+        <v>0.273</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -43946,29 +46163,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0.25</v>
+        <v>0.455</v>
       </c>
       <c r="F28" t="n">
-        <v>13.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -43978,32 +46195,32 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -44012,7 +46229,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -44022,57 +46239,57 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F33" t="n">
-        <v>-7.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -44166,17 +46383,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -44188,7 +46405,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -44198,76 +46415,76 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jaden Mcdaniels</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.39</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -44276,20 +46493,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -44298,19 +46515,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
@@ -44318,7 +46537,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -44328,11 +46547,9 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -44340,7 +46557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -44362,7 +46579,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -44372,7 +46589,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -44384,33 +46601,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -44428,29 +46645,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -44460,41 +46677,41 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -45340,7 +47557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
@@ -45362,7 +47579,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -45384,7 +47601,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
@@ -45406,7 +47623,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C5" t="n">
         <v>48</v>
@@ -45428,7 +47645,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +55,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,14 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P715"/>
+  <dimension ref="A1:P717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42989,12 +42983,20 @@
       <c r="K677" t="n">
         <v>6</v>
       </c>
-      <c r="M677" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L677" t="n">
+        <v>4</v>
+      </c>
+      <c r="M677" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N677" t="inlineStr"/>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P677" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY02PHIBOS-BOSDWHITE9-8</t>
@@ -43045,12 +43047,20 @@
       <c r="K678" t="n">
         <v>10</v>
       </c>
-      <c r="M678" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L678" t="n">
+        <v>26</v>
+      </c>
+      <c r="M678" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N678" t="inlineStr"/>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P678" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY02PHIBOS-BOSDWHITE9-20</t>
@@ -43101,12 +43111,20 @@
       <c r="K679" t="n">
         <v>21</v>
       </c>
-      <c r="M679" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L679" t="n">
+        <v>0</v>
+      </c>
+      <c r="M679" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N679" t="inlineStr"/>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P679" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY02PHIBOS-BOSDWHITE9-3</t>
@@ -43157,12 +43175,20 @@
       <c r="K680" t="n">
         <v>8</v>
       </c>
-      <c r="M680" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L680" t="n">
+        <v>4</v>
+      </c>
+      <c r="M680" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N680" t="inlineStr"/>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P680" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY02PHIBOS-BOSJBROWN7-8</t>
@@ -43213,12 +43239,20 @@
       <c r="K681" t="n">
         <v>14</v>
       </c>
-      <c r="M681" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L681" t="n">
+        <v>33</v>
+      </c>
+      <c r="M681" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N681" t="inlineStr"/>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P681" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY02PHIBOS-BOSJBROWN7-35</t>
@@ -43269,12 +43303,20 @@
       <c r="K682" t="n">
         <v>29</v>
       </c>
-      <c r="M682" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L682" t="n">
+        <v>9</v>
+      </c>
+      <c r="M682" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N682" t="inlineStr"/>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P682" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY02PHIBOS-BOSJBROWN7-8</t>
@@ -43325,12 +43367,20 @@
       <c r="K683" t="n">
         <v>12</v>
       </c>
-      <c r="M683" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L683" t="n">
+        <v>0</v>
+      </c>
+      <c r="M683" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N683" t="inlineStr"/>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P683" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY02PHIBOS-BOSJBROWN7-3</t>
@@ -43381,9 +43431,9 @@
       <c r="K684" t="n">
         <v>25</v>
       </c>
-      <c r="M684" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N684" t="inlineStr"/>
@@ -43437,9 +43487,9 @@
       <c r="K685" t="n">
         <v>10</v>
       </c>
-      <c r="M685" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N685" t="inlineStr"/>
@@ -43493,9 +43543,9 @@
       <c r="K686" t="n">
         <v>14</v>
       </c>
-      <c r="M686" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N686" t="inlineStr"/>
@@ -43549,9 +43599,9 @@
       <c r="K687" t="n">
         <v>11</v>
       </c>
-      <c r="M687" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N687" t="inlineStr"/>
@@ -43605,12 +43655,20 @@
       <c r="K688" t="n">
         <v>47</v>
       </c>
-      <c r="M688" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L688" t="n">
+        <v>12</v>
+      </c>
+      <c r="M688" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N688" t="inlineStr"/>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P688" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY02PHIBOS-PHIJEMBIID21-9</t>
@@ -43661,12 +43719,20 @@
       <c r="K689" t="n">
         <v>14</v>
       </c>
-      <c r="M689" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L689" t="n">
+        <v>1</v>
+      </c>
+      <c r="M689" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N689" t="inlineStr"/>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P689" t="inlineStr">
         <is>
           <t>KXNBABLK-26MAY02PHIBOS-PHIJEMBIID21-3</t>
@@ -43717,12 +43783,20 @@
       <c r="K690" t="n">
         <v>18</v>
       </c>
-      <c r="M690" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L690" t="n">
+        <v>34</v>
+      </c>
+      <c r="M690" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N690" t="inlineStr"/>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P690" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY02PHIBOS-PHIJEMBIID21-35</t>
@@ -43773,12 +43847,20 @@
       <c r="K691" t="n">
         <v>14</v>
       </c>
-      <c r="M691" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L691" t="n">
+        <v>0</v>
+      </c>
+      <c r="M691" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N691" t="inlineStr"/>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P691" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY02PHIBOS-PHIJEMBIID21-3</t>
@@ -43829,12 +43911,20 @@
       <c r="K692" t="n">
         <v>19</v>
       </c>
-      <c r="M692" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L692" t="n">
+        <v>5</v>
+      </c>
+      <c r="M692" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N692" t="inlineStr"/>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P692" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY02PHIBOS-PHIKOUBRE9-8</t>
@@ -43885,12 +43975,20 @@
       <c r="K693" t="n">
         <v>15</v>
       </c>
-      <c r="M693" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L693" t="n">
+        <v>0</v>
+      </c>
+      <c r="M693" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N693" t="inlineStr"/>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P693" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY02PHIBOS-PHIKOUBRE9-3</t>
@@ -43941,12 +44039,20 @@
       <c r="K694" t="n">
         <v>5</v>
       </c>
-      <c r="M694" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L694" t="n">
+        <v>6</v>
+      </c>
+      <c r="M694" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N694" t="inlineStr"/>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P694" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY02PHIBOS-PHIKOUBRE9-25</t>
@@ -43997,12 +44103,20 @@
       <c r="K695" t="n">
         <v>5</v>
       </c>
-      <c r="M695" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L695" t="n">
+        <v>2</v>
+      </c>
+      <c r="M695" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N695" t="inlineStr"/>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P695" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY02PHIBOS-PHIKOUBRE9-8</t>
@@ -44053,12 +44167,22 @@
       <c r="K696" t="n">
         <v>49</v>
       </c>
-      <c r="M696" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N696" t="inlineStr"/>
+      <c r="L696" t="n">
+        <v>12</v>
+      </c>
+      <c r="M696" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N696" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P696" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY02PHIBOS-BOSNQUETA88-8</t>
@@ -44109,12 +44233,20 @@
       <c r="K697" t="n">
         <v>13</v>
       </c>
-      <c r="M697" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L697" t="n">
+        <v>0</v>
+      </c>
+      <c r="M697" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N697" t="inlineStr"/>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P697" t="inlineStr">
         <is>
           <t>KXNBABLK-26MAY02PHIBOS-BOSNQUETA88-3</t>
@@ -44165,12 +44297,20 @@
       <c r="K698" t="n">
         <v>6</v>
       </c>
-      <c r="M698" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L698" t="n">
+        <v>17</v>
+      </c>
+      <c r="M698" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N698" t="inlineStr"/>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P698" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY02PHIBOS-BOSNQUETA88-20</t>
@@ -44221,9 +44361,9 @@
       <c r="K699" t="n">
         <v>15</v>
       </c>
-      <c r="M699" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N699" t="inlineStr"/>
@@ -44277,9 +44417,9 @@
       <c r="K700" t="n">
         <v>5</v>
       </c>
-      <c r="M700" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N700" t="inlineStr"/>
@@ -44297,16 +44437,16 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D701" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E701" t="inlineStr">
         <is>
@@ -44314,34 +44454,34 @@
         </is>
       </c>
       <c r="F701" t="n">
-        <v>23.3</v>
+        <v>8.1</v>
       </c>
       <c r="G701" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H701" t="n">
-        <v>4.3</v>
+        <v>-35.9</v>
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J701" t="n">
         <v>0</v>
       </c>
       <c r="K701" t="n">
-        <v>19</v>
-      </c>
-      <c r="M701" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>44</v>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N701" t="inlineStr"/>
       <c r="P701" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY02PHIBOS-PHIPGEORGE8-8</t>
+          <t>KXNBABLK-26MAY02PHIBOS-BOSNVUCEVIC4-3</t>
         </is>
       </c>
     </row>
@@ -44358,7 +44498,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D702" t="n">
@@ -44370,34 +44510,42 @@
         </is>
       </c>
       <c r="F702" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G702" t="n">
+        <v>19</v>
+      </c>
+      <c r="H702" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J702" t="n">
+        <v>0</v>
+      </c>
+      <c r="K702" t="n">
+        <v>19</v>
+      </c>
+      <c r="L702" t="n">
         <v>3</v>
       </c>
-      <c r="G702" t="n">
-        <v>4</v>
-      </c>
-      <c r="H702" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I702" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="J702" t="n">
-        <v>0</v>
-      </c>
-      <c r="K702" t="n">
-        <v>4</v>
-      </c>
-      <c r="M702" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M702" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N702" t="inlineStr"/>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P702" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY02PHIBOS-PHIPGEORGE8-8</t>
+          <t>KXNBAREB-26MAY02PHIBOS-PHIPGEORGE8-8</t>
         </is>
       </c>
     </row>
@@ -44414,46 +44562,54 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D703" t="n">
+        <v>8</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
         <v>3</v>
       </c>
-      <c r="E703" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F703" t="n">
-        <v>17.2</v>
-      </c>
       <c r="G703" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H703" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J703" t="n">
         <v>0</v>
       </c>
       <c r="K703" t="n">
-        <v>19</v>
-      </c>
-      <c r="M703" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>4</v>
+      </c>
+      <c r="L703" t="n">
+        <v>1</v>
+      </c>
+      <c r="M703" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N703" t="inlineStr"/>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P703" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY02PHIBOS-PHIPGEORGE8-3</t>
+          <t>KXNBAAST-26MAY02PHIBOS-PHIPGEORGE8-8</t>
         </is>
       </c>
     </row>
@@ -44470,11 +44626,11 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D704" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
@@ -44482,34 +44638,42 @@
         </is>
       </c>
       <c r="F704" t="n">
-        <v>9.9</v>
+        <v>17.2</v>
       </c>
       <c r="G704" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H704" t="n">
-        <v>-3.1</v>
+        <v>-1.8</v>
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J704" t="n">
         <v>0</v>
       </c>
       <c r="K704" t="n">
-        <v>13</v>
-      </c>
-      <c r="M704" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>19</v>
+      </c>
+      <c r="L704" t="n">
+        <v>0</v>
+      </c>
+      <c r="M704" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N704" t="inlineStr"/>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P704" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY02PHIBOS-PHIPGEORGE8-25</t>
+          <t>KXNBASTL-26MAY02PHIBOS-PHIPGEORGE8-3</t>
         </is>
       </c>
     </row>
@@ -44521,7 +44685,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -44538,13 +44702,13 @@
         </is>
       </c>
       <c r="F705" t="n">
-        <v>20.4</v>
+        <v>9.9</v>
       </c>
       <c r="G705" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H705" t="n">
-        <v>11.4</v>
+        <v>-3.1</v>
       </c>
       <c r="I705" t="inlineStr">
         <is>
@@ -44552,20 +44716,28 @@
         </is>
       </c>
       <c r="J705" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K705" t="n">
-        <v>9</v>
-      </c>
-      <c r="M705" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>13</v>
+      </c>
+      <c r="L705" t="n">
+        <v>13</v>
+      </c>
+      <c r="M705" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N705" t="inlineStr"/>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P705" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY02PHIBOS-BOSPPRITCHARD11-25</t>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHIPGEORGE8-25</t>
         </is>
       </c>
     </row>
@@ -44582,11 +44754,11 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D706" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
@@ -44594,13 +44766,13 @@
         </is>
       </c>
       <c r="F706" t="n">
-        <v>10.8</v>
+        <v>20.4</v>
       </c>
       <c r="G706" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H706" t="n">
-        <v>5.9</v>
+        <v>11.4</v>
       </c>
       <c r="I706" t="inlineStr">
         <is>
@@ -44608,20 +44780,30 @@
         </is>
       </c>
       <c r="J706" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K706" t="n">
-        <v>5</v>
-      </c>
-      <c r="M706" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N706" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L706" t="n">
+        <v>13</v>
+      </c>
+      <c r="M706" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N706" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P706" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY02PHIBOS-BOSPPRITCHARD11-8</t>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSPPRITCHARD11-25</t>
         </is>
       </c>
     </row>
@@ -44638,7 +44820,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D707" t="n">
@@ -44650,13 +44832,13 @@
         </is>
       </c>
       <c r="F707" t="n">
-        <v>7.1</v>
+        <v>10.8</v>
       </c>
       <c r="G707" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H707" t="n">
-        <v>-1.9</v>
+        <v>5.9</v>
       </c>
       <c r="I707" t="inlineStr">
         <is>
@@ -44667,17 +44849,25 @@
         <v>0</v>
       </c>
       <c r="K707" t="n">
-        <v>9</v>
-      </c>
-      <c r="M707" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L707" t="n">
+        <v>5</v>
+      </c>
+      <c r="M707" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N707" t="inlineStr"/>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P707" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY02PHIBOS-BOSPPRITCHARD11-8</t>
+          <t>KXNBAREB-26MAY02PHIBOS-BOSPPRITCHARD11-8</t>
         </is>
       </c>
     </row>
@@ -44689,16 +44879,16 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D708" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E708" t="inlineStr">
         <is>
@@ -44706,34 +44896,42 @@
         </is>
       </c>
       <c r="F708" t="n">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="G708" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H708" t="n">
-        <v>3.3</v>
+        <v>-1.9</v>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J708" t="n">
         <v>0</v>
       </c>
       <c r="K708" t="n">
-        <v>6</v>
-      </c>
-      <c r="M708" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>9</v>
+      </c>
+      <c r="L708" t="n">
+        <v>7</v>
+      </c>
+      <c r="M708" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N708" t="inlineStr"/>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P708" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY02PHIBOS-BOSSHAUSER30-20</t>
+          <t>KXNBAAST-26MAY02PHIBOS-BOSPPRITCHARD11-8</t>
         </is>
       </c>
     </row>
@@ -44745,16 +44943,16 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D709" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E709" t="inlineStr">
         <is>
@@ -44762,34 +44960,42 @@
         </is>
       </c>
       <c r="F709" t="n">
-        <v>34</v>
+        <v>3.8</v>
       </c>
       <c r="G709" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H709" t="n">
-        <v>-0</v>
+        <v>-6.2</v>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J709" t="n">
         <v>0</v>
       </c>
       <c r="K709" t="n">
-        <v>34</v>
-      </c>
-      <c r="M709" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>10</v>
+      </c>
+      <c r="L709" t="n">
+        <v>1</v>
+      </c>
+      <c r="M709" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N709" t="inlineStr"/>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P709" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY02PHIBOS-PHITMAXEY0-8</t>
+          <t>KXNBASTL-26MAY02PHIBOS-BOSPPRITCHARD11-3</t>
         </is>
       </c>
     </row>
@@ -44801,16 +45007,16 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D710" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
@@ -44818,13 +45024,13 @@
         </is>
       </c>
       <c r="F710" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G710" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H710" t="n">
-        <v>-8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="I710" t="inlineStr">
         <is>
@@ -44835,17 +45041,25 @@
         <v>0</v>
       </c>
       <c r="K710" t="n">
-        <v>16</v>
-      </c>
-      <c r="M710" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>6</v>
+      </c>
+      <c r="L710" t="n">
+        <v>11</v>
+      </c>
+      <c r="M710" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N710" t="inlineStr"/>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P710" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY02PHIBOS-PHITMAXEY0-3</t>
+          <t>KXNBAPTS-26MAY02PHIBOS-BOSSHAUSER30-20</t>
         </is>
       </c>
     </row>
@@ -44862,11 +45076,11 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D711" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
@@ -44874,34 +45088,42 @@
         </is>
       </c>
       <c r="F711" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="G711" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H711" t="n">
-        <v>-10</v>
+        <v>-0</v>
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J711" t="n">
         <v>0</v>
       </c>
       <c r="K711" t="n">
-        <v>13</v>
-      </c>
-      <c r="M711" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>34</v>
+      </c>
+      <c r="L711" t="n">
+        <v>7</v>
+      </c>
+      <c r="M711" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N711" t="inlineStr"/>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P711" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY02PHIBOS-PHITMAXEY0-35</t>
+          <t>KXNBAAST-26MAY02PHIBOS-PHITMAXEY0-8</t>
         </is>
       </c>
     </row>
@@ -44913,16 +45135,16 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D712" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E712" t="inlineStr">
         <is>
@@ -44930,34 +45152,42 @@
         </is>
       </c>
       <c r="F712" t="n">
-        <v>25.8</v>
+        <v>7.2</v>
       </c>
       <c r="G712" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H712" t="n">
-        <v>16.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J712" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K712" t="n">
-        <v>9</v>
-      </c>
-      <c r="M712" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>16</v>
+      </c>
+      <c r="L712" t="n">
+        <v>0</v>
+      </c>
+      <c r="M712" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N712" t="inlineStr"/>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P712" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY02PHIBOS-PHIVEDGECOMBE77-20</t>
+          <t>KXNBASTL-26MAY02PHIBOS-PHITMAXEY0-3</t>
         </is>
       </c>
     </row>
@@ -44969,16 +45199,16 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D713" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E713" t="inlineStr">
         <is>
@@ -44986,34 +45216,42 @@
         </is>
       </c>
       <c r="F713" t="n">
-        <v>42.8</v>
+        <v>3</v>
       </c>
       <c r="G713" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H713" t="n">
-        <v>14.8</v>
+        <v>-10</v>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J713" t="n">
+        <v>0</v>
+      </c>
+      <c r="K713" t="n">
         <v>13</v>
       </c>
-      <c r="K713" t="n">
-        <v>28</v>
-      </c>
-      <c r="M713" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L713" t="n">
+        <v>30</v>
+      </c>
+      <c r="M713" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N713" t="inlineStr"/>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P713" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY02PHIBOS-PHIVEDGECOMBE77-8</t>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHITMAXEY0-35</t>
         </is>
       </c>
     </row>
@@ -45030,11 +45268,11 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D714" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E714" t="inlineStr">
         <is>
@@ -45042,34 +45280,44 @@
         </is>
       </c>
       <c r="F714" t="n">
-        <v>11.8</v>
+        <v>25.8</v>
       </c>
       <c r="G714" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H714" t="n">
-        <v>5.8</v>
+        <v>16.8</v>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J714" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K714" t="n">
-        <v>6</v>
-      </c>
-      <c r="M714" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N714" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L714" t="n">
+        <v>23</v>
+      </c>
+      <c r="M714" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N714" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
       <c r="P714" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY02PHIBOS-PHIVEDGECOMBE77-8</t>
+          <t>KXNBAPTS-26MAY02PHIBOS-PHIVEDGECOMBE77-20</t>
         </is>
       </c>
     </row>
@@ -45086,44 +45334,182 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>8</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G715" t="n">
+        <v>28</v>
+      </c>
+      <c r="H715" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J715" t="n">
+        <v>13</v>
+      </c>
+      <c r="K715" t="n">
+        <v>28</v>
+      </c>
+      <c r="L715" t="n">
+        <v>6</v>
+      </c>
+      <c r="M715" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N715" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY02PHIBOS-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>8</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F716" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G716" t="n">
+        <v>6</v>
+      </c>
+      <c r="H716" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J716" t="n">
+        <v>0</v>
+      </c>
+      <c r="K716" t="n">
+        <v>6</v>
+      </c>
+      <c r="L716" t="n">
+        <v>4</v>
+      </c>
+      <c r="M716" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr"/>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY02PHIBOS-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D715" t="n">
+      <c r="D717" t="n">
         <v>3</v>
       </c>
-      <c r="E715" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F715" t="n">
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F717" t="n">
         <v>6.5</v>
       </c>
-      <c r="G715" t="n">
+      <c r="G717" t="n">
         <v>12</v>
       </c>
-      <c r="H715" t="n">
+      <c r="H717" t="n">
         <v>-5.5</v>
       </c>
-      <c r="I715" t="inlineStr">
+      <c r="I717" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="J715" t="n">
-        <v>0</v>
-      </c>
-      <c r="K715" t="n">
+      <c r="J717" t="n">
+        <v>0</v>
+      </c>
+      <c r="K717" t="n">
         <v>12</v>
       </c>
-      <c r="M715" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N715" t="inlineStr"/>
-      <c r="P715" t="inlineStr">
+      <c r="L717" t="n">
+        <v>0</v>
+      </c>
+      <c r="M717" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr"/>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="P717" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY02PHIBOS-PHIVEDGECOMBE77-3</t>
         </is>
@@ -45514,25 +45900,29 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.147</v>
+      </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>35.23</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.04</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45645,7 +46035,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -45664,13 +46054,13 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="F5" t="n">
         <v>-1.08</v>
@@ -45701,7 +46091,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -45711,19 +46101,19 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>0.067</v>
+        <v>0.053</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.2</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -45733,35 +46123,35 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>0.133</v>
+        <v>0.105</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>0.067</v>
+        <v>0.105</v>
       </c>
       <c r="F9" t="n">
-        <v>17.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -45821,7 +46211,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -45840,13 +46230,13 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -45928,16 +46318,16 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>0.231</v>
       </c>
       <c r="F17" t="n">
-        <v>5.7</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="18">
@@ -46031,42 +46421,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -46075,20 +46465,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -46097,20 +46487,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rj Barrett</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -46119,23 +46509,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -46390,13 +46780,13 @@
         <v>9</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -46567,7 +46957,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -47563,10 +47953,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.128</v>
+        <v>0.121</v>
       </c>
       <c r="F2" t="n">
         <v>-11.75</v>
@@ -47579,16 +47969,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>0.159</v>
+        <v>0.152</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -47604,16 +47994,16 @@
         <v>270</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.65</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="5">
@@ -47626,16 +48016,16 @@
         <v>171</v>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E5" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="F5" t="n">
-        <v>8.710000000000001</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="6">
@@ -47645,16 +48035,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
-        <v>0.163</v>
+        <v>0.148</v>
       </c>
       <c r="F6" t="n">
         <v>-1.88</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P717"/>
+  <dimension ref="A1:P768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45515,6 +45521,2862 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Anthony Black</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>20</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F718" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G718" t="n">
+        <v>10</v>
+      </c>
+      <c r="H718" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J718" t="n">
+        <v>0</v>
+      </c>
+      <c r="K718" t="n">
+        <v>10</v>
+      </c>
+      <c r="M718" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr"/>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-ORLABLACK0-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Anthony Black</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>8</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F719" t="n">
+        <v>3</v>
+      </c>
+      <c r="G719" t="n">
+        <v>6</v>
+      </c>
+      <c r="H719" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J719" t="n">
+        <v>0</v>
+      </c>
+      <c r="K719" t="n">
+        <v>6</v>
+      </c>
+      <c r="M719" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr"/>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03ORLDET-ORLABLACK0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>3</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F720" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G720" t="n">
+        <v>32</v>
+      </c>
+      <c r="H720" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J720" t="n">
+        <v>0</v>
+      </c>
+      <c r="K720" t="n">
+        <v>32</v>
+      </c>
+      <c r="M720" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr"/>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03ORLDET-DETATHOMPSON9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>25</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F721" t="n">
+        <v>3</v>
+      </c>
+      <c r="G721" t="n">
+        <v>3</v>
+      </c>
+      <c r="H721" t="n">
+        <v>0</v>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J721" t="n">
+        <v>0</v>
+      </c>
+      <c r="K721" t="n">
+        <v>3</v>
+      </c>
+      <c r="M721" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr"/>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-DETATHOMPSON9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>8</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F722" t="n">
+        <v>3</v>
+      </c>
+      <c r="G722" t="n">
+        <v>8</v>
+      </c>
+      <c r="H722" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J722" t="n">
+        <v>0</v>
+      </c>
+      <c r="K722" t="n">
+        <v>8</v>
+      </c>
+      <c r="M722" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr"/>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03ORLDET-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>9</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F723" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G723" t="n">
+        <v>48</v>
+      </c>
+      <c r="H723" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J723" t="n">
+        <v>0</v>
+      </c>
+      <c r="K723" t="n">
+        <v>48</v>
+      </c>
+      <c r="M723" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr"/>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY03ORLDET-DETATHOMPSON9-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>8</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F724" t="n">
+        <v>38</v>
+      </c>
+      <c r="G724" t="n">
+        <v>29</v>
+      </c>
+      <c r="H724" t="n">
+        <v>9</v>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J724" t="n">
+        <v>8</v>
+      </c>
+      <c r="K724" t="n">
+        <v>29</v>
+      </c>
+      <c r="M724" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr"/>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY03ORLDET-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>9</v>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F725" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G725" t="n">
+        <v>53</v>
+      </c>
+      <c r="H725" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J725" t="n">
+        <v>0</v>
+      </c>
+      <c r="K725" t="n">
+        <v>53</v>
+      </c>
+      <c r="M725" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr"/>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03ORLDET-DETCCUNNINGHAM2-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>40</v>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F726" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G726" t="n">
+        <v>12</v>
+      </c>
+      <c r="H726" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J726" t="n">
+        <v>0</v>
+      </c>
+      <c r="K726" t="n">
+        <v>12</v>
+      </c>
+      <c r="M726" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr"/>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-DETCCUNNINGHAM2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>3</v>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F727" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G727" t="n">
+        <v>20</v>
+      </c>
+      <c r="H727" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J727" t="n">
+        <v>0</v>
+      </c>
+      <c r="K727" t="n">
+        <v>20</v>
+      </c>
+      <c r="M727" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr"/>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03ORLDET-DETCCUNNINGHAM2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>20</v>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F728" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G728" t="n">
+        <v>4</v>
+      </c>
+      <c r="H728" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J728" t="n">
+        <v>0</v>
+      </c>
+      <c r="K728" t="n">
+        <v>4</v>
+      </c>
+      <c r="M728" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr"/>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-CLEDSCHRODER8-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>10</v>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F729" t="n">
+        <v>6</v>
+      </c>
+      <c r="G729" t="n">
+        <v>5</v>
+      </c>
+      <c r="H729" t="n">
+        <v>1</v>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J729" t="n">
+        <v>0</v>
+      </c>
+      <c r="K729" t="n">
+        <v>5</v>
+      </c>
+      <c r="M729" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr"/>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03TORCLE-CLEDSCHRODER8-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>3</v>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F730" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G730" t="n">
+        <v>13</v>
+      </c>
+      <c r="H730" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J730" t="n">
+        <v>0</v>
+      </c>
+      <c r="K730" t="n">
+        <v>13</v>
+      </c>
+      <c r="M730" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr"/>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03TORCLE-CLEDSCHRODER8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Desmond Bane</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>30</v>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F731" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G731" t="n">
+        <v>10</v>
+      </c>
+      <c r="H731" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J731" t="n">
+        <v>0</v>
+      </c>
+      <c r="K731" t="n">
+        <v>10</v>
+      </c>
+      <c r="M731" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr"/>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-ORLDBANE3-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>8</v>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F732" t="n">
+        <v>10</v>
+      </c>
+      <c r="G732" t="n">
+        <v>9</v>
+      </c>
+      <c r="H732" t="n">
+        <v>1</v>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J732" t="n">
+        <v>0</v>
+      </c>
+      <c r="K732" t="n">
+        <v>9</v>
+      </c>
+      <c r="M732" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr"/>
+      <c r="P732" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03TORCLE-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>35</v>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F733" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G733" t="n">
+        <v>16</v>
+      </c>
+      <c r="H733" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J733" t="n">
+        <v>0</v>
+      </c>
+      <c r="K733" t="n">
+        <v>16</v>
+      </c>
+      <c r="M733" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr"/>
+      <c r="P733" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-CLEDMITCHELL45-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>3</v>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F734" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G734" t="n">
+        <v>16</v>
+      </c>
+      <c r="H734" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J734" t="n">
+        <v>0</v>
+      </c>
+      <c r="K734" t="n">
+        <v>16</v>
+      </c>
+      <c r="M734" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr"/>
+      <c r="P734" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03TORCLE-CLEDMITCHELL45-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>20</v>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F735" t="n">
+        <v>4</v>
+      </c>
+      <c r="G735" t="n">
+        <v>9</v>
+      </c>
+      <c r="H735" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J735" t="n">
+        <v>0</v>
+      </c>
+      <c r="K735" t="n">
+        <v>9</v>
+      </c>
+      <c r="M735" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr"/>
+      <c r="P735" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-DETDROBINSON55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>25</v>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F736" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G736" t="n">
+        <v>13</v>
+      </c>
+      <c r="H736" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J736" t="n">
+        <v>23</v>
+      </c>
+      <c r="K736" t="n">
+        <v>13</v>
+      </c>
+      <c r="M736" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr"/>
+      <c r="P736" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-CLEEMOBLEY4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>3</v>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F737" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G737" t="n">
+        <v>32</v>
+      </c>
+      <c r="H737" t="n">
+        <v>-28.7</v>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J737" t="n">
+        <v>0</v>
+      </c>
+      <c r="K737" t="n">
+        <v>32</v>
+      </c>
+      <c r="M737" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr"/>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03TORCLE-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>20</v>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F738" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G738" t="n">
+        <v>7</v>
+      </c>
+      <c r="H738" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J738" t="n">
+        <v>0</v>
+      </c>
+      <c r="K738" t="n">
+        <v>7</v>
+      </c>
+      <c r="M738" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr"/>
+      <c r="P738" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-TORJPOELTL19-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Jakob Poeltl</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>8</v>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F739" t="n">
+        <v>3</v>
+      </c>
+      <c r="G739" t="n">
+        <v>9</v>
+      </c>
+      <c r="H739" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J739" t="n">
+        <v>0</v>
+      </c>
+      <c r="K739" t="n">
+        <v>9</v>
+      </c>
+      <c r="M739" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr"/>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03TORCLE-TORJPOELTL19-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>8</v>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F740" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="G740" t="n">
+        <v>73</v>
+      </c>
+      <c r="H740" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J740" t="n">
+        <v>13</v>
+      </c>
+      <c r="K740" t="n">
+        <v>73</v>
+      </c>
+      <c r="M740" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr"/>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY03ORLDET-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>25</v>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F741" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G741" t="n">
+        <v>6</v>
+      </c>
+      <c r="H741" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J741" t="n">
+        <v>29</v>
+      </c>
+      <c r="K741" t="n">
+        <v>6</v>
+      </c>
+      <c r="M741" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr"/>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-DETJDUREN0-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>8</v>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F742" t="n">
+        <v>3</v>
+      </c>
+      <c r="G742" t="n">
+        <v>5</v>
+      </c>
+      <c r="H742" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J742" t="n">
+        <v>0</v>
+      </c>
+      <c r="K742" t="n">
+        <v>5</v>
+      </c>
+      <c r="M742" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr"/>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03ORLDET-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>3</v>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F743" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G743" t="n">
+        <v>13</v>
+      </c>
+      <c r="H743" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J743" t="n">
+        <v>0</v>
+      </c>
+      <c r="K743" t="n">
+        <v>13</v>
+      </c>
+      <c r="M743" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr"/>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY03ORLDET-DETJDUREN0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>8</v>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F744" t="n">
+        <v>8</v>
+      </c>
+      <c r="G744" t="n">
+        <v>7</v>
+      </c>
+      <c r="H744" t="n">
+        <v>1</v>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J744" t="n">
+        <v>0</v>
+      </c>
+      <c r="K744" t="n">
+        <v>7</v>
+      </c>
+      <c r="M744" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr"/>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY03ORLDET-ORLJSUGGS4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>3</v>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F745" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G745" t="n">
+        <v>26</v>
+      </c>
+      <c r="H745" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J745" t="n">
+        <v>0</v>
+      </c>
+      <c r="K745" t="n">
+        <v>26</v>
+      </c>
+      <c r="M745" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr"/>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03ORLDET-ORLJSUGGS4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>25</v>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F746" t="n">
+        <v>3</v>
+      </c>
+      <c r="G746" t="n">
+        <v>6</v>
+      </c>
+      <c r="H746" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J746" t="n">
+        <v>0</v>
+      </c>
+      <c r="K746" t="n">
+        <v>6</v>
+      </c>
+      <c r="M746" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr"/>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-ORLJSUGGS4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Jalen Suggs</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>8</v>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F747" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G747" t="n">
+        <v>17</v>
+      </c>
+      <c r="H747" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J747" t="n">
+        <v>0</v>
+      </c>
+      <c r="K747" t="n">
+        <v>17</v>
+      </c>
+      <c r="M747" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr"/>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03ORLDET-ORLJSUGGS4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>8</v>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F748" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G748" t="n">
+        <v>36</v>
+      </c>
+      <c r="H748" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J748" t="n">
+        <v>0</v>
+      </c>
+      <c r="K748" t="n">
+        <v>36</v>
+      </c>
+      <c r="M748" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr"/>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03TORCLE-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>30</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F749" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G749" t="n">
+        <v>13</v>
+      </c>
+      <c r="H749" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J749" t="n">
+        <v>0</v>
+      </c>
+      <c r="K749" t="n">
+        <v>13</v>
+      </c>
+      <c r="M749" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr"/>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-CLEJHARDEN1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>3</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F750" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G750" t="n">
+        <v>16</v>
+      </c>
+      <c r="H750" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J750" t="n">
+        <v>0</v>
+      </c>
+      <c r="K750" t="n">
+        <v>16</v>
+      </c>
+      <c r="M750" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr"/>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03TORCLE-CLEJHARDEN1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>25</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F751" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G751" t="n">
+        <v>4</v>
+      </c>
+      <c r="H751" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J751" t="n">
+        <v>52</v>
+      </c>
+      <c r="K751" t="n">
+        <v>4</v>
+      </c>
+      <c r="M751" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr"/>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-CLEJALLEN31-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>9</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F752" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="G752" t="n">
+        <v>50</v>
+      </c>
+      <c r="H752" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J752" t="n">
+        <v>0</v>
+      </c>
+      <c r="K752" t="n">
+        <v>50</v>
+      </c>
+      <c r="M752" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr"/>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY03ORLDET-ORLPBANCHERO5-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>35</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F753" t="n">
+        <v>13</v>
+      </c>
+      <c r="G753" t="n">
+        <v>10</v>
+      </c>
+      <c r="H753" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J753" t="n">
+        <v>0</v>
+      </c>
+      <c r="K753" t="n">
+        <v>10</v>
+      </c>
+      <c r="M753" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr"/>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-ORLPBANCHERO5-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>8</v>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F754" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G754" t="n">
+        <v>21</v>
+      </c>
+      <c r="H754" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J754" t="n">
+        <v>0</v>
+      </c>
+      <c r="K754" t="n">
+        <v>21</v>
+      </c>
+      <c r="M754" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr"/>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03ORLDET-ORLPBANCHERO5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>3</v>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F755" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G755" t="n">
+        <v>13</v>
+      </c>
+      <c r="H755" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J755" t="n">
+        <v>0</v>
+      </c>
+      <c r="K755" t="n">
+        <v>13</v>
+      </c>
+      <c r="M755" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr"/>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03ORLDET-ORLPBANCHERO5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Paolo Banchero</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>3</v>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F756" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G756" t="n">
+        <v>97</v>
+      </c>
+      <c r="H756" t="n">
+        <v>-92.09999999999999</v>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J756" t="n">
+        <v>0</v>
+      </c>
+      <c r="K756" t="n">
+        <v>97</v>
+      </c>
+      <c r="M756" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr"/>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY03ORLDET-ORLPBANCHERO5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>8</v>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F757" t="n">
+        <v>3</v>
+      </c>
+      <c r="G757" t="n">
+        <v>7</v>
+      </c>
+      <c r="H757" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J757" t="n">
+        <v>0</v>
+      </c>
+      <c r="K757" t="n">
+        <v>7</v>
+      </c>
+      <c r="M757" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr"/>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03TORCLE-TORRBARRETT9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>35</v>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F758" t="n">
+        <v>3</v>
+      </c>
+      <c r="G758" t="n">
+        <v>10</v>
+      </c>
+      <c r="H758" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J758" t="n">
+        <v>0</v>
+      </c>
+      <c r="K758" t="n">
+        <v>10</v>
+      </c>
+      <c r="M758" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr"/>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-TORRBARRETT9-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Rj Barrett</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>3</v>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F759" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G759" t="n">
+        <v>96</v>
+      </c>
+      <c r="H759" t="n">
+        <v>-92.7</v>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J759" t="n">
+        <v>0</v>
+      </c>
+      <c r="K759" t="n">
+        <v>96</v>
+      </c>
+      <c r="M759" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr"/>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03TORCLE-TORRBARRETT9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>3</v>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F760" t="n">
+        <v>19</v>
+      </c>
+      <c r="G760" t="n">
+        <v>21</v>
+      </c>
+      <c r="H760" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J760" t="n">
+        <v>0</v>
+      </c>
+      <c r="K760" t="n">
+        <v>21</v>
+      </c>
+      <c r="M760" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr"/>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03TORCLE-TORSBARNES4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>30</v>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F761" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G761" t="n">
+        <v>16</v>
+      </c>
+      <c r="H761" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J761" t="n">
+        <v>0</v>
+      </c>
+      <c r="K761" t="n">
+        <v>16</v>
+      </c>
+      <c r="M761" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr"/>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03TORCLE-TORSBARNES4-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>8</v>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F762" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G762" t="n">
+        <v>58</v>
+      </c>
+      <c r="H762" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J762" t="n">
+        <v>0</v>
+      </c>
+      <c r="K762" t="n">
+        <v>58</v>
+      </c>
+      <c r="M762" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr"/>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03TORCLE-TORSBARNES4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>8</v>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F763" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G763" t="n">
+        <v>32</v>
+      </c>
+      <c r="H763" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J763" t="n">
+        <v>0</v>
+      </c>
+      <c r="K763" t="n">
+        <v>32</v>
+      </c>
+      <c r="M763" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr"/>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY03ORLDET-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>8</v>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F764" t="n">
+        <v>3</v>
+      </c>
+      <c r="G764" t="n">
+        <v>5</v>
+      </c>
+      <c r="H764" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J764" t="n">
+        <v>0</v>
+      </c>
+      <c r="K764" t="n">
+        <v>5</v>
+      </c>
+      <c r="M764" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr"/>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY03ORLDET-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>30</v>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F765" t="n">
+        <v>3</v>
+      </c>
+      <c r="G765" t="n">
+        <v>7</v>
+      </c>
+      <c r="H765" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J765" t="n">
+        <v>0</v>
+      </c>
+      <c r="K765" t="n">
+        <v>7</v>
+      </c>
+      <c r="M765" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr"/>
+      <c r="P765" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-DETTHARRIS12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>3</v>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F766" t="n">
+        <v>9</v>
+      </c>
+      <c r="G766" t="n">
+        <v>17</v>
+      </c>
+      <c r="H766" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J766" t="n">
+        <v>0</v>
+      </c>
+      <c r="K766" t="n">
+        <v>17</v>
+      </c>
+      <c r="M766" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr"/>
+      <c r="P766" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY03ORLDET-DETTHARRIS12-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>25</v>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F767" t="n">
+        <v>3</v>
+      </c>
+      <c r="G767" t="n">
+        <v>6</v>
+      </c>
+      <c r="H767" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J767" t="n">
+        <v>0</v>
+      </c>
+      <c r="K767" t="n">
+        <v>6</v>
+      </c>
+      <c r="M767" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr"/>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY03ORLDET-ORLWCARTER34-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Wendell Carter Jr.</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>8</v>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F768" t="n">
+        <v>38</v>
+      </c>
+      <c r="G768" t="n">
+        <v>46</v>
+      </c>
+      <c r="H768" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J768" t="n">
+        <v>0</v>
+      </c>
+      <c r="K768" t="n">
+        <v>46</v>
+      </c>
+      <c r="M768" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr"/>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY03ORLDET-ORLWCARTER34-8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45526,7 +48388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45923,6 +48785,33 @@
       <c r="I12" t="n">
         <v>1.04</v>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>51</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>51</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45981,161 +48870,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.278</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.35</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.318</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>7.33</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.51</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.08</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.053</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.053</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>15.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>0.105</v>
+        <v>0.053</v>
       </c>
       <c r="F8" t="n">
-        <v>20.74</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -46151,26 +49040,26 @@
         <v>0.105</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>0.312</v>
+        <v>0.105</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -46179,64 +49068,64 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.278</v>
+        <v>0.312</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.29</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.74</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.133</v>
+        <v>0.312</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -46245,11 +49134,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
@@ -46261,48 +49150,48 @@
         <v>0.312</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.062</v>
+        <v>0.143</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.312</v>
+        <v>0.533</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -46311,42 +49200,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>15</v>
       </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>12.33</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>0.533</v>
+        <v>0.133</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -46355,42 +49244,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.231</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -46399,20 +49288,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -46421,42 +49310,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -46465,20 +49354,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -46487,20 +49376,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.333</v>
+        <v>0.455</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -46509,42 +49398,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rj Barrett</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>0.273</v>
+        <v>0.375</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -46553,20 +49442,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>11</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.455</v>
+        <v>0.273</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -46575,29 +49464,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.25</v>
+        <v>0.111</v>
       </c>
       <c r="F29" t="n">
-        <v>13.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -46607,32 +49496,32 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -46641,7 +49530,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -46651,76 +49540,76 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-3.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>10</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -46729,64 +49618,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-7.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>0.111</v>
+        <v>0.222</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>9</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -46795,20 +49684,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -46817,86 +49706,86 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jaden Mcdaniels</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -46905,41 +49794,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -46947,17 +49838,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -46969,7 +49860,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -46979,11 +49870,9 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
         <v>0</v>
       </c>
@@ -46991,7 +49880,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -47001,7 +49890,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -47013,7 +49902,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -47023,7 +49912,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -47035,42 +49924,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -47079,42 +49968,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.05</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -47123,39 +50012,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
         <v>4</v>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>3</v>
-      </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
         <v>4</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>3</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -47167,19 +50056,21 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Donte Divincenzo</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
         <v>4</v>
       </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
@@ -47187,17 +50078,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -47209,7 +50100,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -47219,7 +50110,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -47231,7 +50122,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Donte Divincenzo</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -47241,11 +50132,9 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>0</v>
       </c>
@@ -47253,23 +50142,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -47947,7 +50836,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
@@ -47969,7 +50858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -47991,7 +50880,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
@@ -48013,7 +50902,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C5" t="n">
         <v>51</v>
@@ -48035,7 +50924,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1176"/>
+  <dimension ref="A1:P1227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75715,6 +75721,2862 @@
         </is>
       </c>
     </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1177" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1177" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1177" t="n">
+        <v>41</v>
+      </c>
+      <c r="M1177" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1177" t="inlineStr"/>
+      <c r="P1177" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1178" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1178" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1178" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1178" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1178" t="inlineStr"/>
+      <c r="P1178" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-DETATHOMPSON9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1179" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1179" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1179" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1179" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1179" t="inlineStr"/>
+      <c r="P1179" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1180" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1180" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1180" t="n">
+        <v>36</v>
+      </c>
+      <c r="M1180" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1180" t="inlineStr"/>
+      <c r="P1180" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09DETCLE-DETATHOMPSON9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Austin Reaves</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1181" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1181" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1181" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1181" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1181" t="inlineStr"/>
+      <c r="P1181" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09OKCLAL-LALAREAVES15-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1182" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1182" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1182" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1182" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1182" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1182" t="inlineStr"/>
+      <c r="P1182" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1183" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1183" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1183" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1183" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1183" t="inlineStr"/>
+      <c r="P1183" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09DETCLE-DETCCUNNINGHAM2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1184" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1184" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1184" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1184" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1184" t="inlineStr"/>
+      <c r="P1184" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-DETCCUNNINGHAM2-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1185" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1185" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>72</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1185" t="n">
+        <v>72</v>
+      </c>
+      <c r="M1185" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1185" t="inlineStr"/>
+      <c r="P1185" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1186" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1186" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1186" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1186" t="n">
+        <v>51</v>
+      </c>
+      <c r="M1186" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1186" t="inlineStr"/>
+      <c r="P1186" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09OKCLAL-OKCCHOLMGREN7-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1187" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1187" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1187" t="n">
+        <v>31</v>
+      </c>
+      <c r="M1187" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1187" t="inlineStr"/>
+      <c r="P1187" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY09OKCLAL-OKCCHOLMGREN7-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1188" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1188" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1188" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1188" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1188" t="inlineStr"/>
+      <c r="P1188" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY09OKCLAL-LALDAYTON5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1189" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1189" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>57</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1189" t="n">
+        <v>57</v>
+      </c>
+      <c r="M1189" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1189" t="inlineStr"/>
+      <c r="P1189" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09OKCLAL-LALDAYTON5-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1190" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1190" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1190" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1190" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1190" t="inlineStr"/>
+      <c r="P1190" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-CLEDSCHRODER8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1191" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1191" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1191" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1191" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1191" t="inlineStr"/>
+      <c r="P1191" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1192" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1192" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1192" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1192" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1192" t="inlineStr"/>
+      <c r="P1192" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1193" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1193" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1193" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1193" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1193" t="inlineStr"/>
+      <c r="P1193" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09DETCLE-CLEDMITCHELL45-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1194" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1194" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1194" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1194" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1194" t="inlineStr"/>
+      <c r="P1194" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEDMITCHELL45-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1195" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1195" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1195" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1195" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1195" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1195" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1195" t="inlineStr"/>
+      <c r="P1195" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-DETDROBINSON55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1196" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1196" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1196" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1196" t="n">
+        <v>15</v>
+      </c>
+      <c r="K1196" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1196" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1196" t="inlineStr"/>
+      <c r="P1196" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEEMOBLEY4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1197" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1197" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1197" t="n">
+        <v>49</v>
+      </c>
+      <c r="H1197" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1197" t="n">
+        <v>49</v>
+      </c>
+      <c r="M1197" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1197" t="inlineStr"/>
+      <c r="P1197" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-CLEEMOBLEY4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1198" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1198" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G1198" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1198" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1198" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1198" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1198" t="inlineStr"/>
+      <c r="P1198" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09DETCLE-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1199" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1199" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1199" t="n">
+        <v>29</v>
+      </c>
+      <c r="M1199" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1199" t="inlineStr"/>
+      <c r="P1199" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY09DETCLE-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1200" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1200" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1200" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1200" t="n">
+        <v>54</v>
+      </c>
+      <c r="M1200" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1200" t="inlineStr"/>
+      <c r="P1200" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09OKCLAL-OKCIHARTENSTEIN55-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1201" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1201" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1201" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1201" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1201" t="inlineStr"/>
+      <c r="P1201" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-DETJDUREN0-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1202" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1202" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1202" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1202" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1202" t="inlineStr"/>
+      <c r="P1202" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1203" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1203" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>84</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1203" t="n">
+        <v>84</v>
+      </c>
+      <c r="M1203" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1203" t="inlineStr"/>
+      <c r="P1203" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1204" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1204" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1204" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1204" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1204" t="inlineStr"/>
+      <c r="P1204" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY09DETCLE-DETJDUREN0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1205" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1205" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1205" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1205" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1205" t="inlineStr"/>
+      <c r="P1205" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1206" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1206" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1206" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1206" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1206" t="inlineStr"/>
+      <c r="P1206" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09DETCLE-CLEJHARDEN1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1207" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1207" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1207" t="n">
+        <v>37</v>
+      </c>
+      <c r="M1207" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1207" t="inlineStr"/>
+      <c r="P1207" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1208" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1208" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1208" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1208" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1208" t="inlineStr"/>
+      <c r="P1208" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEJHARDEN1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1209" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1209" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1209" t="n">
+        <v>33</v>
+      </c>
+      <c r="K1209" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1209" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1209" t="inlineStr"/>
+      <c r="P1209" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEJALLEN31-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1210" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1210" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1210" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1210" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1210" t="inlineStr"/>
+      <c r="P1210" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY09DETCLE-CLEJALLEN31-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1211" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1211" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1211" t="n">
+        <v>47</v>
+      </c>
+      <c r="M1211" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1211" t="inlineStr"/>
+      <c r="P1211" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-CLEJALLEN31-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Jaylon Tyson</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1212" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1212" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1212" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1212" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1212" t="inlineStr"/>
+      <c r="P1212" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEJTYSON20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1213" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1213" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1213" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1213" t="n">
+        <v>14</v>
+      </c>
+      <c r="M1213" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1213" t="inlineStr"/>
+      <c r="P1213" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09OKCLAL-LALLJAMES23-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1214" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1214" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1214" t="n">
+        <v>36</v>
+      </c>
+      <c r="M1214" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1214" t="inlineStr"/>
+      <c r="P1214" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09OKCLAL-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1215" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1215" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1215" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1215" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1215" t="inlineStr"/>
+      <c r="P1215" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY09OKCLAL-LALLJAMES23-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1216" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1216" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1216" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1216" t="n">
+        <v>52</v>
+      </c>
+      <c r="M1216" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1216" t="inlineStr"/>
+      <c r="P1216" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09OKCLAL-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1217" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1217" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>34</v>
+      </c>
+      <c r="H1217" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1217" t="n">
+        <v>34</v>
+      </c>
+      <c r="M1217" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1217" t="inlineStr"/>
+      <c r="P1217" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09OKCLAL-OKCLDORT5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1218" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1218" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>67</v>
+      </c>
+      <c r="H1218" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1218" t="n">
+        <v>67</v>
+      </c>
+      <c r="M1218" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1218" t="inlineStr"/>
+      <c r="P1218" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09OKCLAL-OKCLDORT5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1219" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1219" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1219" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1219" t="n">
+        <v>22</v>
+      </c>
+      <c r="M1219" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1219" t="inlineStr"/>
+      <c r="P1219" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09OKCLAL-LALMSMART36-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1220" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1220" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1220" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1220" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1220" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1220" t="inlineStr"/>
+      <c r="P1220" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09OKCLAL-LALMSMART36-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1221" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1221" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1221" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1221" t="n">
+        <v>41</v>
+      </c>
+      <c r="M1221" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1221" t="inlineStr"/>
+      <c r="P1221" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1222" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1222" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1222" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1222" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1222" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1222" t="inlineStr"/>
+      <c r="P1222" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1223" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1223" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1223" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1223" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1223" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1223" t="inlineStr"/>
+      <c r="P1223" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1224" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1224" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1224" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1224" t="n">
+        <v>32</v>
+      </c>
+      <c r="M1224" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1224" t="inlineStr"/>
+      <c r="P1224" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1225" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1225" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1225" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1225" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1225" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1225" t="inlineStr"/>
+      <c r="P1225" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1226" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1226" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1226" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1226" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1226" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1226" t="inlineStr"/>
+      <c r="P1226" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-DETTHARRIS12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1227" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1227" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1227" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1227" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1227" t="inlineStr"/>
+      <c r="P1227" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09DETCLE-DETTHARRIS12-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -75726,7 +78588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76344,6 +79206,33 @@
       <c r="I19" t="n">
         <v>0.39</v>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>51</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>51</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -76406,7 +79295,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -76428,7 +79317,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -76450,7 +79339,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
@@ -76472,7 +79361,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
@@ -76494,7 +79383,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -76516,7 +79405,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
@@ -76534,51 +79423,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0.065</v>
+        <v>0.355</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.51</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>0.355</v>
+        <v>0.065</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.19</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vj Edgecombe</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -76588,54 +79477,54 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>0.133</v>
+        <v>0.148</v>
       </c>
       <c r="F10" t="n">
-        <v>9.880000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Vj Edgecombe</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>0.067</v>
+        <v>0.133</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>0.148</v>
+        <v>0.067</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -76644,23 +79533,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="14">
@@ -76670,7 +79559,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
@@ -76688,23 +79577,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.28</v>
       </c>
       <c r="F15" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -76714,7 +79603,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
@@ -76732,7 +79621,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -76742,145 +79631,145 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.74</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amen Thompson</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E19" t="n">
-        <v>0.318</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>7.33</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>0.095</v>
+        <v>0.318</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.08</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0.235</v>
+        <v>0.095</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>0.048</v>
+        <v>0.235</v>
       </c>
       <c r="F22" t="n">
-        <v>15.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>0.333</v>
+        <v>0.048</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="24">
@@ -76974,64 +79863,64 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jaden Mcdaniels</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -77040,20 +79929,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rj Barrett</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -77062,20 +79951,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" t="n">
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -77194,20 +80083,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -77216,29 +80105,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>0.143</v>
+        <v>0.083</v>
       </c>
       <c r="F39" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -77248,35 +80137,35 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.091</v>
+        <v>0.143</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5600000000000001</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>11</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -77392,64 +80281,64 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F47" t="n">
-        <v>13.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>10</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>10</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -77458,7 +80347,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -77474,13 +80363,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-7.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -77496,57 +80385,57 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.84</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>-4.08</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -77568,11 +80457,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -77584,48 +80473,48 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>9</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>9</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>0.222</v>
+        <v>0.111</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -77634,20 +80523,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -77678,11 +80567,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -77700,7 +80589,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -78414,7 +81303,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C2" t="n">
         <v>22</v>
@@ -78436,7 +81325,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
@@ -78458,7 +81347,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C4" t="n">
         <v>27</v>
@@ -78480,7 +81369,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
@@ -78502,7 +81391,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
         <v>26</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +55,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,14 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1227"/>
+  <dimension ref="A1:P1238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75765,12 +75759,20 @@
       <c r="K1177" t="n">
         <v>41</v>
       </c>
-      <c r="M1177" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1177" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1177" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1177" t="inlineStr"/>
+      <c r="O1177" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1177" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY09DETCLE-DETATHOMPSON9-8</t>
@@ -75821,12 +75823,20 @@
       <c r="K1178" t="n">
         <v>5</v>
       </c>
-      <c r="M1178" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1178" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1178" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1178" t="inlineStr"/>
+      <c r="O1178" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1178" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY09DETCLE-DETATHOMPSON9-25</t>
@@ -75877,12 +75887,20 @@
       <c r="K1179" t="n">
         <v>5</v>
       </c>
-      <c r="M1179" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1179" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1179" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1179" t="inlineStr"/>
+      <c r="O1179" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1179" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY09DETCLE-DETATHOMPSON9-8</t>
@@ -75933,12 +75951,20 @@
       <c r="K1180" t="n">
         <v>36</v>
       </c>
-      <c r="M1180" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1180" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1180" t="inlineStr"/>
+      <c r="O1180" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1180" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY09DETCLE-DETATHOMPSON9-3</t>
@@ -75989,12 +76015,20 @@
       <c r="K1181" t="n">
         <v>25</v>
       </c>
-      <c r="M1181" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1181" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1181" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1181" t="inlineStr"/>
+      <c r="O1181" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1181" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY09OKCLAL-LALAREAVES15-8</t>
@@ -76009,16 +76043,16 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1182" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
@@ -76026,13 +76060,13 @@
         </is>
       </c>
       <c r="F1182" t="n">
-        <v>28.8</v>
+        <v>15.3</v>
       </c>
       <c r="G1182" t="n">
         <v>18</v>
       </c>
       <c r="H1182" t="n">
-        <v>10.8</v>
+        <v>-2.7</v>
       </c>
       <c r="I1182" t="inlineStr">
         <is>
@@ -76040,20 +76074,28 @@
         </is>
       </c>
       <c r="J1182" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K1182" t="n">
         <v>18</v>
       </c>
-      <c r="M1182" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1182" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1182" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1182" t="inlineStr"/>
+      <c r="O1182" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1182" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09DETCLE-DETCCUNNINGHAM2-8</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-LALAREAVES15-30</t>
         </is>
       </c>
     </row>
@@ -76070,11 +76112,11 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1183" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1183" t="inlineStr">
         <is>
@@ -76082,34 +76124,44 @@
         </is>
       </c>
       <c r="F1183" t="n">
-        <v>12</v>
+        <v>28.8</v>
       </c>
       <c r="G1183" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H1183" t="n">
-        <v>-5</v>
+        <v>10.8</v>
       </c>
       <c r="I1183" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1183" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1183" t="n">
-        <v>17</v>
-      </c>
-      <c r="M1183" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1183" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="L1183" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1183" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N1183" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="O1183" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1183" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09DETCLE-DETCCUNNINGHAM2-3</t>
+          <t>KXNBAREB-26MAY09DETCLE-DETCCUNNINGHAM2-8</t>
         </is>
       </c>
     </row>
@@ -76126,11 +76178,11 @@
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D1184" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
@@ -76138,34 +76190,42 @@
         </is>
       </c>
       <c r="F1184" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="G1184" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H1184" t="n">
-        <v>-6.1</v>
+        <v>-5</v>
       </c>
       <c r="I1184" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1184" t="n">
         <v>0</v>
       </c>
       <c r="K1184" t="n">
-        <v>19</v>
-      </c>
-      <c r="M1184" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>17</v>
+      </c>
+      <c r="L1184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1184" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1184" t="inlineStr"/>
+      <c r="O1184" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1184" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-DETCCUNNINGHAM2-35</t>
+          <t>KXNBASTL-26MAY09DETCLE-DETCCUNNINGHAM2-3</t>
         </is>
       </c>
     </row>
@@ -76182,11 +76242,11 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1185" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E1185" t="inlineStr">
         <is>
@@ -76194,13 +76254,13 @@
         </is>
       </c>
       <c r="F1185" t="n">
-        <v>58.5</v>
+        <v>12.9</v>
       </c>
       <c r="G1185" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="H1185" t="n">
-        <v>-13.5</v>
+        <v>-6.1</v>
       </c>
       <c r="I1185" t="inlineStr">
         <is>
@@ -76211,17 +76271,25 @@
         <v>0</v>
       </c>
       <c r="K1185" t="n">
-        <v>72</v>
-      </c>
-      <c r="M1185" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>19</v>
+      </c>
+      <c r="L1185" t="n">
+        <v>27</v>
+      </c>
+      <c r="M1185" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1185" t="inlineStr"/>
+      <c r="O1185" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1185" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09DETCLE-DETCCUNNINGHAM2-8</t>
+          <t>KXNBAPTS-26MAY09DETCLE-DETCCUNNINGHAM2-35</t>
         </is>
       </c>
     </row>
@@ -76233,16 +76301,16 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D1186" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
@@ -76250,13 +76318,13 @@
         </is>
       </c>
       <c r="F1186" t="n">
-        <v>57.5</v>
+        <v>58.5</v>
       </c>
       <c r="G1186" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="H1186" t="n">
-        <v>6.5</v>
+        <v>-13.5</v>
       </c>
       <c r="I1186" t="inlineStr">
         <is>
@@ -76264,20 +76332,28 @@
         </is>
       </c>
       <c r="J1186" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K1186" t="n">
-        <v>51</v>
-      </c>
-      <c r="M1186" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>72</v>
+      </c>
+      <c r="L1186" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1186" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1186" t="inlineStr"/>
+      <c r="O1186" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1186" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09OKCLAL-OKCCHOLMGREN7-9</t>
+          <t>KXNBAAST-26MAY09DETCLE-DETCCUNNINGHAM2-8</t>
         </is>
       </c>
     </row>
@@ -76289,16 +76365,16 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1187" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E1187" t="inlineStr">
         <is>
@@ -76306,13 +76382,13 @@
         </is>
       </c>
       <c r="F1187" t="n">
-        <v>32</v>
+        <v>5.8</v>
       </c>
       <c r="G1187" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1187" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I1187" t="inlineStr">
         <is>
@@ -76323,17 +76399,25 @@
         <v>0</v>
       </c>
       <c r="K1187" t="n">
-        <v>31</v>
-      </c>
-      <c r="M1187" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L1187" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1187" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1187" t="inlineStr"/>
+      <c r="O1187" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1187" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY09OKCLAL-OKCCHOLMGREN7-3</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-OKCCWALLACE22-20</t>
         </is>
       </c>
     </row>
@@ -76345,16 +76429,16 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1188" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1188" t="inlineStr">
         <is>
@@ -76362,34 +76446,44 @@
         </is>
       </c>
       <c r="F1188" t="n">
-        <v>8.6</v>
+        <v>57.5</v>
       </c>
       <c r="G1188" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="H1188" t="n">
-        <v>-1.4</v>
+        <v>6.5</v>
       </c>
       <c r="I1188" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1188" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1188" t="n">
-        <v>10</v>
-      </c>
-      <c r="M1188" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1188" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="L1188" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1188" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N1188" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O1188" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1188" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY09OKCLAL-LALDAYTON5-3</t>
+          <t>KXNBAREB-26MAY09OKCLAL-OKCCHOLMGREN7-9</t>
         </is>
       </c>
     </row>
@@ -76401,16 +76495,16 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D1189" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1189" t="inlineStr">
         <is>
@@ -76418,34 +76512,42 @@
         </is>
       </c>
       <c r="F1189" t="n">
-        <v>55.2</v>
+        <v>32</v>
       </c>
       <c r="G1189" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="H1189" t="n">
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="I1189" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1189" t="n">
         <v>0</v>
       </c>
       <c r="K1189" t="n">
-        <v>57</v>
-      </c>
-      <c r="M1189" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>31</v>
+      </c>
+      <c r="L1189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1189" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1189" t="inlineStr"/>
+      <c r="O1189" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1189" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09OKCLAL-LALDAYTON5-9</t>
+          <t>KXNBABLK-26MAY09OKCLAL-OKCCHOLMGREN7-3</t>
         </is>
       </c>
     </row>
@@ -76457,16 +76559,16 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1190" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E1190" t="inlineStr">
         <is>
@@ -76474,34 +76576,42 @@
         </is>
       </c>
       <c r="F1190" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="G1190" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H1190" t="n">
-        <v>-3.5</v>
+        <v>-7.8</v>
       </c>
       <c r="I1190" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J1190" t="n">
         <v>0</v>
       </c>
       <c r="K1190" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1190" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>14</v>
+      </c>
+      <c r="L1190" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1190" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1190" t="inlineStr"/>
+      <c r="O1190" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1190" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09DETCLE-CLEDSCHRODER8-8</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-OKCCHOLMGREN7-25</t>
         </is>
       </c>
     </row>
@@ -76513,16 +76623,16 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D1191" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1191" t="inlineStr">
         <is>
@@ -76530,34 +76640,42 @@
         </is>
       </c>
       <c r="F1191" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="G1191" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H1191" t="n">
-        <v>-2.7</v>
+        <v>-1.4</v>
       </c>
       <c r="I1191" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1191" t="n">
         <v>0</v>
       </c>
       <c r="K1191" t="n">
-        <v>7</v>
-      </c>
-      <c r="M1191" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>10</v>
+      </c>
+      <c r="L1191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1191" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1191" t="inlineStr"/>
+      <c r="O1191" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1191" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09DETCLE-CLEDMITCHELL45-8</t>
+          <t>KXNBABLK-26MAY09OKCLAL-LALDAYTON5-3</t>
         </is>
       </c>
     </row>
@@ -76569,16 +76687,16 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1192" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1192" t="inlineStr">
         <is>
@@ -76586,13 +76704,13 @@
         </is>
       </c>
       <c r="F1192" t="n">
-        <v>3</v>
+        <v>55.2</v>
       </c>
       <c r="G1192" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="H1192" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="I1192" t="inlineStr">
         <is>
@@ -76603,17 +76721,25 @@
         <v>0</v>
       </c>
       <c r="K1192" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1192" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>57</v>
+      </c>
+      <c r="L1192" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1192" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1192" t="inlineStr"/>
+      <c r="O1192" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1192" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09DETCLE-CLEDMITCHELL45-8</t>
+          <t>KXNBAREB-26MAY09OKCLAL-LALDAYTON5-9</t>
         </is>
       </c>
     </row>
@@ -76625,16 +76751,16 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1193" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E1193" t="inlineStr">
         <is>
@@ -76642,13 +76768,13 @@
         </is>
       </c>
       <c r="F1193" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="G1193" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H1193" t="n">
-        <v>-9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="I1193" t="inlineStr">
         <is>
@@ -76659,17 +76785,25 @@
         <v>0</v>
       </c>
       <c r="K1193" t="n">
-        <v>15</v>
-      </c>
-      <c r="M1193" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L1193" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1193" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1193" t="inlineStr"/>
+      <c r="O1193" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1193" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09DETCLE-CLEDMITCHELL45-3</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-LALDAYTON5-20</t>
         </is>
       </c>
     </row>
@@ -76681,16 +76815,16 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D1194" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E1194" t="inlineStr">
         <is>
@@ -76698,34 +76832,42 @@
         </is>
       </c>
       <c r="F1194" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="G1194" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H1194" t="n">
-        <v>-12.2</v>
+        <v>-3.5</v>
       </c>
       <c r="I1194" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1194" t="n">
         <v>0</v>
       </c>
       <c r="K1194" t="n">
-        <v>18</v>
-      </c>
-      <c r="M1194" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L1194" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1194" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1194" t="inlineStr"/>
+      <c r="O1194" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1194" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-CLEDMITCHELL45-35</t>
+          <t>KXNBAAST-26MAY09DETCLE-CLEDSCHRODER8-8</t>
         </is>
       </c>
     </row>
@@ -76737,16 +76879,16 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1195" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E1195" t="inlineStr">
         <is>
@@ -76754,13 +76896,13 @@
         </is>
       </c>
       <c r="F1195" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="G1195" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H1195" t="n">
-        <v>-9</v>
+        <v>-2.7</v>
       </c>
       <c r="I1195" t="inlineStr">
         <is>
@@ -76771,17 +76913,25 @@
         <v>0</v>
       </c>
       <c r="K1195" t="n">
-        <v>12</v>
-      </c>
-      <c r="M1195" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>7</v>
+      </c>
+      <c r="L1195" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1195" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1195" t="inlineStr"/>
+      <c r="O1195" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1195" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-DETDROBINSON55-20</t>
+          <t>KXNBAREB-26MAY09DETCLE-CLEDMITCHELL45-8</t>
         </is>
       </c>
     </row>
@@ -76793,16 +76943,16 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D1196" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E1196" t="inlineStr">
         <is>
@@ -76810,13 +76960,13 @@
         </is>
       </c>
       <c r="F1196" t="n">
-        <v>17.2</v>
+        <v>3</v>
       </c>
       <c r="G1196" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H1196" t="n">
-        <v>7.2</v>
+        <v>-5</v>
       </c>
       <c r="I1196" t="inlineStr">
         <is>
@@ -76824,20 +76974,28 @@
         </is>
       </c>
       <c r="J1196" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K1196" t="n">
-        <v>10</v>
-      </c>
-      <c r="M1196" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>8</v>
+      </c>
+      <c r="L1196" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1196" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1196" t="inlineStr"/>
+      <c r="O1196" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1196" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-CLEEMOBLEY4-25</t>
+          <t>KXNBAAST-26MAY09DETCLE-CLEDMITCHELL45-8</t>
         </is>
       </c>
     </row>
@@ -76849,16 +77007,16 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D1197" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1197" t="inlineStr">
         <is>
@@ -76866,34 +77024,42 @@
         </is>
       </c>
       <c r="F1197" t="n">
-        <v>51</v>
+        <v>5.3</v>
       </c>
       <c r="G1197" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="H1197" t="n">
-        <v>2</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="I1197" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1197" t="n">
         <v>0</v>
       </c>
       <c r="K1197" t="n">
-        <v>49</v>
-      </c>
-      <c r="M1197" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>15</v>
+      </c>
+      <c r="L1197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1197" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1197" t="inlineStr"/>
+      <c r="O1197" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1197" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09DETCLE-CLEEMOBLEY4-9</t>
+          <t>KXNBASTL-26MAY09DETCLE-CLEDMITCHELL45-3</t>
         </is>
       </c>
     </row>
@@ -76905,16 +77071,16 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1198" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E1198" t="inlineStr">
         <is>
@@ -76922,34 +77088,42 @@
         </is>
       </c>
       <c r="F1198" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="G1198" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H1198" t="n">
-        <v>-3.3</v>
+        <v>-12.2</v>
       </c>
       <c r="I1198" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J1198" t="n">
         <v>0</v>
       </c>
       <c r="K1198" t="n">
-        <v>12</v>
-      </c>
-      <c r="M1198" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>18</v>
+      </c>
+      <c r="L1198" t="n">
+        <v>35</v>
+      </c>
+      <c r="M1198" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1198" t="inlineStr"/>
+      <c r="O1198" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1198" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09DETCLE-CLEEMOBLEY4-3</t>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEDMITCHELL45-35</t>
         </is>
       </c>
     </row>
@@ -76961,51 +77135,59 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1199" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1199" t="n">
         <v>3</v>
       </c>
-      <c r="E1199" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F1199" t="n">
-        <v>25.4</v>
-      </c>
       <c r="G1199" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H1199" t="n">
-        <v>-3.6</v>
+        <v>-9</v>
       </c>
       <c r="I1199" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1199" t="n">
         <v>0</v>
       </c>
       <c r="K1199" t="n">
-        <v>29</v>
-      </c>
-      <c r="M1199" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>12</v>
+      </c>
+      <c r="L1199" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1199" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1199" t="inlineStr"/>
+      <c r="O1199" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1199" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY09DETCLE-CLEEMOBLEY4-3</t>
+          <t>KXNBAPTS-26MAY09DETCLE-DETDROBINSON55-20</t>
         </is>
       </c>
     </row>
@@ -77017,16 +77199,16 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1200" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E1200" t="inlineStr">
         <is>
@@ -77034,13 +77216,13 @@
         </is>
       </c>
       <c r="F1200" t="n">
-        <v>47.4</v>
+        <v>17.2</v>
       </c>
       <c r="G1200" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="H1200" t="n">
-        <v>-6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I1200" t="inlineStr">
         <is>
@@ -77048,20 +77230,30 @@
         </is>
       </c>
       <c r="J1200" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K1200" t="n">
-        <v>54</v>
-      </c>
-      <c r="M1200" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1200" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L1200" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1200" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1200" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="O1200" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1200" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09OKCLAL-OKCIHARTENSTEIN55-9</t>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEEMOBLEY4-25</t>
         </is>
       </c>
     </row>
@@ -77073,16 +77265,16 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1201" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E1201" t="inlineStr">
         <is>
@@ -77090,13 +77282,13 @@
         </is>
       </c>
       <c r="F1201" t="n">
-        <v>10.9</v>
+        <v>51</v>
       </c>
       <c r="G1201" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="H1201" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="I1201" t="inlineStr">
         <is>
@@ -77107,17 +77299,25 @@
         <v>0</v>
       </c>
       <c r="K1201" t="n">
-        <v>6</v>
-      </c>
-      <c r="M1201" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>49</v>
+      </c>
+      <c r="L1201" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1201" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1201" t="inlineStr"/>
+      <c r="O1201" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1201" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-DETJDUREN0-25</t>
+          <t>KXNBAREB-26MAY09DETCLE-CLEEMOBLEY4-9</t>
         </is>
       </c>
     </row>
@@ -77129,16 +77329,16 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D1202" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1202" t="inlineStr">
         <is>
@@ -77146,13 +77346,13 @@
         </is>
       </c>
       <c r="F1202" t="n">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G1202" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H1202" t="n">
-        <v>-2</v>
+        <v>-3.3</v>
       </c>
       <c r="I1202" t="inlineStr">
         <is>
@@ -77163,17 +77363,25 @@
         <v>0</v>
       </c>
       <c r="K1202" t="n">
-        <v>5</v>
-      </c>
-      <c r="M1202" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>12</v>
+      </c>
+      <c r="L1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1202" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1202" t="inlineStr"/>
+      <c r="O1202" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1202" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09DETCLE-DETJDUREN0-8</t>
+          <t>KXNBASTL-26MAY09DETCLE-CLEEMOBLEY4-3</t>
         </is>
       </c>
     </row>
@@ -77185,16 +77393,16 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D1203" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1203" t="inlineStr">
         <is>
@@ -77202,34 +77410,42 @@
         </is>
       </c>
       <c r="F1203" t="n">
-        <v>81.8</v>
+        <v>25.4</v>
       </c>
       <c r="G1203" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="H1203" t="n">
-        <v>-2.2</v>
+        <v>-3.6</v>
       </c>
       <c r="I1203" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1203" t="n">
         <v>0</v>
       </c>
       <c r="K1203" t="n">
-        <v>84</v>
-      </c>
-      <c r="M1203" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>29</v>
+      </c>
+      <c r="L1203" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1203" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1203" t="inlineStr"/>
+      <c r="O1203" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1203" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09DETCLE-DETJDUREN0-8</t>
+          <t>KXNBABLK-26MAY09DETCLE-CLEEMOBLEY4-3</t>
         </is>
       </c>
     </row>
@@ -77241,16 +77457,16 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1204" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1204" t="inlineStr">
         <is>
@@ -77258,34 +77474,42 @@
         </is>
       </c>
       <c r="F1204" t="n">
-        <v>5.2</v>
+        <v>47.4</v>
       </c>
       <c r="G1204" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="H1204" t="n">
-        <v>-10.8</v>
+        <v>-6.6</v>
       </c>
       <c r="I1204" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1204" t="n">
         <v>0</v>
       </c>
       <c r="K1204" t="n">
-        <v>16</v>
-      </c>
-      <c r="M1204" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>54</v>
+      </c>
+      <c r="L1204" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1204" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1204" t="inlineStr"/>
+      <c r="O1204" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1204" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY09DETCLE-DETJDUREN0-3</t>
+          <t>KXNBAREB-26MAY09OKCLAL-OKCIHARTENSTEIN55-9</t>
         </is>
       </c>
     </row>
@@ -77297,16 +77521,16 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1205" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1205" t="inlineStr">
         <is>
@@ -77314,13 +77538,13 @@
         </is>
       </c>
       <c r="F1205" t="n">
-        <v>24.2</v>
+        <v>3</v>
       </c>
       <c r="G1205" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H1205" t="n">
-        <v>5.2</v>
+        <v>-2</v>
       </c>
       <c r="I1205" t="inlineStr">
         <is>
@@ -77331,17 +77555,25 @@
         <v>0</v>
       </c>
       <c r="K1205" t="n">
-        <v>19</v>
-      </c>
-      <c r="M1205" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L1205" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1205" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1205" t="inlineStr"/>
+      <c r="O1205" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1205" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09DETCLE-CLEJHARDEN1-8</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-OKCIHARTENSTEIN55-20</t>
         </is>
       </c>
     </row>
@@ -77353,30 +77585,30 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Jake Laravia</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1206" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1206" t="n">
         <v>3</v>
       </c>
-      <c r="E1206" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F1206" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G1206" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H1206" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="I1206" t="inlineStr">
         <is>
@@ -77387,17 +77619,17 @@
         <v>0</v>
       </c>
       <c r="K1206" t="n">
-        <v>16</v>
-      </c>
-      <c r="M1206" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>3</v>
+      </c>
+      <c r="M1206" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="N1206" t="inlineStr"/>
       <c r="P1206" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09DETCLE-CLEJHARDEN1-3</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-LALJLARAVIA12-20</t>
         </is>
       </c>
     </row>
@@ -77409,16 +77641,16 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1207" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E1207" t="inlineStr">
         <is>
@@ -77426,13 +77658,13 @@
         </is>
       </c>
       <c r="F1207" t="n">
-        <v>29.1</v>
+        <v>10.9</v>
       </c>
       <c r="G1207" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H1207" t="n">
-        <v>-7.9</v>
+        <v>4.9</v>
       </c>
       <c r="I1207" t="inlineStr">
         <is>
@@ -77443,17 +77675,25 @@
         <v>0</v>
       </c>
       <c r="K1207" t="n">
-        <v>37</v>
-      </c>
-      <c r="M1207" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>6</v>
+      </c>
+      <c r="L1207" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1207" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1207" t="inlineStr"/>
+      <c r="O1207" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1207" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09DETCLE-CLEJHARDEN1-8</t>
+          <t>KXNBAPTS-26MAY09DETCLE-DETJDUREN0-25</t>
         </is>
       </c>
     </row>
@@ -77465,16 +77705,16 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D1208" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E1208" t="inlineStr">
         <is>
@@ -77485,31 +77725,39 @@
         <v>3</v>
       </c>
       <c r="G1208" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H1208" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="I1208" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1208" t="n">
         <v>0</v>
       </c>
       <c r="K1208" t="n">
-        <v>11</v>
-      </c>
-      <c r="M1208" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L1208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1208" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1208" t="inlineStr"/>
+      <c r="O1208" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1208" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-CLEJHARDEN1-30</t>
+          <t>KXNBAAST-26MAY09DETCLE-DETJDUREN0-8</t>
         </is>
       </c>
     </row>
@@ -77521,16 +77769,16 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1209" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E1209" t="inlineStr">
         <is>
@@ -77538,34 +77786,42 @@
         </is>
       </c>
       <c r="F1209" t="n">
-        <v>28.4</v>
+        <v>81.8</v>
       </c>
       <c r="G1209" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="H1209" t="n">
-        <v>17.4</v>
+        <v>-2.2</v>
       </c>
       <c r="I1209" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J1209" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K1209" t="n">
-        <v>11</v>
-      </c>
-      <c r="M1209" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>84</v>
+      </c>
+      <c r="L1209" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1209" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1209" t="inlineStr"/>
+      <c r="O1209" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1209" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-CLEJALLEN31-20</t>
+          <t>KXNBAREB-26MAY09DETCLE-DETJDUREN0-8</t>
         </is>
       </c>
     </row>
@@ -77577,7 +77833,7 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="C1210" t="inlineStr">
@@ -77594,13 +77850,13 @@
         </is>
       </c>
       <c r="F1210" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="G1210" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H1210" t="n">
-        <v>2</v>
+        <v>-10.8</v>
       </c>
       <c r="I1210" t="inlineStr">
         <is>
@@ -77611,17 +77867,25 @@
         <v>0</v>
       </c>
       <c r="K1210" t="n">
-        <v>17</v>
-      </c>
-      <c r="M1210" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>16</v>
+      </c>
+      <c r="L1210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1210" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1210" t="inlineStr"/>
+      <c r="O1210" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1210" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY09DETCLE-CLEJALLEN31-3</t>
+          <t>KXNBABLK-26MAY09DETCLE-DETJDUREN0-3</t>
         </is>
       </c>
     </row>
@@ -77633,7 +77897,7 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
@@ -77650,13 +77914,13 @@
         </is>
       </c>
       <c r="F1211" t="n">
-        <v>48.9</v>
+        <v>24.2</v>
       </c>
       <c r="G1211" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H1211" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="I1211" t="inlineStr">
         <is>
@@ -77667,17 +77931,25 @@
         <v>0</v>
       </c>
       <c r="K1211" t="n">
-        <v>47</v>
-      </c>
-      <c r="M1211" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>19</v>
+      </c>
+      <c r="L1211" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1211" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1211" t="inlineStr"/>
+      <c r="O1211" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1211" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09DETCLE-CLEJALLEN31-8</t>
+          <t>KXNBAREB-26MAY09DETCLE-CLEJHARDEN1-8</t>
         </is>
       </c>
     </row>
@@ -77689,16 +77961,16 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D1212" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E1212" t="inlineStr">
         <is>
@@ -77706,13 +77978,13 @@
         </is>
       </c>
       <c r="F1212" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="G1212" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H1212" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="I1212" t="inlineStr">
         <is>
@@ -77723,17 +77995,25 @@
         <v>0</v>
       </c>
       <c r="K1212" t="n">
-        <v>6</v>
-      </c>
-      <c r="M1212" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>16</v>
+      </c>
+      <c r="L1212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1212" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1212" t="inlineStr"/>
+      <c r="O1212" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1212" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-CLEJTYSON20-20</t>
+          <t>KXNBASTL-26MAY09DETCLE-CLEJHARDEN1-3</t>
         </is>
       </c>
     </row>
@@ -77745,16 +78025,16 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D1213" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1213" t="inlineStr">
         <is>
@@ -77762,34 +78042,42 @@
         </is>
       </c>
       <c r="F1213" t="n">
-        <v>24.4</v>
+        <v>29.1</v>
       </c>
       <c r="G1213" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H1213" t="n">
-        <v>10.4</v>
+        <v>-7.9</v>
       </c>
       <c r="I1213" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1213" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K1213" t="n">
-        <v>14</v>
-      </c>
-      <c r="M1213" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>37</v>
+      </c>
+      <c r="L1213" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1213" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1213" t="inlineStr"/>
+      <c r="O1213" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1213" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09OKCLAL-LALLJAMES23-3</t>
+          <t>KXNBAAST-26MAY09DETCLE-CLEJHARDEN1-8</t>
         </is>
       </c>
     </row>
@@ -77801,16 +78089,16 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1214" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E1214" t="inlineStr">
         <is>
@@ -77818,34 +78106,42 @@
         </is>
       </c>
       <c r="F1214" t="n">
-        <v>33.1</v>
+        <v>3</v>
       </c>
       <c r="G1214" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H1214" t="n">
-        <v>-2.9</v>
+        <v>-8</v>
       </c>
       <c r="I1214" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J1214" t="n">
         <v>0</v>
       </c>
       <c r="K1214" t="n">
-        <v>36</v>
-      </c>
-      <c r="M1214" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>11</v>
+      </c>
+      <c r="L1214" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1214" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1214" t="inlineStr"/>
+      <c r="O1214" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1214" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09OKCLAL-LALLJAMES23-8</t>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEJHARDEN1-30</t>
         </is>
       </c>
     </row>
@@ -77857,16 +78153,16 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1215" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E1215" t="inlineStr">
         <is>
@@ -77874,34 +78170,44 @@
         </is>
       </c>
       <c r="F1215" t="n">
-        <v>3.7</v>
+        <v>28.4</v>
       </c>
       <c r="G1215" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H1215" t="n">
-        <v>-9.300000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="I1215" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1215" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K1215" t="n">
-        <v>13</v>
-      </c>
-      <c r="M1215" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1215" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L1215" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1215" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1215" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="O1215" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1215" t="inlineStr">
         <is>
-          <t>KXNBABLK-26MAY09OKCLAL-LALLJAMES23-3</t>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEJALLEN31-20</t>
         </is>
       </c>
     </row>
@@ -77913,16 +78219,16 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D1216" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1216" t="inlineStr">
         <is>
@@ -77930,34 +78236,42 @@
         </is>
       </c>
       <c r="F1216" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G1216" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H1216" t="n">
-        <v>-15</v>
+        <v>2</v>
       </c>
       <c r="I1216" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1216" t="n">
         <v>0</v>
       </c>
       <c r="K1216" t="n">
-        <v>52</v>
-      </c>
-      <c r="M1216" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>17</v>
+      </c>
+      <c r="L1216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1216" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1216" t="inlineStr"/>
+      <c r="O1216" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1216" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09OKCLAL-LALLJAMES23-8</t>
+          <t>KXNBABLK-26MAY09DETCLE-CLEJALLEN31-3</t>
         </is>
       </c>
     </row>
@@ -77969,16 +78283,16 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1217" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1217" t="inlineStr">
         <is>
@@ -77986,34 +78300,42 @@
         </is>
       </c>
       <c r="F1217" t="n">
-        <v>6.6</v>
+        <v>48.9</v>
       </c>
       <c r="G1217" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H1217" t="n">
-        <v>-27.4</v>
+        <v>1.9</v>
       </c>
       <c r="I1217" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1217" t="n">
         <v>0</v>
       </c>
       <c r="K1217" t="n">
-        <v>34</v>
-      </c>
-      <c r="M1217" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>47</v>
+      </c>
+      <c r="L1217" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1217" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1217" t="inlineStr"/>
+      <c r="O1217" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1217" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09OKCLAL-OKCLDORT5-3</t>
+          <t>KXNBAREB-26MAY09DETCLE-CLEJALLEN31-8</t>
         </is>
       </c>
     </row>
@@ -78025,16 +78347,16 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1218" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1218" t="inlineStr">
         <is>
@@ -78045,10 +78367,10 @@
         <v>3</v>
       </c>
       <c r="G1218" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="H1218" t="n">
-        <v>-64</v>
+        <v>-3</v>
       </c>
       <c r="I1218" t="inlineStr">
         <is>
@@ -78059,17 +78381,25 @@
         <v>0</v>
       </c>
       <c r="K1218" t="n">
-        <v>67</v>
-      </c>
-      <c r="M1218" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>6</v>
+      </c>
+      <c r="L1218" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1218" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1218" t="inlineStr"/>
+      <c r="O1218" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1218" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09OKCLAL-OKCLDORT5-8</t>
+          <t>KXNBAPTS-26MAY09DETCLE-CLEJTYSON20-20</t>
         </is>
       </c>
     </row>
@@ -78081,7 +78411,7 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="C1219" t="inlineStr">
@@ -78098,13 +78428,13 @@
         </is>
       </c>
       <c r="F1219" t="n">
-        <v>25.7</v>
+        <v>24.4</v>
       </c>
       <c r="G1219" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H1219" t="n">
-        <v>3.7</v>
+        <v>10.4</v>
       </c>
       <c r="I1219" t="inlineStr">
         <is>
@@ -78112,20 +78442,30 @@
         </is>
       </c>
       <c r="J1219" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K1219" t="n">
-        <v>22</v>
-      </c>
-      <c r="M1219" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1219" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="L1219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1219" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1219" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="O1219" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1219" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09OKCLAL-LALMSMART36-3</t>
+          <t>KXNBASTL-26MAY09OKCLAL-LALLJAMES23-3</t>
         </is>
       </c>
     </row>
@@ -78137,12 +78477,12 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="D1220" t="n">
@@ -78154,34 +78494,42 @@
         </is>
       </c>
       <c r="F1220" t="n">
-        <v>7.7</v>
+        <v>33.1</v>
       </c>
       <c r="G1220" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H1220" t="n">
-        <v>0.7</v>
+        <v>-2.9</v>
       </c>
       <c r="I1220" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="J1220" t="n">
         <v>0</v>
       </c>
       <c r="K1220" t="n">
-        <v>7</v>
-      </c>
-      <c r="M1220" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>36</v>
+      </c>
+      <c r="L1220" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1220" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1220" t="inlineStr"/>
+      <c r="O1220" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1220" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09OKCLAL-LALMSMART36-8</t>
+          <t>KXNBAREB-26MAY09OKCLAL-LALLJAMES23-8</t>
         </is>
       </c>
     </row>
@@ -78193,16 +78541,16 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="D1221" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1221" t="inlineStr">
         <is>
@@ -78210,34 +78558,42 @@
         </is>
       </c>
       <c r="F1221" t="n">
-        <v>40</v>
+        <v>3.7</v>
       </c>
       <c r="G1221" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="H1221" t="n">
-        <v>-1.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I1221" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1221" t="n">
         <v>0</v>
       </c>
       <c r="K1221" t="n">
-        <v>41</v>
-      </c>
-      <c r="M1221" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>13</v>
+      </c>
+      <c r="L1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1221" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1221" t="inlineStr"/>
+      <c r="O1221" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1221" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+          <t>KXNBABLK-26MAY09OKCLAL-LALLJAMES23-3</t>
         </is>
       </c>
     </row>
@@ -78249,12 +78605,12 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="D1222" t="n">
@@ -78266,34 +78622,42 @@
         </is>
       </c>
       <c r="F1222" t="n">
-        <v>4.3</v>
+        <v>37</v>
       </c>
       <c r="G1222" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1222" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1222" t="n">
+        <v>52</v>
+      </c>
+      <c r="L1222" t="n">
         <v>8</v>
       </c>
-      <c r="H1222" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="I1222" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="J1222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1222" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1222" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M1222" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1222" t="inlineStr"/>
+      <c r="O1222" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1222" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+          <t>KXNBAAST-26MAY09OKCLAL-LALLJAMES23-8</t>
         </is>
       </c>
     </row>
@@ -78305,16 +78669,16 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="D1223" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E1223" t="inlineStr">
         <is>
@@ -78322,17 +78686,17 @@
         </is>
       </c>
       <c r="F1223" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="G1223" t="n">
         <v>19</v>
       </c>
       <c r="H1223" t="n">
-        <v>-11</v>
+        <v>-15.2</v>
       </c>
       <c r="I1223" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J1223" t="n">
@@ -78341,15 +78705,23 @@
       <c r="K1223" t="n">
         <v>19</v>
       </c>
-      <c r="M1223" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1223" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1223" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1223" t="inlineStr"/>
+      <c r="O1223" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1223" t="inlineStr">
         <is>
-          <t>KXNBASTL-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-3</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-LALLJAMES23-30</t>
         </is>
       </c>
     </row>
@@ -78361,16 +78733,16 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D1224" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1224" t="inlineStr">
         <is>
@@ -78378,34 +78750,42 @@
         </is>
       </c>
       <c r="F1224" t="n">
-        <v>36.6</v>
+        <v>6.6</v>
       </c>
       <c r="G1224" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1224" t="n">
-        <v>4.6</v>
+        <v>-27.4</v>
       </c>
       <c r="I1224" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1224" t="n">
         <v>0</v>
       </c>
       <c r="K1224" t="n">
-        <v>32</v>
-      </c>
-      <c r="M1224" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>34</v>
+      </c>
+      <c r="L1224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1224" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1224" t="inlineStr"/>
+      <c r="O1224" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1224" t="inlineStr">
         <is>
-          <t>KXNBAREB-26MAY09DETCLE-DETTHARRIS12-8</t>
+          <t>KXNBASTL-26MAY09OKCLAL-OKCLDORT5-3</t>
         </is>
       </c>
     </row>
@@ -78417,7 +78797,7 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="C1225" t="inlineStr">
@@ -78437,10 +78817,10 @@
         <v>3</v>
       </c>
       <c r="G1225" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="H1225" t="n">
-        <v>-2</v>
+        <v>-64</v>
       </c>
       <c r="I1225" t="inlineStr">
         <is>
@@ -78451,17 +78831,25 @@
         <v>0</v>
       </c>
       <c r="K1225" t="n">
-        <v>5</v>
-      </c>
-      <c r="M1225" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>67</v>
+      </c>
+      <c r="L1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1225" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1225" t="inlineStr"/>
+      <c r="O1225" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1225" t="inlineStr">
         <is>
-          <t>KXNBAAST-26MAY09DETCLE-DETTHARRIS12-8</t>
+          <t>KXNBAAST-26MAY09OKCLAL-OKCLDORT5-8</t>
         </is>
       </c>
     </row>
@@ -78473,7 +78861,7 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="C1226" t="inlineStr">
@@ -78482,7 +78870,7 @@
         </is>
       </c>
       <c r="D1226" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E1226" t="inlineStr">
         <is>
@@ -78490,34 +78878,42 @@
         </is>
       </c>
       <c r="F1226" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1226" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="I1226" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J1226" t="n">
         <v>0</v>
       </c>
       <c r="K1226" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1226" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>5</v>
+      </c>
+      <c r="L1226" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1226" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1226" t="inlineStr"/>
+      <c r="O1226" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="P1226" t="inlineStr">
         <is>
-          <t>KXNBAPTS-26MAY09DETCLE-DETTHARRIS12-30</t>
+          <t>KXNBAPTS-26MAY09OKCLAL-OKCLDORT5-20</t>
         </is>
       </c>
     </row>
@@ -78529,7 +78925,7 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="C1227" t="inlineStr">
@@ -78546,32 +78942,744 @@
         </is>
       </c>
       <c r="F1227" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1227" t="n">
+        <v>22</v>
+      </c>
+      <c r="L1227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1227" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1227" t="inlineStr"/>
+      <c r="O1227" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1227" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09OKCLAL-LALMSMART36-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1228" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1228" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1228" t="n">
+        <v>7</v>
+      </c>
+      <c r="L1228" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1228" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1228" t="inlineStr"/>
+      <c r="O1228" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1228" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09OKCLAL-LALMSMART36-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1229" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1229" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1229" t="n">
+        <v>13</v>
+      </c>
+      <c r="L1229" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1229" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1229" t="inlineStr"/>
+      <c r="O1229" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1229" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09OKCLAL-LALMSMART36-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1230" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1230" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1230" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1230" t="n">
+        <v>19</v>
+      </c>
+      <c r="L1230" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1230" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N1230" t="inlineStr"/>
+      <c r="O1230" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1230" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09OKCLAL-LALRHACHIMURA28-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1231" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1231" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1231" t="n">
+        <v>41</v>
+      </c>
+      <c r="L1231" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1231" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="N1231" t="inlineStr"/>
+      <c r="O1231" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1231" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1232" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1232" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1232" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1232" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1232" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1232" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1232" t="inlineStr"/>
+      <c r="O1232" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1232" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1233" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1233" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1233" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1233" t="n">
+        <v>19</v>
+      </c>
+      <c r="L1233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1233" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1233" t="inlineStr"/>
+      <c r="O1233" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1233" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1234" t="n">
+        <v>40</v>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1234" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1234" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1234" t="n">
+        <v>11</v>
+      </c>
+      <c r="L1234" t="n">
+        <v>23</v>
+      </c>
+      <c r="M1234" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1234" t="inlineStr"/>
+      <c r="O1234" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1234" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09OKCLAL-OKCSGILGEOUSALEXANDER2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1235" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1235" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1235" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1235" t="n">
+        <v>32</v>
+      </c>
+      <c r="L1235" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1235" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1235" t="inlineStr"/>
+      <c r="O1235" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1235" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY09DETCLE-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1236" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1236" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1236" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1236" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1236" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1236" t="inlineStr"/>
+      <c r="O1236" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1236" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY09DETCLE-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1237" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1237" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1237" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1237" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1237" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1237" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1237" t="inlineStr"/>
+      <c r="O1237" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1237" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY09DETCLE-DETTHARRIS12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1238" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1238" t="n">
         <v>12.6</v>
       </c>
-      <c r="G1227" t="n">
+      <c r="G1238" t="n">
         <v>18</v>
       </c>
-      <c r="H1227" t="n">
+      <c r="H1238" t="n">
         <v>-5.4</v>
       </c>
-      <c r="I1227" t="inlineStr">
+      <c r="I1238" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="J1227" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1227" t="n">
+      <c r="J1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1238" t="n">
         <v>18</v>
       </c>
-      <c r="M1227" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1227" t="inlineStr"/>
-      <c r="P1227" t="inlineStr">
+      <c r="L1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1238" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1238" t="inlineStr"/>
+      <c r="O1238" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="P1238" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY09DETCLE-DETTHARRIS12-3</t>
         </is>
@@ -79214,25 +80322,29 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>62</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
         <v>51</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.164</v>
+      </c>
       <c r="H20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>6.09</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -79295,19 +80407,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" t="n">
-        <v>0.15</v>
+        <v>0.156</v>
       </c>
       <c r="F2" t="n">
-        <v>7.25</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="3">
@@ -79323,10 +80435,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>0.189</v>
+        <v>0.171</v>
       </c>
       <c r="F3" t="n">
         <v>-2.38</v>
@@ -79342,16 +80454,16 @@
         <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
-        <v>0.243</v>
+        <v>0.268</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.45</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="5">
@@ -79367,10 +80479,10 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>0.257</v>
+        <v>0.231</v>
       </c>
       <c r="F5" t="n">
         <v>-2.64</v>
@@ -79386,13 +80498,13 @@
         <v>37</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -79411,10 +80523,10 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>0.242</v>
+        <v>0.216</v>
       </c>
       <c r="F7" t="n">
         <v>13.94</v>
@@ -79433,57 +80545,57 @@
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>0.355</v>
+        <v>0.314</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.19</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>0.065</v>
+        <v>0.161</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.148</v>
+        <v>0.065</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="11">
@@ -79543,10 +80655,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12</v>
+        <v>0.103</v>
       </c>
       <c r="F13" t="n">
         <v>4.71</v>
@@ -79555,7 +80667,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -79565,35 +80677,35 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>59.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="16">
@@ -79603,16 +80715,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -79625,19 +80737,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
         <v>0.333</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="18">
@@ -79819,64 +80931,64 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>19</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>0.333</v>
+        <v>0.158</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>18</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -79885,45 +80997,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jaden Mcdaniels</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>17</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>0.118</v>
+        <v>0.294</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>0.267</v>
+        <v>0.118</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="31">
@@ -80093,7 +81205,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -80127,29 +81239,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="F40" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -80159,54 +81271,54 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.091</v>
+        <v>0.143</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5600000000000001</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>0.182</v>
+        <v>0.091</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>11</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -80215,20 +81327,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>11</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E44" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -80237,20 +81349,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>11</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>0.273</v>
+        <v>0.091</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -80259,20 +81371,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>11</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>0.091</v>
+        <v>0.273</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -80281,20 +81393,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>11</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2</v>
+        <v>0.091</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -80369,29 +81481,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F51" t="n">
-        <v>-7.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -80407,70 +81519,70 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.84</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>-4.08</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>10</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>10</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -80479,45 +81591,45 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>9</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="58">
@@ -80567,7 +81679,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -80577,7 +81689,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -80589,17 +81701,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -80611,17 +81723,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Jake Laravia</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
         <v>6</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -80633,7 +81745,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -80643,7 +81755,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -80655,7 +81767,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jake Laravia</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -81306,13 +82418,13 @@
         <v>225</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E2" t="n">
-        <v>0.105</v>
+        <v>0.117</v>
       </c>
       <c r="F2" t="n">
         <v>-11.19</v>
@@ -81331,10 +82443,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>0.151</v>
+        <v>0.141</v>
       </c>
       <c r="F3" t="n">
         <v>-1.44</v>
@@ -81347,19 +82459,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="E4" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="F4" t="n">
-        <v>81.54000000000001</v>
+        <v>76.41</v>
       </c>
     </row>
     <row r="5">
@@ -81372,16 +82484,16 @@
         <v>305</v>
       </c>
       <c r="C5" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D5" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E5" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="F5" t="n">
-        <v>-30.76</v>
+        <v>-18.14</v>
       </c>
     </row>
     <row r="6">
@@ -81397,13 +82509,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E6" t="n">
-        <v>0.157</v>
+        <v>0.148</v>
       </c>
       <c r="F6" t="n">
-        <v>6.72</v>
+        <v>5.32</v>
       </c>
     </row>
   </sheetData>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1238"/>
+  <dimension ref="A1:P1365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -79685,6 +79691,7118 @@
         </is>
       </c>
     </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1239" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1239" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1239" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1239" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1239" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1239" t="inlineStr"/>
+      <c r="P1239" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-MINAEDWARDS5-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1240" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1240" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1240" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1240" t="n">
+        <v>28</v>
+      </c>
+      <c r="M1240" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1240" t="inlineStr"/>
+      <c r="P1240" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10SASMIN-MINAEDWARDS5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1241" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1241" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1241" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1241" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1241" t="inlineStr"/>
+      <c r="P1241" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10SASMIN-MINAEDWARDS5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1242" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1242" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1242" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1242" t="n">
+        <v>14</v>
+      </c>
+      <c r="M1242" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1242" t="inlineStr"/>
+      <c r="P1242" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10SASMIN-MINAEDWARDS5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1243" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1243" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1243" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1243" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1243" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1243" t="inlineStr"/>
+      <c r="P1243" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-DETATHOMPSON9-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1244" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1244" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1244" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1244" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1244" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1244" t="inlineStr"/>
+      <c r="P1244" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11DETCLE-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1245" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1245" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1245" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1245" t="n">
+        <v>45</v>
+      </c>
+      <c r="M1245" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1245" t="inlineStr"/>
+      <c r="P1245" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1246" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1246" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1246" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1246" t="n">
+        <v>35</v>
+      </c>
+      <c r="M1246" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1246" t="inlineStr"/>
+      <c r="P1246" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11DETCLE-DETATHOMPSON9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Austin Reaves</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1247" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1247" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1247" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1247" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1247" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1247" t="inlineStr"/>
+      <c r="P1247" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-LALAREAVES15-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Austin Reaves</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1248" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1248" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1248" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1248" t="n">
+        <v>35</v>
+      </c>
+      <c r="M1248" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1248" t="inlineStr"/>
+      <c r="P1248" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11OKCLAL-LALAREAVES15-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Ayo Dosunmu</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1249" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1249" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1249" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1249" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1249" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1249" t="inlineStr"/>
+      <c r="P1249" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-MINADOSUNMU13-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1250" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1250" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1250" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1250" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1250" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1250" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1250" t="inlineStr"/>
+      <c r="P1250" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1251" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1251" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1251" t="n">
+        <v>56</v>
+      </c>
+      <c r="M1251" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1251" t="inlineStr"/>
+      <c r="P1251" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11DETCLE-DETCCUNNINGHAM2-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1252" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1252" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1252" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1252" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1252" t="inlineStr"/>
+      <c r="P1252" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11DETCLE-DETCCUNNINGHAM2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1253" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1253" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1253" t="n">
+        <v>20</v>
+      </c>
+      <c r="M1253" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1253" t="inlineStr"/>
+      <c r="P1253" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-DETCCUNNINGHAM2-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Cason Wallace</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1254" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1254" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1254" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1254" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1254" t="inlineStr"/>
+      <c r="P1254" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-OKCCWALLACE22-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1255" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1255" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>58</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1255" t="n">
+        <v>58</v>
+      </c>
+      <c r="M1255" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1255" t="inlineStr"/>
+      <c r="P1255" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11OKCLAL-OKCCHOLMGREN7-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1256" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1256" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1256" t="n">
+        <v>30</v>
+      </c>
+      <c r="M1256" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1256" t="inlineStr"/>
+      <c r="P1256" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY11OKCLAL-OKCCHOLMGREN7-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1257" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1257" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1257" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1257" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1257" t="inlineStr"/>
+      <c r="P1257" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-OKCCHOLMGREN7-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>De'Aaron Fox</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1258" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1258" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1258" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1258" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1258" t="inlineStr"/>
+      <c r="P1258" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10SASMIN-SASDFOX4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>De'Aaron Fox</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1259" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1259" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1259" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1259" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1259" t="inlineStr"/>
+      <c r="P1259" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-SASDFOX4-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>De'Aaron Fox</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1260" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1260" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1260" t="n">
+        <v>22</v>
+      </c>
+      <c r="M1260" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1260" t="inlineStr"/>
+      <c r="P1260" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10SASMIN-SASDFOX4-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1261" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1261" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1261" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1261" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1261" t="inlineStr"/>
+      <c r="P1261" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-LALDAYTON5-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1262" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1262" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1262" t="n">
+        <v>54</v>
+      </c>
+      <c r="M1262" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1262" t="inlineStr"/>
+      <c r="P1262" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11OKCLAL-LALDAYTON5-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Deandre Ayton</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1263" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1263" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1263" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1263" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1263" t="inlineStr"/>
+      <c r="P1263" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY11OKCLAL-LALDAYTON5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1264" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1264" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1264" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1264" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1264" t="inlineStr"/>
+      <c r="P1264" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10SASMIN-SASDVASSELL24-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1265" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1265" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1265" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1265" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1265" t="inlineStr"/>
+      <c r="P1265" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-SASDVASSELL24-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1266" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1266" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1266" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1266" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1266" t="inlineStr"/>
+      <c r="P1266" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1267" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1267" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1267" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1267" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1267" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1267" t="inlineStr"/>
+      <c r="P1267" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11DETCLE-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1268" t="n">
+        <v>40</v>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1268" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1268" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1268" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1268" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1268" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1268" t="inlineStr"/>
+      <c r="P1268" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-CLEDMITCHELL45-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1269" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1269" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G1269" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1269" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1269" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1269" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1269" t="inlineStr"/>
+      <c r="P1269" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11DETCLE-CLEDMITCHELL45-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1270" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1270" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1270" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1270" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1270" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1270" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1270" t="inlineStr"/>
+      <c r="P1270" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-DETDROBINSON55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1271" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1271" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G1271" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1271" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1271" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1271" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1271" t="inlineStr"/>
+      <c r="P1271" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-SASDHARPER2-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1272" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1272" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G1272" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1272" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1272" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1272" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1272" t="inlineStr"/>
+      <c r="P1272" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-CLEEMOBLEY4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1273" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1273" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1273" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1273" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1273" t="inlineStr"/>
+      <c r="P1273" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY11DETCLE-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1274" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1274" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G1274" t="n">
+        <v>46</v>
+      </c>
+      <c r="H1274" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1274" t="n">
+        <v>46</v>
+      </c>
+      <c r="M1274" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1274" t="inlineStr"/>
+      <c r="P1274" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-CLEEMOBLEY4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1275" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1275" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G1275" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1275" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1275" t="n">
+        <v>27</v>
+      </c>
+      <c r="M1275" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1275" t="inlineStr"/>
+      <c r="P1275" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11DETCLE-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1276" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1276" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1276" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1276" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1276" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1276" t="inlineStr"/>
+      <c r="P1276" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-OKCIHARTENSTEIN55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Isaiah Hartenstein</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1277" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1277" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G1277" t="n">
+        <v>68</v>
+      </c>
+      <c r="H1277" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1277" t="n">
+        <v>68</v>
+      </c>
+      <c r="M1277" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1277" t="inlineStr"/>
+      <c r="P1277" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11OKCLAL-OKCIHARTENSTEIN55-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1278" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1278" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G1278" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1278" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1278" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1278" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1278" t="inlineStr"/>
+      <c r="P1278" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10SASMIN-MINJMCDANIELS3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1279" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1279" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G1279" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1279" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1279" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1279" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1279" t="inlineStr"/>
+      <c r="P1279" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-MINJMCDANIELS3-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1280" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1280" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1280" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1280" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1280" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1280" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1280" t="inlineStr"/>
+      <c r="P1280" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10SASMIN-MINJMCDANIELS3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Jaden Mcdaniels</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1281" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1281" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G1281" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1281" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1281" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1281" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1281" t="inlineStr"/>
+      <c r="P1281" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10SASMIN-MINJMCDANIELS3-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1282" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1282" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G1282" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1282" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1282" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1282" t="n">
+        <v>30</v>
+      </c>
+      <c r="M1282" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1282" t="inlineStr"/>
+      <c r="P1282" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10NYKPHI-NYKJBRUNSON11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1283" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1283" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G1283" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1283" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1283" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1283" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1283" t="inlineStr"/>
+      <c r="P1283" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-NYKJBRUNSON11-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1284" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1284" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G1284" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1284" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1284" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1284" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1284" t="inlineStr"/>
+      <c r="P1284" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-NYKJBRUNSON11-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1285" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1285" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G1285" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1285" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1285" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1285" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1285" t="inlineStr"/>
+      <c r="P1285" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-NYKJBRUNSON11-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1286" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1286" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G1286" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1286" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1286" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1286" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1286" t="inlineStr"/>
+      <c r="P1286" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-DETJDUREN0-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1287" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1287" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1287" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1287" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1287" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1287" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1287" t="inlineStr"/>
+      <c r="P1287" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11DETCLE-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1288" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1288" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1288" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1288" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1288" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1288" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1288" t="inlineStr"/>
+      <c r="P1288" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-DETJDUREN0-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1289" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1289" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G1289" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1289" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1289" t="n">
+        <v>24</v>
+      </c>
+      <c r="M1289" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1289" t="inlineStr"/>
+      <c r="P1289" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY11DETCLE-DETJDUREN0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1290" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1290" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G1290" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1290" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1290" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1290" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1290" t="inlineStr"/>
+      <c r="P1290" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1291" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1291" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G1291" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1291" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1291" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1291" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1291" t="inlineStr"/>
+      <c r="P1291" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11DETCLE-CLEJHARDEN1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1292" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1292" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1292" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1292" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1292" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1292" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1292" t="inlineStr"/>
+      <c r="P1292" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-CLEJHARDEN1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1293" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1293" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G1293" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1293" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1293" t="n">
+        <v>43</v>
+      </c>
+      <c r="M1293" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1293" t="inlineStr"/>
+      <c r="P1293" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11DETCLE-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1294" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1294" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G1294" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1294" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1294" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1294" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1294" t="inlineStr"/>
+      <c r="P1294" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-CLEJALLEN31-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1295" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1295" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G1295" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1295" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1295" t="n">
+        <v>22</v>
+      </c>
+      <c r="M1295" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1295" t="inlineStr"/>
+      <c r="P1295" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY11DETCLE-CLEJALLEN31-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1296" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1296" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G1296" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1296" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1296" t="n">
+        <v>48</v>
+      </c>
+      <c r="M1296" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1296" t="inlineStr"/>
+      <c r="P1296" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-CLEJALLEN31-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1297" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1297" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G1297" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1297" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1297" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1297" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1297" t="inlineStr"/>
+      <c r="P1297" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-PHIJEMBIID21-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1298" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1298" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1298" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1298" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1298" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1298" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1298" t="inlineStr"/>
+      <c r="P1298" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY10NYKPHI-PHIJEMBIID21-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1299" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1299" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1299" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1299" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1299" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1299" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1299" t="inlineStr"/>
+      <c r="P1299" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-PHIJEMBIID21-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1300" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1300" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1300" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1300" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1300" t="n">
+        <v>54</v>
+      </c>
+      <c r="M1300" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1300" t="inlineStr"/>
+      <c r="P1300" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-PHIJEMBIID21-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1301" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1301" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G1301" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1301" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1301" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1301" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1301" t="inlineStr"/>
+      <c r="P1301" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-NYKJHART3-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1302" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1302" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1302" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1302" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1302" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1302" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1302" t="inlineStr"/>
+      <c r="P1302" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-NYKJHART3-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1303" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1303" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1303" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1303" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1303" t="n">
+        <v>14</v>
+      </c>
+      <c r="M1303" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1303" t="inlineStr"/>
+      <c r="P1303" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10NYKPHI-NYKJHART3-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1304" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1304" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="G1304" t="n">
+        <v>57</v>
+      </c>
+      <c r="H1304" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1304" t="n">
+        <v>57</v>
+      </c>
+      <c r="M1304" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1304" t="inlineStr"/>
+      <c r="P1304" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-NYKJHART3-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Josh Hart</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1305" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1305" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1305" t="n">
+        <v>78</v>
+      </c>
+      <c r="H1305" t="n">
+        <v>-75</v>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1305" t="n">
+        <v>78</v>
+      </c>
+      <c r="M1305" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1305" t="inlineStr"/>
+      <c r="P1305" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY10NYKPHI-NYKJHART3-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1306" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1306" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1306" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1306" t="n">
+        <v>40</v>
+      </c>
+      <c r="M1306" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1306" t="inlineStr"/>
+      <c r="P1306" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10SASMIN-MINJRANDLE30-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1307" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1307" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1307" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1307" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1307" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1307" t="inlineStr"/>
+      <c r="P1307" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-MINJRANDLE30-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Julius Randle</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1308" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1308" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1308" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1308" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1308" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1308" t="inlineStr"/>
+      <c r="P1308" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10SASMIN-MINJRANDLE30-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1309" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1309" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1309" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1309" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1309" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1309" t="inlineStr"/>
+      <c r="P1309" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-NYKKTOWNS32-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1310" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1310" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1310" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1310" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1310" t="inlineStr"/>
+      <c r="P1310" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-NYKKTOWNS32-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1311" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1311" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1311" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1311" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1311" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1311" t="inlineStr"/>
+      <c r="P1311" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY10NYKPHI-NYKKTOWNS32-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1312" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1312" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1312" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1312" t="n">
+        <v>20</v>
+      </c>
+      <c r="M1312" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1312" t="inlineStr"/>
+      <c r="P1312" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-NYKKTOWNS32-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1313" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1313" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1313" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1313" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1313" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1313" t="inlineStr"/>
+      <c r="P1313" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-PHIKOUBRE9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1314" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1314" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1314" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1314" t="n">
+        <v>24</v>
+      </c>
+      <c r="M1314" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1314" t="inlineStr"/>
+      <c r="P1314" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-PHIKOUBRE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1315" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1315" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1315" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1315" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1315" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1315" t="inlineStr"/>
+      <c r="P1315" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-PHIKOUBRE9-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Kelly Oubre Jr.</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1316" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1316" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1316" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1316" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1316" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1316" t="inlineStr"/>
+      <c r="P1316" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10NYKPHI-PHIKOUBRE9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1317" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1317" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1317" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1317" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1317" t="inlineStr"/>
+      <c r="P1317" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11OKCLAL-LALLJAMES23-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1318" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1318" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1318" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1318" t="n">
+        <v>37</v>
+      </c>
+      <c r="M1318" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1318" t="inlineStr"/>
+      <c r="P1318" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11OKCLAL-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1319" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1319" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1319" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1319" t="n">
+        <v>52</v>
+      </c>
+      <c r="M1319" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1319" t="inlineStr"/>
+      <c r="P1319" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11OKCLAL-LALLJAMES23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1320" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1320" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1320" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1320" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1320" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1320" t="inlineStr"/>
+      <c r="P1320" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-LALLJAMES23-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Lebron James</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1321" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1321" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>88</v>
+      </c>
+      <c r="H1321" t="n">
+        <v>-85</v>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1321" t="n">
+        <v>88</v>
+      </c>
+      <c r="M1321" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1321" t="inlineStr"/>
+      <c r="P1321" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY11OKCLAL-LALLJAMES23-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1322" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1322" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1322" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1322" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1322" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1322" t="inlineStr"/>
+      <c r="P1322" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-OKCLDORT5-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1323" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1323" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1323" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1323" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1323" t="inlineStr"/>
+      <c r="P1323" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11OKCLAL-OKCLDORT5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Luguentz Dort</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1324" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1324" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1324" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1324" t="n">
+        <v>26</v>
+      </c>
+      <c r="M1324" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1324" t="inlineStr"/>
+      <c r="P1324" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11OKCLAL-OKCLDORT5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1325" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1325" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1325" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1325" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1325" t="inlineStr"/>
+      <c r="P1325" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11OKCLAL-LALMSMART36-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1326" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1326" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1326" t="n">
+        <v>23</v>
+      </c>
+      <c r="M1326" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1326" t="inlineStr"/>
+      <c r="P1326" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11OKCLAL-LALMSMART36-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Marcus Smart</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1327" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1327" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1327" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1327" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1327" t="inlineStr"/>
+      <c r="P1327" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-LALMSMART36-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1328" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1328" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1328" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1328" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1328" t="inlineStr"/>
+      <c r="P1328" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-NYKMBRIDGES25-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1329" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1329" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1329" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1329" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1329" t="inlineStr"/>
+      <c r="P1329" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-NYKMBRIDGES25-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1330" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1330" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1330" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1330" t="n">
+        <v>14</v>
+      </c>
+      <c r="M1330" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1330" t="inlineStr"/>
+      <c r="P1330" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-NYKMBRIDGES25-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Mikal Bridges</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1331" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1331" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>77</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>-74</v>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1331" t="n">
+        <v>77</v>
+      </c>
+      <c r="M1331" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1331" t="inlineStr"/>
+      <c r="P1331" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY10NYKPHI-NYKMBRIDGES25-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Mitchell Robinson</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1332" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1332" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1332" t="n">
+        <v>44</v>
+      </c>
+      <c r="M1332" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1332" t="inlineStr"/>
+      <c r="P1332" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-NYKMROBINSON23-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Mitchell Robinson</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1333" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1333" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1333" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1333" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1333" t="inlineStr"/>
+      <c r="P1333" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-NYKMROBINSON23-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1334" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1334" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1334" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1334" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1334" t="inlineStr"/>
+      <c r="P1334" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10NYKPHI-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1335" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1335" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1335" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1335" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1335" t="inlineStr"/>
+      <c r="P1335" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-PHIPGEORGE8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1336" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1336" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1336" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1336" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1336" t="inlineStr"/>
+      <c r="P1336" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-PHIPGEORGE8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Paul George</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1337" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1337" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1337" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1337" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1337" t="inlineStr"/>
+      <c r="P1337" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-PHIPGEORGE8-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Rudy Gobert</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1338" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1338" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1338" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1338" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1338" t="inlineStr"/>
+      <c r="P1338" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY10SASMIN-MINRGOBERT27-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Rudy Gobert</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1339" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1339" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1339" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1339" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1339" t="inlineStr"/>
+      <c r="P1339" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-MINRGOBERT27-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Rudy Gobert</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1340" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1340" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>78</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1340" t="n">
+        <v>78</v>
+      </c>
+      <c r="M1340" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1340" t="inlineStr"/>
+      <c r="P1340" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10SASMIN-MINRGOBERT27-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Rui Hachimura</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1341" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1341" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1341" t="n">
+        <v>24</v>
+      </c>
+      <c r="M1341" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1341" t="inlineStr"/>
+      <c r="P1341" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-LALRHACHIMURA28-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1342" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1342" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1342" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1342" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1342" t="inlineStr"/>
+      <c r="P1342" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1343" t="n">
+        <v>40</v>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1343" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1343" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1343" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1343" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1343" t="inlineStr"/>
+      <c r="P1343" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11OKCLAL-OKCSGILGEOUSALEXANDER2-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1344" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1344" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1344" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1344" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1344" t="inlineStr"/>
+      <c r="P1344" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11OKCLAL-OKCSGILGEOUSALEXANDER2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1345" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1345" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1345" t="n">
+        <v>37</v>
+      </c>
+      <c r="M1345" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1345" t="inlineStr"/>
+      <c r="P1345" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11OKCLAL-OKCSGILGEOUSALEXANDER2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1346" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1346" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1346" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1346" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1346" t="n">
+        <v>38</v>
+      </c>
+      <c r="M1346" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1346" t="inlineStr"/>
+      <c r="P1346" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10SASMIN-SASSCASTLE5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1347" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1347" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1347" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1347" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1347" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1347" t="inlineStr"/>
+      <c r="P1347" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-SASSCASTLE5-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1348" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1348" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1348" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1348" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1348" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1348" t="inlineStr"/>
+      <c r="P1348" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10SASMIN-SASSCASTLE5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Stephon Castle</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1349" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1349" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1349" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1349" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1349" t="inlineStr"/>
+      <c r="P1349" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10SASMIN-SASSCASTLE5-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1350" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1350" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1350" t="n">
+        <v>32</v>
+      </c>
+      <c r="M1350" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1350" t="inlineStr"/>
+      <c r="P1350" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY11DETCLE-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1351" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1351" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1351" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1351" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1351" t="inlineStr"/>
+      <c r="P1351" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY11DETCLE-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1352" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1352" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1352" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1352" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1352" t="inlineStr"/>
+      <c r="P1352" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY11DETCLE-DETTHARRIS12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1353" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1353" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1353" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1353" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1353" t="inlineStr"/>
+      <c r="P1353" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY11DETCLE-DETTHARRIS12-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1354" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1354" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1354" t="n">
+        <v>31</v>
+      </c>
+      <c r="M1354" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1354" t="inlineStr"/>
+      <c r="P1354" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10NYKPHI-PHITMAXEY0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1355" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1355" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1355" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1355" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1355" t="inlineStr"/>
+      <c r="P1355" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-PHITMAXEY0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1356" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1356" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1356" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1356" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1356" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1356" t="inlineStr"/>
+      <c r="P1356" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-PHITMAXEY0-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1357" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1357" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1357" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1357" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1357" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1357" t="inlineStr"/>
+      <c r="P1357" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10SASMIN-SASVWEMBANYAMA1-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1358" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1358" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1358" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1358" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1358" t="inlineStr"/>
+      <c r="P1358" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10SASMIN-SASVWEMBANYAMA1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1359" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1359" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1359" t="n">
+        <v>43</v>
+      </c>
+      <c r="M1359" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1359" t="inlineStr"/>
+      <c r="P1359" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY10SASMIN-SASVWEMBANYAMA1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1360" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1360" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1360" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1360" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1360" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1360" t="inlineStr"/>
+      <c r="P1360" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10SASMIN-SASVWEMBANYAMA1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1361" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1361" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1361" t="n">
+        <v>20</v>
+      </c>
+      <c r="M1361" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1361" t="inlineStr"/>
+      <c r="P1361" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10SASMIN-SASVWEMBANYAMA1-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1362" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1362" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1362" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1362" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1362" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1362" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1362" t="inlineStr"/>
+      <c r="P1362" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY10NYKPHI-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1363" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1363" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1363" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1363" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1363" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1363" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1363" t="inlineStr"/>
+      <c r="P1363" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY10NYKPHI-PHIVEDGECOMBE77-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1364" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1364" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1364" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1364" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1364" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1364" t="inlineStr"/>
+      <c r="P1364" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY10NYKPHI-PHIVEDGECOMBE77-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Vj Edgecombe</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1365" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1365" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1365" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1365" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1365" t="inlineStr"/>
+      <c r="P1365" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY10NYKPHI-PHIVEDGECOMBE77-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -79696,7 +86814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -80345,6 +87463,33 @@
       <c r="I20" t="n">
         <v>0.1</v>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>127</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>127</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -80407,7 +87552,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
@@ -80429,7 +87574,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -80451,7 +87596,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
@@ -80473,7 +87618,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
@@ -80495,7 +87640,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -80517,7 +87662,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
@@ -80539,7 +87684,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
@@ -80561,7 +87706,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
@@ -80583,7 +87728,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -80605,7 +87750,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -80627,7 +87772,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -80649,7 +87794,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -80671,7 +87816,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
@@ -80693,7 +87838,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
@@ -80715,7 +87860,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
@@ -80737,7 +87882,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
@@ -80755,45 +87900,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.29</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.74</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="20">
@@ -80821,177 +87966,177 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jayson Tatum</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.235</v>
+        <v>0.158</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>0.048</v>
+        <v>0.095</v>
       </c>
       <c r="F23" t="n">
-        <v>15.53</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1</v>
+        <v>0.235</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>20</v>
       </c>
-      <c r="C25" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" t="n">
-        <v>11</v>
-      </c>
       <c r="E25" t="n">
-        <v>0.45</v>
+        <v>0.048</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.44</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Jaden Mcdaniels</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>0.158</v>
+        <v>0.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.74</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="29">
@@ -81001,7 +88146,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C29" t="n">
         <v>5</v>
@@ -81019,42 +88164,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jaden Mcdaniels</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>0.118</v>
+        <v>0.154</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.74</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>0.125</v>
+        <v>0.308</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -81063,20 +88208,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rj Barrett</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -81085,42 +88230,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="F33" t="n">
-        <v>12.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>0.267</v>
+        <v>0.125</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -81129,86 +88274,86 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Rj Barrett</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E35" t="n">
-        <v>0.154</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>0.308</v>
+        <v>0.091</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>15</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
         <v>12</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-7.31</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -81217,20 +88362,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -81239,20 +88384,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>0.25</v>
+        <v>0.091</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -81261,64 +88406,64 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Og Anunoby</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>0.143</v>
+        <v>0.091</v>
       </c>
       <c r="F41" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>0.091</v>
+        <v>0.1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5600000000000001</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>0.182</v>
+        <v>0.25</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -81327,64 +88472,64 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -81393,20 +88538,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>0.091</v>
+        <v>0.083</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -81415,33 +88560,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tari Eason</t>
+          <t>Og Anunoby</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3</v>
+        <v>0.143</v>
       </c>
       <c r="F48" t="n">
-        <v>13.43</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jabari Smith Jr.</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C49" t="n">
         <v>2</v>
@@ -81459,20 +88604,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Reed Sheppard</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -81481,20 +88626,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>11</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
         <v>10</v>
       </c>
-      <c r="C51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" t="n">
-        <v>8</v>
-      </c>
       <c r="E51" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -81503,95 +88648,95 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Tari Eason</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F52" t="n">
-        <v>-7.97</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Jabari Smith Jr.</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Reed Sheppard</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>10</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>-4.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>10</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -81607,48 +88752,48 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -81657,20 +88802,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -81679,7 +88824,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -81723,20 +88868,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jake Laravia</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>7</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -81745,17 +88890,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -81767,11 +88912,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Jake Laravia</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -81789,7 +88934,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -81799,7 +88944,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -81811,7 +88956,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -81821,7 +88966,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -81833,42 +88978,42 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -81877,17 +89022,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mitchell Robinson</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -81899,29 +89044,29 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.05</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -81931,13 +89076,13 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="72">
@@ -81987,7 +89132,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Donte Divincenzo</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -81997,9 +89142,11 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
@@ -82007,21 +89154,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Donte Divincenzo</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
         <v>0</v>
       </c>
@@ -82415,7 +89560,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C2" t="n">
         <v>26</v>
@@ -82437,7 +89582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
@@ -82459,7 +89604,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="C4" t="n">
         <v>29</v>
@@ -82481,7 +89626,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="C5" t="n">
         <v>104</v>
@@ -82503,7 +89648,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="C6" t="n">
         <v>26</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1458"/>
+  <dimension ref="A1:P1490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -93787,6 +93793,1798 @@
         </is>
       </c>
     </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1459" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1459" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1459" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1459" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1459" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1459" t="inlineStr"/>
+      <c r="P1459" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETATHOMPSON9-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1460" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1460" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1460" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1460" t="n">
+        <v>47</v>
+      </c>
+      <c r="M1460" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1460" t="inlineStr"/>
+      <c r="P1460" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1461" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1461" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I1461" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1461" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1461" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1461" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1461" t="inlineStr"/>
+      <c r="P1461" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1462" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1462" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>87</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>-57.9</v>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1462" t="n">
+        <v>87</v>
+      </c>
+      <c r="M1462" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1462" t="inlineStr"/>
+      <c r="P1462" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-DETATHOMPSON9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1463" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1463" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1463" t="n">
+        <v>54</v>
+      </c>
+      <c r="M1463" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1463" t="inlineStr"/>
+      <c r="P1463" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETCCUNNINGHAM2-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1464" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1464" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1464" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1464" t="n">
+        <v>30</v>
+      </c>
+      <c r="M1464" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1464" t="inlineStr"/>
+      <c r="P1464" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1465" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1465" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1465" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1465" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1465" t="inlineStr"/>
+      <c r="P1465" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETCCUNNINGHAM2-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1466" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>87</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>-79.09999999999999</v>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1466" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1466" t="n">
+        <v>87</v>
+      </c>
+      <c r="M1466" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1466" t="inlineStr"/>
+      <c r="P1466" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-DETCCUNNINGHAM2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1467" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1467" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1467" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1467" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1467" t="inlineStr"/>
+      <c r="P1467" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1468" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1468" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1468" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1468" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1468" t="inlineStr"/>
+      <c r="P1468" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1469" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1469" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1469" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1469" t="n">
+        <v>25</v>
+      </c>
+      <c r="M1469" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1469" t="inlineStr"/>
+      <c r="P1469" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEDMITCHELL45-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1470" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>90</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>-86.59999999999999</v>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1470" t="n">
+        <v>90</v>
+      </c>
+      <c r="M1470" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1470" t="inlineStr"/>
+      <c r="P1470" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-CLEDMITCHELL45-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1471" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1471" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1471" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1471" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1471" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1471" t="inlineStr"/>
+      <c r="P1471" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETDROBINSON55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1472" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1472" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1472" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1472" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1472" t="inlineStr"/>
+      <c r="P1472" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEEMOBLEY4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1473" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1473" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1473" t="n">
+        <v>50</v>
+      </c>
+      <c r="M1473" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1473" t="inlineStr"/>
+      <c r="P1473" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEEMOBLEY4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1474" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>87</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>-75</v>
+      </c>
+      <c r="I1474" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1474" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1474" t="n">
+        <v>87</v>
+      </c>
+      <c r="M1474" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1474" t="inlineStr"/>
+      <c r="P1474" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1475" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>84</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>-77.5</v>
+      </c>
+      <c r="I1475" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1475" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1475" t="n">
+        <v>84</v>
+      </c>
+      <c r="M1475" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1475" t="inlineStr"/>
+      <c r="P1475" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY17CLEDET-CLEEMOBLEY4-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1476" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1476" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I1476" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1476" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1476" t="n">
+        <v>16</v>
+      </c>
+      <c r="M1476" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1476" t="inlineStr"/>
+      <c r="P1476" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETJDUREN0-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1477" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1477" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I1477" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1477" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1477" t="n">
+        <v>56</v>
+      </c>
+      <c r="M1477" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1477" t="inlineStr"/>
+      <c r="P1477" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETJDUREN0-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1478" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1478" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I1478" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1478" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1478" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1478" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1478" t="inlineStr"/>
+      <c r="P1478" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1479" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1479" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>89</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>-80.2</v>
+      </c>
+      <c r="I1479" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1479" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1479" t="n">
+        <v>89</v>
+      </c>
+      <c r="M1479" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1479" t="inlineStr"/>
+      <c r="P1479" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY17CLEDET-DETJDUREN0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1480" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1480" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I1480" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1480" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1480" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1480" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1480" t="inlineStr"/>
+      <c r="P1480" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1481" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1481" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I1481" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1481" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1481" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1481" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1481" t="inlineStr"/>
+      <c r="P1481" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEJHARDEN1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1482" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1482" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I1482" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1482" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1482" t="n">
+        <v>39</v>
+      </c>
+      <c r="M1482" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1482" t="inlineStr"/>
+      <c r="P1482" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1483" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1483" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>90</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>-70.8</v>
+      </c>
+      <c r="I1483" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1483" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1483" t="n">
+        <v>90</v>
+      </c>
+      <c r="M1483" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1483" t="inlineStr"/>
+      <c r="P1483" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-CLEJHARDEN1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1484" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1484" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1484" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1484" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1484" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1484" t="inlineStr"/>
+      <c r="P1484" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEJALLEN31-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1485" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1485" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1485" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1485" t="n">
+        <v>55</v>
+      </c>
+      <c r="M1485" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1485" t="inlineStr"/>
+      <c r="P1485" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEJALLEN31-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1486" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1486" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>87</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>-74.2</v>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1486" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1486" t="n">
+        <v>87</v>
+      </c>
+      <c r="M1486" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1486" t="inlineStr"/>
+      <c r="P1486" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY17CLEDET-CLEJALLEN31-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1487" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1487" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1487" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1487" t="n">
+        <v>36</v>
+      </c>
+      <c r="M1487" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1487" t="inlineStr"/>
+      <c r="P1487" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1488" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1488" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1488" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1488" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1488" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1488" t="inlineStr"/>
+      <c r="P1488" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETTHARRIS12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1489" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1489" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1489" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1489" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1489" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1489" t="inlineStr"/>
+      <c r="P1489" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1490" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1490" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>87</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>-78.8</v>
+      </c>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1490" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1490" t="n">
+        <v>87</v>
+      </c>
+      <c r="M1490" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1490" t="inlineStr"/>
+      <c r="P1490" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-DETTHARRIS12-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -93798,7 +95596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -94540,6 +96338,33 @@
       <c r="I23" t="n">
         <v>-0.3</v>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>32</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>32</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -94598,89 +96423,89 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>0.167</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.245</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.38</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cade Cunningham</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>0.245</v>
+        <v>0.196</v>
       </c>
       <c r="F4" t="n">
-        <v>3.91</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>0.196</v>
+        <v>0.167</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.64</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="6">
@@ -94690,7 +96515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -94712,7 +96537,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
@@ -94734,7 +96559,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
@@ -94756,7 +96581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
@@ -94774,45 +96599,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.158</v>
+        <v>0.216</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>0.216</v>
+        <v>0.158</v>
       </c>
       <c r="F11" t="n">
-        <v>53.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -95548,7 +97373,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -96632,7 +98457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C2" t="n">
         <v>31</v>
@@ -96654,7 +98479,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -96676,7 +98501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C4" t="n">
         <v>34</v>
@@ -96698,7 +98523,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C5" t="n">
         <v>118</v>
@@ -96720,7 +98545,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
         <v>31</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +55,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,14 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -93837,12 +93831,20 @@
       <c r="K1459" t="n">
         <v>10</v>
       </c>
-      <c r="M1459" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1459" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1459" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1459" t="inlineStr"/>
+      <c r="O1459" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1459" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-DETATHOMPSON9-20</t>
@@ -93893,12 +93895,20 @@
       <c r="K1460" t="n">
         <v>47</v>
       </c>
-      <c r="M1460" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1460" t="n">
+        <v>9</v>
+      </c>
+      <c r="M1460" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1460" t="inlineStr"/>
+      <c r="O1460" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1460" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-DETATHOMPSON9-8</t>
@@ -93949,12 +93959,20 @@
       <c r="K1461" t="n">
         <v>19</v>
       </c>
-      <c r="M1461" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1461" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1461" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1461" t="inlineStr"/>
+      <c r="O1461" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1461" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY17CLEDET-DETATHOMPSON9-8</t>
@@ -94005,12 +94023,20 @@
       <c r="K1462" t="n">
         <v>87</v>
       </c>
-      <c r="M1462" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1462" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1462" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1462" t="inlineStr"/>
+      <c r="O1462" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1462" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY17CLEDET-DETATHOMPSON9-3</t>
@@ -94061,12 +94087,20 @@
       <c r="K1463" t="n">
         <v>54</v>
       </c>
-      <c r="M1463" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1463" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1463" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1463" t="inlineStr"/>
+      <c r="O1463" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1463" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY17CLEDET-DETCCUNNINGHAM2-9</t>
@@ -94117,12 +94151,20 @@
       <c r="K1464" t="n">
         <v>30</v>
       </c>
-      <c r="M1464" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1464" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1464" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1464" t="inlineStr"/>
+      <c r="O1464" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1464" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-DETCCUNNINGHAM2-8</t>
@@ -94173,12 +94215,20 @@
       <c r="K1465" t="n">
         <v>21</v>
       </c>
-      <c r="M1465" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1465" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1465" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1465" t="inlineStr"/>
+      <c r="O1465" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1465" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-DETCCUNNINGHAM2-35</t>
@@ -94229,12 +94279,20 @@
       <c r="K1466" t="n">
         <v>87</v>
       </c>
-      <c r="M1466" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1466" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1466" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
+      <c r="O1466" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1466" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY17CLEDET-DETCCUNNINGHAM2-3</t>
@@ -94285,12 +94343,20 @@
       <c r="K1467" t="n">
         <v>13</v>
       </c>
-      <c r="M1467" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1467" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1467" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1467" t="inlineStr"/>
+      <c r="O1467" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1467" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-CLEDMITCHELL45-8</t>
@@ -94341,12 +94407,20 @@
       <c r="K1468" t="n">
         <v>12</v>
       </c>
-      <c r="M1468" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1468" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1468" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1468" t="inlineStr"/>
+      <c r="O1468" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1468" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY17CLEDET-CLEDMITCHELL45-8</t>
@@ -94397,12 +94471,20 @@
       <c r="K1469" t="n">
         <v>25</v>
       </c>
-      <c r="M1469" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1469" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1469" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1469" t="inlineStr"/>
+      <c r="O1469" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1469" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-CLEDMITCHELL45-35</t>
@@ -94453,12 +94535,20 @@
       <c r="K1470" t="n">
         <v>90</v>
       </c>
-      <c r="M1470" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1470" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1470" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1470" t="inlineStr"/>
+      <c r="O1470" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1470" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY17CLEDET-CLEDMITCHELL45-3</t>
@@ -94509,12 +94599,20 @@
       <c r="K1471" t="n">
         <v>11</v>
       </c>
-      <c r="M1471" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1471" t="n">
+        <v>14</v>
+      </c>
+      <c r="M1471" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1471" t="inlineStr"/>
+      <c r="O1471" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1471" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-DETDROBINSON55-20</t>
@@ -94565,12 +94663,20 @@
       <c r="K1472" t="n">
         <v>11</v>
       </c>
-      <c r="M1472" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1472" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1472" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1472" t="inlineStr"/>
+      <c r="O1472" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1472" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-CLEEMOBLEY4-25</t>
@@ -94621,12 +94727,20 @@
       <c r="K1473" t="n">
         <v>50</v>
       </c>
-      <c r="M1473" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1473" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1473" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1473" t="inlineStr"/>
+      <c r="O1473" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1473" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-CLEEMOBLEY4-9</t>
@@ -94677,12 +94791,20 @@
       <c r="K1474" t="n">
         <v>87</v>
       </c>
-      <c r="M1474" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1474" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1474" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1474" t="inlineStr"/>
+      <c r="O1474" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1474" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY17CLEDET-CLEEMOBLEY4-3</t>
@@ -94733,12 +94855,20 @@
       <c r="K1475" t="n">
         <v>84</v>
       </c>
-      <c r="M1475" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1475" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1475" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1475" t="inlineStr"/>
+      <c r="O1475" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1475" t="inlineStr">
         <is>
           <t>KXNBABLK-26MAY17CLEDET-CLEEMOBLEY4-4</t>
@@ -94789,12 +94919,22 @@
       <c r="K1476" t="n">
         <v>16</v>
       </c>
-      <c r="M1476" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1476" t="inlineStr"/>
+      <c r="L1476" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1476" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1476" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="O1476" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1476" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-DETJDUREN0-20</t>
@@ -94845,12 +94985,20 @@
       <c r="K1477" t="n">
         <v>56</v>
       </c>
-      <c r="M1477" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1477" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1477" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1477" t="inlineStr"/>
+      <c r="O1477" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1477" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-DETJDUREN0-9</t>
@@ -94901,12 +95049,20 @@
       <c r="K1478" t="n">
         <v>9</v>
       </c>
-      <c r="M1478" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1478" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1478" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1478" t="inlineStr"/>
+      <c r="O1478" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1478" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY17CLEDET-DETJDUREN0-8</t>
@@ -94957,12 +95113,20 @@
       <c r="K1479" t="n">
         <v>89</v>
       </c>
-      <c r="M1479" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1479" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1479" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1479" t="inlineStr"/>
+      <c r="O1479" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1479" t="inlineStr">
         <is>
           <t>KXNBABLK-26MAY17CLEDET-DETJDUREN0-3</t>
@@ -95013,12 +95177,22 @@
       <c r="K1480" t="n">
         <v>17</v>
       </c>
-      <c r="M1480" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1480" t="inlineStr"/>
+      <c r="L1480" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1480" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1480" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="O1480" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1480" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-CLEJHARDEN1-8</t>
@@ -95069,12 +95243,20 @@
       <c r="K1481" t="n">
         <v>11</v>
       </c>
-      <c r="M1481" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1481" t="n">
+        <v>23</v>
+      </c>
+      <c r="M1481" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1481" t="inlineStr"/>
+      <c r="O1481" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1481" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-CLEJHARDEN1-30</t>
@@ -95125,12 +95307,20 @@
       <c r="K1482" t="n">
         <v>39</v>
       </c>
-      <c r="M1482" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1482" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1482" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1482" t="inlineStr"/>
+      <c r="O1482" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1482" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY17CLEDET-CLEJHARDEN1-8</t>
@@ -95181,12 +95371,20 @@
       <c r="K1483" t="n">
         <v>90</v>
       </c>
-      <c r="M1483" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1483" t="n">
+        <v>4</v>
+      </c>
+      <c r="M1483" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1483" t="inlineStr"/>
+      <c r="O1483" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1483" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY17CLEDET-CLEJHARDEN1-3</t>
@@ -95237,12 +95435,22 @@
       <c r="K1484" t="n">
         <v>17</v>
       </c>
-      <c r="M1484" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N1484" t="inlineStr"/>
+      <c r="L1484" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1484" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="N1484" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="O1484" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1484" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-CLEJALLEN31-20</t>
@@ -95293,12 +95501,20 @@
       <c r="K1485" t="n">
         <v>55</v>
       </c>
-      <c r="M1485" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1485" t="n">
+        <v>8</v>
+      </c>
+      <c r="M1485" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
       <c r="N1485" t="inlineStr"/>
+      <c r="O1485" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1485" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-CLEJALLEN31-8</t>
@@ -95349,12 +95565,20 @@
       <c r="K1486" t="n">
         <v>87</v>
       </c>
-      <c r="M1486" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1486" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1486" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1486" t="inlineStr"/>
+      <c r="O1486" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1486" t="inlineStr">
         <is>
           <t>KXNBABLK-26MAY17CLEDET-CLEJALLEN31-3</t>
@@ -95405,12 +95629,20 @@
       <c r="K1487" t="n">
         <v>36</v>
       </c>
-      <c r="M1487" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1487" t="n">
+        <v>5</v>
+      </c>
+      <c r="M1487" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1487" t="inlineStr"/>
+      <c r="O1487" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1487" t="inlineStr">
         <is>
           <t>KXNBAREB-26MAY17CLEDET-DETTHARRIS12-8</t>
@@ -95461,12 +95693,20 @@
       <c r="K1488" t="n">
         <v>12</v>
       </c>
-      <c r="M1488" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1488" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1488" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
+      <c r="O1488" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1488" t="inlineStr">
         <is>
           <t>KXNBAPTS-26MAY17CLEDET-DETTHARRIS12-30</t>
@@ -95517,12 +95757,20 @@
       <c r="K1489" t="n">
         <v>19</v>
       </c>
-      <c r="M1489" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1489" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1489" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1489" t="inlineStr"/>
+      <c r="O1489" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1489" t="inlineStr">
         <is>
           <t>KXNBAAST-26MAY17CLEDET-DETTHARRIS12-8</t>
@@ -95573,12 +95821,20 @@
       <c r="K1490" t="n">
         <v>87</v>
       </c>
-      <c r="M1490" s="4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="L1490" t="n">
+        <v>2</v>
+      </c>
+      <c r="M1490" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="N1490" t="inlineStr"/>
+      <c r="O1490" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P1490" t="inlineStr">
         <is>
           <t>KXNBASTL-26MAY17CLEDET-DETTHARRIS12-3</t>
@@ -96349,22 +96605,26 @@
         <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.09</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -96430,13 +96690,13 @@
         <v>57</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.193</v>
       </c>
       <c r="F2" t="n">
         <v>-2.38</v>
@@ -96455,10 +96715,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>0.245</v>
+        <v>0.228</v>
       </c>
       <c r="F3" t="n">
         <v>3.91</v>
@@ -96477,10 +96737,10 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>0.196</v>
+        <v>0.182</v>
       </c>
       <c r="F4" t="n">
         <v>-2.64</v>
@@ -96521,10 +96781,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E6" t="n">
-        <v>0.082</v>
+        <v>0.075</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -96540,16 +96800,16 @@
         <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E7" t="n">
-        <v>0.224</v>
+        <v>0.226</v>
       </c>
       <c r="F7" t="n">
-        <v>9.66</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="8">
@@ -96565,10 +96825,10 @@
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>0.277</v>
+        <v>0.255</v>
       </c>
       <c r="F8" t="n">
         <v>-9.640000000000001</v>
@@ -96584,16 +96844,16 @@
         <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>0.122</v>
+        <v>0.156</v>
       </c>
       <c r="F9" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="10">
@@ -96606,16 +96866,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>0.216</v>
+        <v>0.225</v>
       </c>
       <c r="F10" t="n">
-        <v>53.99</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="11">
@@ -97379,7 +97639,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -98463,10 +98723,10 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E2" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="F2" t="n">
         <v>-17.67</v>
@@ -98482,13 +98742,13 @@
         <v>119</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>0.133</v>
+        <v>0.138</v>
       </c>
       <c r="F3" t="n">
         <v>-1.44</v>
@@ -98507,13 +98767,13 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="F4" t="n">
-        <v>68.26000000000001</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="5">
@@ -98526,16 +98786,16 @@
         <v>363</v>
       </c>
       <c r="C5" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D5" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E5" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="F5" t="n">
-        <v>-19.87</v>
+        <v>-21.74</v>
       </c>
     </row>
     <row r="6">
@@ -98548,13 +98808,13 @@
         <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E6" t="n">
-        <v>0.144</v>
+        <v>0.149</v>
       </c>
       <c r="F6" t="n">
         <v>4.27</v>

--- a/results/picks_report.xlsx
+++ b/results/picks_report.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +73,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1490"/>
+  <dimension ref="A1:P1524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -95841,6 +95847,1910 @@
         </is>
       </c>
     </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1491" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1491" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1491" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1491" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1491" t="inlineStr"/>
+      <c r="P1491" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETATHOMPSON9-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1492" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1492" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1492" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1492" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1492" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1492" t="inlineStr"/>
+      <c r="P1492" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1493" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1493" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="I1493" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1493" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1493" t="n">
+        <v>44</v>
+      </c>
+      <c r="M1493" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1493" t="inlineStr"/>
+      <c r="P1493" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETATHOMPSON9-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1494" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1494" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="I1494" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1494" t="n">
+        <v>39</v>
+      </c>
+      <c r="M1494" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1494" t="inlineStr"/>
+      <c r="P1494" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-DETATHOMPSON9-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1495" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1495" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I1495" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1495" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1495" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1495" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1495" t="inlineStr"/>
+      <c r="P1495" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETCCUNNINGHAM2-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1496" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1496" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I1496" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1496" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1496" t="n">
+        <v>52</v>
+      </c>
+      <c r="M1496" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1496" t="inlineStr"/>
+      <c r="P1496" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETCCUNNINGHAM2-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1497" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1497" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="I1497" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1497" t="n">
+        <v>19</v>
+      </c>
+      <c r="M1497" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1497" t="inlineStr"/>
+      <c r="P1497" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETCCUNNINGHAM2-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1498" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1498" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="I1498" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1498" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1498" t="n">
+        <v>21</v>
+      </c>
+      <c r="M1498" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1498" t="inlineStr"/>
+      <c r="P1498" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-DETCCUNNINGHAM2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1499" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1499" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>86</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>-81.3</v>
+      </c>
+      <c r="I1499" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1499" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1499" t="n">
+        <v>86</v>
+      </c>
+      <c r="M1499" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1499" t="inlineStr"/>
+      <c r="P1499" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-CLEDSCHRODER8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Dennis Schroder</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1500" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1500" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>94</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>-89</v>
+      </c>
+      <c r="I1500" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1500" t="n">
+        <v>94</v>
+      </c>
+      <c r="M1500" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1500" t="inlineStr"/>
+      <c r="P1500" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEDSCHRODER8-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1501" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1501" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1501" t="n">
+        <v>17</v>
+      </c>
+      <c r="M1501" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1501" t="inlineStr"/>
+      <c r="P1501" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEDMITCHELL45-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1502" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1502" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I1502" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1502" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1502" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1502" t="inlineStr"/>
+      <c r="P1502" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1503" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1503" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1503" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1503" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1503" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1503" t="inlineStr"/>
+      <c r="P1503" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEDMITCHELL45-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Donovan Mitchell</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1504" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1504" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="I1504" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1504" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1504" t="n">
+        <v>15</v>
+      </c>
+      <c r="M1504" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1504" t="inlineStr"/>
+      <c r="P1504" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-CLEDMITCHELL45-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Duncan Robinson</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1505" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1505" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I1505" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1505" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1505" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1505" t="inlineStr"/>
+      <c r="P1505" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETDROBINSON55-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1506" t="n">
+        <v>25</v>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1506" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1506" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1506" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1506" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1506" t="inlineStr"/>
+      <c r="P1506" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEEMOBLEY4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1507" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1507" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1507" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1507" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1507" t="inlineStr"/>
+      <c r="P1507" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-CLEEMOBLEY4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1508" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1508" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1508" t="n">
+        <v>47</v>
+      </c>
+      <c r="M1508" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1508" t="inlineStr"/>
+      <c r="P1508" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEEMOBLEY4-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1509" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1509" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1509" t="n">
+        <v>20</v>
+      </c>
+      <c r="M1509" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1509" t="inlineStr"/>
+      <c r="P1509" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY17CLEDET-CLEEMOBLEY4-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1510" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1510" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1510" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1510" t="n">
+        <v>13</v>
+      </c>
+      <c r="M1510" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1510" t="inlineStr"/>
+      <c r="P1510" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETJDUREN0-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1511" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1511" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1511" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1511" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1511" t="n">
+        <v>55</v>
+      </c>
+      <c r="M1511" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1511" t="inlineStr"/>
+      <c r="P1511" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETJDUREN0-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1512" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1512" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1512" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1512" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1512" t="inlineStr"/>
+      <c r="P1512" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETJDUREN0-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1513" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1513" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1513" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1513" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1513" t="inlineStr"/>
+      <c r="P1513" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY17CLEDET-DETJDUREN0-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1514" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1514" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1514" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1514" t="n">
+        <v>25</v>
+      </c>
+      <c r="K1514" t="n">
+        <v>12</v>
+      </c>
+      <c r="M1514" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1514" t="inlineStr"/>
+      <c r="P1514" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1515" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1515" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1515" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I1515" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1515" t="n">
+        <v>20</v>
+      </c>
+      <c r="M1515" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1515" t="inlineStr"/>
+      <c r="P1515" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-CLEJHARDEN1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1516" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1516" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I1516" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1516" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1516" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1516" t="inlineStr"/>
+      <c r="P1516" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEJHARDEN1-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>James Harden</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1517" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1517" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>34</v>
+      </c>
+      <c r="H1517" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="I1517" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1517" t="n">
+        <v>34</v>
+      </c>
+      <c r="M1517" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1517" t="inlineStr"/>
+      <c r="P1517" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-CLEJHARDEN1-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1518" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1518" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1518" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I1518" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1518" t="n">
+        <v>18</v>
+      </c>
+      <c r="K1518" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1518" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1518" t="inlineStr"/>
+      <c r="P1518" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-CLEJALLEN31-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1519" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1519" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I1519" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1519" t="n">
+        <v>52</v>
+      </c>
+      <c r="M1519" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1519" t="inlineStr"/>
+      <c r="P1519" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-CLEJALLEN31-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Jarrett Allen</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D1520" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1520" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1520" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="I1520" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1520" t="n">
+        <v>23</v>
+      </c>
+      <c r="M1520" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1520" t="inlineStr"/>
+      <c r="P1520" t="inlineStr">
+        <is>
+          <t>KXNBABLK-26MAY17CLEDET-CLEJALLEN31-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="D1521" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1521" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I1521" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1521" t="n">
+        <v>31</v>
+      </c>
+      <c r="M1521" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1521" t="inlineStr"/>
+      <c r="P1521" t="inlineStr">
+        <is>
+          <t>KXNBAREB-26MAY17CLEDET-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="D1522" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1522" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1522" t="n">
+        <v>3</v>
+      </c>
+      <c r="M1522" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1522" t="inlineStr"/>
+      <c r="P1522" t="inlineStr">
+        <is>
+          <t>KXNBAAST-26MAY17CLEDET-DETTHARRIS12-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="D1523" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1523" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I1523" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1523" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1523" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1523" t="inlineStr"/>
+      <c r="P1523" t="inlineStr">
+        <is>
+          <t>KXNBAPTS-26MAY17CLEDET-DETTHARRIS12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Tobias Harris</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D1524" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F1524" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I1524" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1524" t="n">
+        <v>18</v>
+      </c>
+      <c r="M1524" s="4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N1524" t="inlineStr"/>
+      <c r="P1524" t="inlineStr">
+        <is>
+          <t>KXNBASTL-26MAY17CLEDET-DETTHARRIS12-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -95852,7 +97762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -96625,6 +98535,33 @@
       <c r="I24" t="n">
         <v>-0.09</v>
       </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>34</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>34</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -96687,7 +98624,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
@@ -96709,7 +98646,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
@@ -96731,7 +98668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
@@ -96749,89 +98686,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lebron James</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>0.167</v>
+        <v>0.075</v>
       </c>
       <c r="F5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
-        <v>0.075</v>
+        <v>0.226</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
-        <v>0.226</v>
+        <v>0.255</v>
       </c>
       <c r="F7" t="n">
-        <v>7.79</v>
+        <v>-9.640000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Lebron James</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>0.255</v>
+        <v>0.167</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.640000000000001</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -96841,7 +98778,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -96863,7 +98800,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
@@ -97299,64 +99236,64 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-16.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>18</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>0.278</v>
+        <v>0.111</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-16.56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alperen Sengun</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>18</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>0.333</v>
+        <v>0.278</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -97365,20 +99302,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>18</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>0.278</v>
+        <v>0.333</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -97387,20 +99324,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -97563,20 +99500,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>15</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -97585,20 +99522,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>15</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>0.267</v>
+        <v>0.067</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -97607,45 +99544,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E44" t="n">
-        <v>0.143</v>
+        <v>0.267</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>14</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="46">
@@ -98717,7 +100654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C2" t="n">
         <v>31</v>
@@ -98739,7 +100676,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C3" t="n">
         <v>16</v>
@@ -98761,7 +100698,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C4" t="n">
         <v>34</v>
@@ -98783,7 +100720,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C5" t="n">
         <v>121</v>
@@ -98805,7 +100742,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
         <v>33</v>
